--- a/Deliverables/BOM/Espark_BOM.xlsx
+++ b/Deliverables/BOM/Espark_BOM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\JohnWollam-LCDProject\Deliverables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\JohnWollam-LCDProject\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="230">
   <si>
     <t>Component list</t>
   </si>
@@ -589,77 +589,149 @@
     <t>LCSC</t>
   </si>
   <si>
-    <t>ARG05DTC5002</t>
-  </si>
-  <si>
-    <t>C2828840</t>
-  </si>
-  <si>
     <t>RC1206JR-073R6L</t>
   </si>
   <si>
+    <t>LBSS138LT1G</t>
+  </si>
+  <si>
+    <t>Solder Brigde</t>
+  </si>
+  <si>
+    <t>FFH25405-S16S1001K6K</t>
+  </si>
+  <si>
+    <t>C2834190</t>
+  </si>
+  <si>
+    <t>5TJ480000XYLBC</t>
+  </si>
+  <si>
+    <t>Do not mount</t>
+  </si>
+  <si>
+    <t>Total Cost</t>
+  </si>
+  <si>
+    <t>Cost per Board</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>C106221</t>
+  </si>
+  <si>
+    <t>C105621</t>
+  </si>
+  <si>
+    <t>C105174</t>
+  </si>
+  <si>
+    <t>C100042</t>
+  </si>
+  <si>
+    <t>C90057</t>
+  </si>
+  <si>
+    <t>C107092</t>
+  </si>
+  <si>
+    <t>C7230</t>
+  </si>
+  <si>
+    <t>C60580</t>
+  </si>
+  <si>
+    <t>C2886579</t>
+  </si>
+  <si>
+    <t>C8465</t>
+  </si>
+  <si>
+    <t>C93225</t>
+  </si>
+  <si>
+    <t>C105575</t>
+  </si>
+  <si>
+    <t>C98220</t>
+  </si>
+  <si>
+    <t>C114630</t>
+  </si>
+  <si>
+    <t>C103893</t>
+  </si>
+  <si>
+    <t>C374641</t>
+  </si>
+  <si>
+    <t>C22765</t>
+  </si>
+  <si>
+    <t>C273526</t>
+  </si>
+  <si>
+    <t>C2053863</t>
+  </si>
+  <si>
+    <t>C435835</t>
+  </si>
+  <si>
+    <t>C100023</t>
+  </si>
+  <si>
+    <t>C132564</t>
+  </si>
+  <si>
+    <t>C191227</t>
+  </si>
+  <si>
+    <t>JL301-50010U02</t>
+  </si>
+  <si>
+    <t>C409141</t>
+  </si>
+  <si>
+    <t>Design change needed</t>
+  </si>
+  <si>
+    <t>Alternate suggested due to low stock</t>
+  </si>
+  <si>
+    <t>PZ254V-11-03P</t>
+  </si>
+  <si>
+    <t>C2937625</t>
+  </si>
+  <si>
+    <t>C8490</t>
+  </si>
+  <si>
+    <t>AR03BTC5002A</t>
+  </si>
+  <si>
+    <t>C304067</t>
+  </si>
+  <si>
     <t>C246070</t>
   </si>
   <si>
-    <t>Custum Supplier</t>
-  </si>
-  <si>
-    <t>Custom Supplier</t>
-  </si>
-  <si>
-    <t>LBSS138LT1G</t>
-  </si>
-  <si>
-    <t>C8490</t>
-  </si>
-  <si>
-    <t>Solder Brigde</t>
-  </si>
-  <si>
-    <t>FFH25405-S16S1001K6K</t>
-  </si>
-  <si>
-    <t>C2834190</t>
-  </si>
-  <si>
-    <t>5TJ480000XYLBC</t>
-  </si>
-  <si>
     <t>C2149247</t>
-  </si>
-  <si>
-    <t>Do not mount</t>
-  </si>
-  <si>
-    <t>Slight change in Footprint</t>
-  </si>
-  <si>
-    <t>Less Stock</t>
-  </si>
-  <si>
-    <t>Wattage ratting is different</t>
-  </si>
-  <si>
-    <t>Total Cost</t>
-  </si>
-  <si>
-    <t>Cost per Board</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
-    <numFmt numFmtId="172" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -860,6 +932,13 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1152,7 +1231,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1283,21 +1362,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1311,7 +1375,7 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="18" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1332,7 +1396,7 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="23" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="23" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1350,7 +1414,7 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="18" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1371,7 +1435,7 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="18" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1401,7 +1465,7 @@
     <xf numFmtId="165" fontId="19" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="19" fillId="2" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1410,25 +1474,16 @@
     <xf numFmtId="165" fontId="19" fillId="4" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="19" fillId="4" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="4" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="19" fillId="2" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="19" fillId="2" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1440,7 +1495,7 @@
     <xf numFmtId="165" fontId="24" fillId="2" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="23" fillId="2" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="23" fillId="2" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1455,13 +1510,13 @@
     <xf numFmtId="165" fontId="19" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="19" fillId="2" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="17" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="17" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="17" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="17" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1470,6 +1525,65 @@
     <xf numFmtId="0" fontId="28" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="4" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1516,7 +1630,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1814,7 +1928,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:W42"/>
+  <dimension ref="A1:AF86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -1839,9 +1953,11 @@
     <col min="21" max="21" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1852,17 +1968,17 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="51"/>
-    </row>
-    <row r="2" spans="1:23" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="121"/>
+    </row>
+    <row r="2" spans="1:29" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="35"/>
@@ -1885,13 +2001,13 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="54"/>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="S2" s="123"/>
+      <c r="T2" s="123"/>
+      <c r="U2" s="123"/>
+      <c r="V2" s="123"/>
+      <c r="W2" s="124"/>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="36"/>
@@ -1906,21 +2022,21 @@
       <c r="H3" s="4"/>
       <c r="I3" s="12"/>
       <c r="J3" s="4"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="55"/>
-      <c r="O3" s="55"/>
-      <c r="P3" s="55"/>
-      <c r="Q3" s="55"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
-      <c r="V3" s="56"/>
-      <c r="W3" s="52"/>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="50"/>
+      <c r="Q3" s="50"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="51"/>
+      <c r="U3" s="51"/>
+      <c r="V3" s="51"/>
+      <c r="W3" s="122"/>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="36"/>
@@ -1947,9 +2063,9 @@
       <c r="T4" s="47"/>
       <c r="U4" s="47"/>
       <c r="V4" s="47"/>
-      <c r="W4" s="52"/>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W4" s="122"/>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="36"/>
@@ -1976,9 +2092,9 @@
       <c r="T5" s="48"/>
       <c r="U5" s="48"/>
       <c r="V5" s="48"/>
-      <c r="W5" s="52"/>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W5" s="122"/>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="37"/>
@@ -2001,9 +2117,9 @@
       <c r="T6" s="48"/>
       <c r="U6" s="48"/>
       <c r="V6" s="48"/>
-      <c r="W6" s="52"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W6" s="122"/>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="38"/>
@@ -2026,9 +2142,9 @@
       <c r="T7" s="45"/>
       <c r="U7" s="45"/>
       <c r="V7" s="45"/>
-      <c r="W7" s="52"/>
-    </row>
-    <row r="8" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="W7" s="122"/>
+    </row>
+    <row r="8" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
       <c r="C8" s="39"/>
@@ -2051,2138 +2167,2377 @@
       <c r="T8" s="46"/>
       <c r="U8" s="46"/>
       <c r="V8" s="46"/>
-      <c r="W8" s="52"/>
-    </row>
-    <row r="9" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="W8" s="122"/>
+    </row>
+    <row r="9" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="86" t="s">
+      <c r="C9" s="81" t="s">
         <v>161</v>
       </c>
-      <c r="D9" s="86" t="s">
+      <c r="D9" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="87" t="s">
+      <c r="E9" s="82" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="86" t="s">
+      <c r="F9" s="81" t="s">
         <v>72</v>
       </c>
-      <c r="G9" s="87" t="s">
+      <c r="G9" s="82" t="s">
         <v>88</v>
       </c>
-      <c r="H9" s="86" t="s">
+      <c r="H9" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="I9" s="86" t="s">
+      <c r="I9" s="81" t="s">
         <v>162</v>
       </c>
-      <c r="J9" s="86" t="s">
+      <c r="J9" s="81" t="s">
         <v>163</v>
       </c>
-      <c r="K9" s="86" t="s">
+      <c r="K9" s="81" t="s">
         <v>140</v>
       </c>
-      <c r="L9" s="87" t="s">
+      <c r="L9" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="M9" s="86" t="s">
+      <c r="M9" s="81" t="s">
         <v>177</v>
       </c>
-      <c r="N9" s="86" t="s">
+      <c r="N9" s="81" t="s">
         <v>178</v>
       </c>
-      <c r="O9" s="86" t="s">
+      <c r="O9" s="81" t="s">
         <v>179</v>
       </c>
-      <c r="P9" s="86" t="s">
+      <c r="P9" s="81" t="s">
         <v>180</v>
       </c>
-      <c r="Q9" s="86" t="s">
+      <c r="Q9" s="81" t="s">
         <v>164</v>
       </c>
-      <c r="R9" s="86" t="s">
+      <c r="R9" s="81" t="s">
         <v>181</v>
       </c>
-      <c r="S9" s="86" t="s">
+      <c r="S9" s="81" t="s">
         <v>182</v>
       </c>
-      <c r="T9" s="86" t="s">
+      <c r="T9" s="81" t="s">
         <v>183</v>
       </c>
-      <c r="U9" s="86" t="s">
+      <c r="U9" s="81" t="s">
         <v>184</v>
       </c>
-      <c r="V9" s="57" t="s">
+      <c r="V9" s="52" t="s">
         <v>165</v>
       </c>
-      <c r="W9" s="57" t="s">
+      <c r="W9" s="52" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="58">
+      <c r="B10" s="53">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="54" t="s">
         <v>167</v>
       </c>
-      <c r="D10" s="59" t="s">
+      <c r="D10" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="59" t="s">
+      <c r="E10" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="59" t="s">
+      <c r="F10" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="G10" s="59" t="s">
+      <c r="G10" s="54" t="s">
         <v>89</v>
       </c>
-      <c r="H10" s="59" t="s">
+      <c r="H10" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="I10" s="83"/>
-      <c r="J10" s="83"/>
-      <c r="K10" s="59" t="s">
+      <c r="I10" s="78"/>
+      <c r="J10" s="78" t="s">
+        <v>196</v>
+      </c>
+      <c r="K10" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="L10" s="59">
+      <c r="L10" s="54">
         <v>6</v>
       </c>
-      <c r="M10" s="59">
+      <c r="M10" s="54">
         <f>L10*10</f>
         <v>60</v>
       </c>
-      <c r="N10" s="59">
+      <c r="N10" s="54">
         <v>100</v>
       </c>
-      <c r="O10" s="59">
+      <c r="O10" s="54">
         <f>L10*25</f>
         <v>150</v>
       </c>
-      <c r="P10" s="59">
+      <c r="P10" s="54">
         <v>200</v>
       </c>
-      <c r="Q10" s="88" t="s">
+      <c r="Q10" s="83" t="s">
         <v>185</v>
       </c>
-      <c r="R10" s="89">
+      <c r="R10" s="84">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="S10" s="90">
+      <c r="S10" s="85">
         <f>R10*N10</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="T10" s="89">
+      <c r="T10" s="84">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="U10" s="60">
+      <c r="U10" s="55">
         <f>T10*P10</f>
         <v>0.57999999999999996</v>
       </c>
-      <c r="V10" s="59"/>
-      <c r="W10" s="61"/>
-    </row>
-    <row r="11" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V10" s="54"/>
+      <c r="W10" s="56"/>
+      <c r="Y10" s="105"/>
+      <c r="Z10" s="105"/>
+      <c r="AA10" s="105"/>
+      <c r="AB10" s="106"/>
+      <c r="AC10" s="106"/>
+    </row>
+    <row r="11" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="58">
+      <c r="B11" s="53">
         <f t="shared" ref="B11:B39" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="62" t="s">
+      <c r="C11" s="57" t="s">
         <v>167</v>
       </c>
-      <c r="D11" s="62" t="s">
+      <c r="D11" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="62" t="s">
+      <c r="E11" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="62" t="s">
+      <c r="F11" s="57" t="s">
         <v>73</v>
       </c>
-      <c r="G11" s="62" t="s">
+      <c r="G11" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="H11" s="62" t="s">
+      <c r="H11" s="57" t="s">
         <v>117</v>
       </c>
-      <c r="I11" s="84"/>
-      <c r="J11" s="84"/>
-      <c r="K11" s="62" t="s">
+      <c r="I11" s="79"/>
+      <c r="J11" s="79" t="s">
+        <v>197</v>
+      </c>
+      <c r="K11" s="57" t="s">
         <v>142</v>
       </c>
-      <c r="L11" s="62">
+      <c r="L11" s="57">
         <v>2</v>
       </c>
-      <c r="M11" s="62">
+      <c r="M11" s="57">
         <f>L11*10</f>
         <v>20</v>
       </c>
-      <c r="N11" s="62">
+      <c r="N11" s="57">
         <v>100</v>
       </c>
-      <c r="O11" s="62">
+      <c r="O11" s="57">
         <f t="shared" ref="O11:O40" si="1">L11*25</f>
         <v>50</v>
       </c>
-      <c r="P11" s="62">
+      <c r="P11" s="57">
         <v>100</v>
       </c>
-      <c r="Q11" s="91" t="s">
+      <c r="Q11" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="R11" s="92">
+      <c r="R11" s="87">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="S11" s="93">
+      <c r="S11" s="88">
         <f t="shared" ref="S11:S40" si="2">R11*N11</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="T11" s="92">
+      <c r="T11" s="87">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="U11" s="80">
+      <c r="U11" s="75">
         <f t="shared" ref="U11:U40" si="3">T11*P11</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="V11" s="62"/>
-      <c r="W11" s="63"/>
-    </row>
-    <row r="12" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V11" s="57"/>
+      <c r="W11" s="58"/>
+      <c r="Y11" s="105"/>
+      <c r="Z11" s="105"/>
+      <c r="AA11" s="105"/>
+      <c r="AB11" s="106"/>
+      <c r="AC11" s="106"/>
+    </row>
+    <row r="12" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="58">
+      <c r="B12" s="53">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="C12" s="54" t="s">
         <v>167</v>
       </c>
-      <c r="D12" s="59" t="s">
+      <c r="D12" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="59" t="s">
+      <c r="E12" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="59" t="s">
+      <c r="F12" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="G12" s="59" t="s">
+      <c r="G12" s="54" t="s">
         <v>91</v>
       </c>
-      <c r="H12" s="59" t="s">
+      <c r="H12" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="I12" s="83"/>
-      <c r="J12" s="83"/>
-      <c r="K12" s="59" t="s">
+      <c r="I12" s="78"/>
+      <c r="J12" s="78" t="s">
+        <v>198</v>
+      </c>
+      <c r="K12" s="54" t="s">
         <v>143</v>
       </c>
-      <c r="L12" s="59">
+      <c r="L12" s="54">
         <v>2</v>
       </c>
-      <c r="M12" s="59">
+      <c r="M12" s="54">
         <f t="shared" ref="M12:M40" si="4">L12*10</f>
         <v>20</v>
       </c>
-      <c r="N12" s="59">
+      <c r="N12" s="54">
         <v>40</v>
       </c>
-      <c r="O12" s="59">
+      <c r="O12" s="54">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="P12" s="59">
+      <c r="P12" s="54">
         <v>60</v>
       </c>
-      <c r="Q12" s="88" t="s">
+      <c r="Q12" s="83" t="s">
         <v>185</v>
       </c>
-      <c r="R12" s="89">
-        <v>3.95E-2</v>
-      </c>
-      <c r="S12" s="90">
+      <c r="R12" s="84">
+        <v>2.9399999999999999E-2</v>
+      </c>
+      <c r="S12" s="85">
         <f t="shared" si="2"/>
-        <v>1.58</v>
-      </c>
-      <c r="T12" s="89">
-        <v>3.95E-2</v>
-      </c>
-      <c r="U12" s="60">
+        <v>1.1759999999999999</v>
+      </c>
+      <c r="T12" s="84">
+        <v>2.9399999999999999E-2</v>
+      </c>
+      <c r="U12" s="55">
         <f t="shared" si="3"/>
-        <v>2.37</v>
-      </c>
-      <c r="V12" s="59"/>
-      <c r="W12" s="76"/>
-    </row>
-    <row r="13" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1.764</v>
+      </c>
+      <c r="V12" s="54"/>
+      <c r="W12" s="71"/>
+      <c r="Y12" s="105"/>
+      <c r="Z12" s="105"/>
+      <c r="AA12" s="105"/>
+      <c r="AB12" s="106"/>
+      <c r="AC12" s="106"/>
+    </row>
+    <row r="13" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="58">
+      <c r="B13" s="53">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="62" t="s">
+      <c r="C13" s="57" t="s">
         <v>167</v>
       </c>
-      <c r="D13" s="62" t="s">
+      <c r="D13" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="62" t="s">
+      <c r="E13" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="62" t="s">
+      <c r="F13" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="G13" s="62" t="s">
+      <c r="G13" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="H13" s="62" t="s">
+      <c r="H13" s="57" t="s">
         <v>117</v>
       </c>
-      <c r="I13" s="84"/>
-      <c r="J13" s="84"/>
-      <c r="K13" s="62" t="s">
+      <c r="I13" s="79"/>
+      <c r="J13" s="79" t="s">
+        <v>199</v>
+      </c>
+      <c r="K13" s="57" t="s">
         <v>144</v>
       </c>
-      <c r="L13" s="62">
+      <c r="L13" s="57">
         <v>1</v>
       </c>
-      <c r="M13" s="62">
+      <c r="M13" s="57">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N13" s="62">
+      <c r="N13" s="57">
         <v>100</v>
       </c>
-      <c r="O13" s="62">
+      <c r="O13" s="57">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P13" s="62">
+      <c r="P13" s="57">
         <v>100</v>
       </c>
-      <c r="Q13" s="91" t="s">
+      <c r="Q13" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="R13" s="92">
+      <c r="R13" s="87">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="S13" s="93">
+      <c r="S13" s="88">
         <f t="shared" si="2"/>
         <v>0.22</v>
       </c>
-      <c r="T13" s="92">
+      <c r="T13" s="87">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="U13" s="80">
+      <c r="U13" s="75">
         <f t="shared" si="3"/>
         <v>0.22</v>
       </c>
-      <c r="V13" s="62"/>
-      <c r="W13" s="63"/>
-    </row>
-    <row r="14" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V13" s="57"/>
+      <c r="W13" s="58"/>
+      <c r="Y13" s="105"/>
+      <c r="Z13" s="105"/>
+      <c r="AA13" s="105"/>
+      <c r="AB13" s="106"/>
+      <c r="AC13" s="106"/>
+    </row>
+    <row r="14" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="58">
+      <c r="B14" s="53">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="54" t="s">
         <v>167</v>
       </c>
-      <c r="D14" s="59" t="s">
+      <c r="D14" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="59" t="s">
+      <c r="E14" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="F14" s="59" t="s">
+      <c r="F14" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="G14" s="59" t="s">
+      <c r="G14" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="H14" s="59" t="s">
+      <c r="H14" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="I14" s="83"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="59" t="s">
+      <c r="I14" s="78"/>
+      <c r="J14" s="78" t="s">
+        <v>200</v>
+      </c>
+      <c r="K14" s="54" t="s">
         <v>145</v>
       </c>
-      <c r="L14" s="59">
+      <c r="L14" s="54">
         <v>2</v>
       </c>
-      <c r="M14" s="59">
+      <c r="M14" s="54">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="N14" s="59">
+      <c r="N14" s="54">
         <v>30</v>
       </c>
-      <c r="O14" s="59">
+      <c r="O14" s="54">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="P14" s="59">
+      <c r="P14" s="54">
         <v>60</v>
       </c>
-      <c r="Q14" s="88" t="s">
+      <c r="Q14" s="83" t="s">
         <v>185</v>
       </c>
-      <c r="R14" s="89">
+      <c r="R14" s="84">
         <v>6.7699999999999996E-2</v>
       </c>
-      <c r="S14" s="90">
+      <c r="S14" s="85">
         <f t="shared" si="2"/>
         <v>2.0309999999999997</v>
       </c>
-      <c r="T14" s="89">
+      <c r="T14" s="84">
         <v>6.7699999999999996E-2</v>
       </c>
-      <c r="U14" s="60">
+      <c r="U14" s="55">
         <f t="shared" si="3"/>
         <v>4.0619999999999994</v>
       </c>
-      <c r="V14" s="59"/>
-      <c r="W14" s="79"/>
-    </row>
-    <row r="15" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V14" s="54"/>
+      <c r="W14" s="74"/>
+      <c r="Y14" s="105"/>
+      <c r="Z14" s="105"/>
+      <c r="AA14" s="105"/>
+      <c r="AB14" s="106"/>
+      <c r="AC14" s="106"/>
+    </row>
+    <row r="15" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="58">
+      <c r="B15" s="53">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="62" t="s">
+      <c r="C15" s="57" t="s">
         <v>167</v>
       </c>
-      <c r="D15" s="62" t="s">
+      <c r="D15" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="62" t="s">
+      <c r="E15" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="62" t="s">
+      <c r="F15" s="57" t="s">
         <v>73</v>
       </c>
-      <c r="G15" s="62" t="s">
+      <c r="G15" s="57" t="s">
         <v>94</v>
       </c>
-      <c r="H15" s="62" t="s">
+      <c r="H15" s="57" t="s">
         <v>117</v>
       </c>
-      <c r="I15" s="84"/>
-      <c r="J15" s="84"/>
-      <c r="K15" s="62" t="s">
+      <c r="I15" s="79"/>
+      <c r="J15" s="79" t="s">
+        <v>201</v>
+      </c>
+      <c r="K15" s="57" t="s">
         <v>146</v>
       </c>
-      <c r="L15" s="62">
+      <c r="L15" s="57">
         <v>1</v>
       </c>
-      <c r="M15" s="62">
+      <c r="M15" s="57">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N15" s="62">
+      <c r="N15" s="57">
         <v>100</v>
       </c>
-      <c r="O15" s="62">
+      <c r="O15" s="57">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P15" s="62">
+      <c r="P15" s="57">
         <v>100</v>
       </c>
-      <c r="Q15" s="91" t="s">
+      <c r="Q15" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="R15" s="92">
+      <c r="R15" s="87">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="S15" s="93">
+      <c r="S15" s="88">
         <f t="shared" si="2"/>
         <v>0.26</v>
       </c>
-      <c r="T15" s="92">
+      <c r="T15" s="87">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="U15" s="80">
+      <c r="U15" s="75">
         <f t="shared" si="3"/>
         <v>0.26</v>
       </c>
-      <c r="V15" s="62"/>
-      <c r="W15" s="63"/>
-    </row>
-    <row r="16" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V15" s="57"/>
+      <c r="W15" s="58"/>
+      <c r="Y15" s="105"/>
+      <c r="Z15" s="105"/>
+      <c r="AA15" s="105"/>
+      <c r="AB15" s="106"/>
+      <c r="AC15" s="106"/>
+    </row>
+    <row r="16" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="58">
+      <c r="B16" s="53">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="59" t="s">
+      <c r="C16" s="54" t="s">
         <v>167</v>
       </c>
-      <c r="D16" s="59" t="s">
+      <c r="D16" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="G16" s="59" t="s">
+      <c r="G16" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="H16" s="59" t="s">
+      <c r="H16" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="I16" s="83"/>
-      <c r="J16" s="83"/>
-      <c r="K16" s="59" t="s">
+      <c r="I16" s="78"/>
+      <c r="J16" s="78" t="s">
+        <v>202</v>
+      </c>
+      <c r="K16" s="54" t="s">
         <v>147</v>
       </c>
-      <c r="L16" s="59">
+      <c r="L16" s="54">
         <v>1</v>
       </c>
-      <c r="M16" s="59">
+      <c r="M16" s="54">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N16" s="59">
-        <v>15</v>
-      </c>
-      <c r="O16" s="59">
+      <c r="N16" s="54">
+        <v>12</v>
+      </c>
+      <c r="O16" s="54">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P16" s="59">
-        <v>30</v>
-      </c>
-      <c r="Q16" s="88" t="s">
+      <c r="P16" s="54">
+        <v>28</v>
+      </c>
+      <c r="Q16" s="83" t="s">
         <v>185</v>
       </c>
-      <c r="R16" s="89">
+      <c r="R16" s="84">
         <v>0.8125</v>
       </c>
-      <c r="S16" s="90">
+      <c r="S16" s="85">
         <f t="shared" si="2"/>
-        <v>12.1875</v>
-      </c>
-      <c r="T16" s="89">
+        <v>9.75</v>
+      </c>
+      <c r="T16" s="84">
         <v>0.78839999999999999</v>
       </c>
-      <c r="U16" s="60">
+      <c r="U16" s="55">
         <f t="shared" si="3"/>
-        <v>23.652000000000001</v>
-      </c>
-      <c r="V16" s="59"/>
-      <c r="W16" s="79"/>
-    </row>
-    <row r="17" spans="1:23" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>22.075199999999999</v>
+      </c>
+      <c r="V16" s="54"/>
+      <c r="W16" s="74"/>
+      <c r="Y16" s="105"/>
+      <c r="Z16" s="105"/>
+      <c r="AA16" s="105"/>
+      <c r="AB16" s="106"/>
+      <c r="AC16" s="106"/>
+    </row>
+    <row r="17" spans="1:29" s="113" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="58">
+      <c r="B17" s="107">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="62" t="s">
+      <c r="C17" s="108" t="s">
         <v>167</v>
       </c>
-      <c r="D17" s="62" t="s">
+      <c r="D17" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="62" t="s">
+      <c r="E17" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="62" t="s">
+      <c r="F17" s="108" t="s">
         <v>166</v>
       </c>
-      <c r="G17" s="62" t="s">
+      <c r="G17" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="H17" s="62" t="s">
+      <c r="H17" s="108" t="s">
         <v>121</v>
       </c>
-      <c r="I17" s="84"/>
-      <c r="J17" s="84"/>
-      <c r="K17" s="62" t="s">
+      <c r="I17" s="109"/>
+      <c r="J17" s="108" t="s">
+        <v>218</v>
+      </c>
+      <c r="K17" s="108" t="s">
         <v>148</v>
       </c>
-      <c r="L17" s="62">
+      <c r="L17" s="108">
         <v>1</v>
       </c>
-      <c r="M17" s="62">
+      <c r="M17" s="108">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N17" s="62">
-        <v>15</v>
-      </c>
-      <c r="O17" s="62">
+      <c r="N17" s="108">
+        <v>12</v>
+      </c>
+      <c r="O17" s="108">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P17" s="62">
-        <v>30</v>
-      </c>
-      <c r="Q17" s="91" t="s">
+      <c r="P17" s="108">
+        <v>28</v>
+      </c>
+      <c r="Q17" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="R17" s="92">
+      <c r="R17" s="87">
         <v>0.37180000000000002</v>
       </c>
-      <c r="S17" s="93">
+      <c r="S17" s="111">
         <f t="shared" si="2"/>
-        <v>5.577</v>
-      </c>
-      <c r="T17" s="92">
+        <v>4.4616000000000007</v>
+      </c>
+      <c r="T17" s="87">
         <v>0.33910000000000001</v>
       </c>
-      <c r="U17" s="80">
+      <c r="U17" s="112">
         <f t="shared" si="3"/>
-        <v>10.173</v>
-      </c>
-      <c r="V17" s="62"/>
-      <c r="W17" s="63"/>
-    </row>
-    <row r="18" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>9.4947999999999997</v>
+      </c>
+      <c r="V17" s="108"/>
+      <c r="W17" s="58"/>
+      <c r="Y17" s="114"/>
+      <c r="Z17" s="114"/>
+      <c r="AA17" s="115"/>
+      <c r="AB17" s="115"/>
+      <c r="AC17" s="115"/>
+    </row>
+    <row r="18" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="B18" s="58">
+      <c r="B18" s="53">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="59" t="s">
+      <c r="C18" s="54" t="s">
         <v>168</v>
       </c>
-      <c r="D18" s="59" t="s">
+      <c r="D18" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="59" t="s">
+      <c r="E18" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="59" t="s">
+      <c r="F18" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="G18" s="59" t="s">
+      <c r="G18" s="54" t="s">
         <v>96</v>
       </c>
-      <c r="H18" s="59" t="s">
+      <c r="H18" s="54" t="s">
         <v>122</v>
       </c>
-      <c r="I18" s="83"/>
-      <c r="J18" s="83"/>
-      <c r="K18" s="59" t="s">
-        <v>205</v>
-      </c>
-      <c r="L18" s="59">
+      <c r="I18" s="78"/>
+      <c r="J18" s="78" t="s">
+        <v>203</v>
+      </c>
+      <c r="K18" s="54" t="s">
+        <v>195</v>
+      </c>
+      <c r="L18" s="54">
         <v>2</v>
       </c>
-      <c r="M18" s="59">
+      <c r="M18" s="54">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="N18" s="59">
+      <c r="N18" s="54">
         <v>40</v>
       </c>
-      <c r="O18" s="59">
+      <c r="O18" s="54">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="P18" s="59">
+      <c r="P18" s="54">
         <v>60</v>
       </c>
-      <c r="Q18" s="88" t="s">
+      <c r="Q18" s="83" t="s">
         <v>185</v>
       </c>
-      <c r="R18" s="89">
+      <c r="R18" s="84">
         <v>2.58E-2</v>
       </c>
-      <c r="S18" s="90">
+      <c r="S18" s="85">
         <f t="shared" si="2"/>
         <v>1.032</v>
       </c>
-      <c r="T18" s="89">
+      <c r="T18" s="84">
         <v>2.58E-2</v>
       </c>
-      <c r="U18" s="60">
+      <c r="U18" s="55">
         <f t="shared" si="3"/>
         <v>1.548</v>
       </c>
-      <c r="V18" s="59"/>
-      <c r="W18" s="76"/>
-    </row>
-    <row r="19" spans="1:23" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V18" s="54"/>
+      <c r="W18" s="71"/>
+      <c r="Y18" s="105"/>
+      <c r="Z18" s="105"/>
+      <c r="AA18" s="105"/>
+      <c r="AB18" s="106"/>
+      <c r="AC18" s="106"/>
+    </row>
+    <row r="19" spans="1:29" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-      <c r="B19" s="58">
+      <c r="B19" s="53">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="62" t="s">
+      <c r="C19" s="57" t="s">
         <v>168</v>
       </c>
-      <c r="D19" s="62" t="s">
+      <c r="D19" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="62" t="s">
+      <c r="E19" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="F19" s="62" t="s">
+      <c r="F19" s="57" t="s">
         <v>78</v>
       </c>
-      <c r="G19" s="62" t="s">
+      <c r="G19" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="H19" s="62" t="s">
+      <c r="H19" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="I19" s="84"/>
-      <c r="J19" s="84"/>
-      <c r="K19" s="62" t="s">
-        <v>205</v>
-      </c>
-      <c r="L19" s="62">
+      <c r="I19" s="79"/>
+      <c r="J19" s="79" t="s">
+        <v>204</v>
+      </c>
+      <c r="K19" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="L19" s="57">
         <v>1</v>
       </c>
-      <c r="M19" s="62">
+      <c r="M19" s="57">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N19" s="62">
+      <c r="N19" s="57">
         <v>20</v>
       </c>
-      <c r="O19" s="62">
+      <c r="O19" s="57">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P19" s="62">
+      <c r="P19" s="57">
         <v>40</v>
       </c>
-      <c r="Q19" s="91" t="s">
+      <c r="Q19" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="R19" s="92">
+      <c r="R19" s="87">
         <v>3.1300000000000001E-2</v>
       </c>
-      <c r="S19" s="93">
+      <c r="S19" s="88">
         <f t="shared" si="2"/>
         <v>0.626</v>
       </c>
-      <c r="T19" s="92">
+      <c r="T19" s="87">
         <v>3.1300000000000001E-2</v>
       </c>
-      <c r="U19" s="80">
+      <c r="U19" s="75">
         <f t="shared" si="3"/>
         <v>1.252</v>
       </c>
-      <c r="V19" s="62"/>
-      <c r="W19" s="63"/>
-    </row>
-    <row r="20" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V19" s="57"/>
+      <c r="W19" s="58"/>
+      <c r="Y19" s="105"/>
+      <c r="Z19" s="105"/>
+      <c r="AA19" s="105"/>
+      <c r="AB19" s="106"/>
+      <c r="AC19" s="106"/>
+    </row>
+    <row r="20" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="58">
+      <c r="B20" s="53">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="59" t="s">
+      <c r="C20" s="54" t="s">
         <v>169</v>
       </c>
-      <c r="D20" s="59" t="s">
+      <c r="D20" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="59" t="s">
+      <c r="E20" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="59" t="s">
+      <c r="F20" s="54" t="s">
         <v>166</v>
       </c>
-      <c r="G20" s="59" t="s">
+      <c r="G20" s="54" t="s">
         <v>98</v>
       </c>
-      <c r="H20" s="59" t="s">
+      <c r="H20" s="54" t="s">
         <v>124</v>
       </c>
-      <c r="I20" s="83"/>
-      <c r="J20" s="83"/>
-      <c r="K20" s="59" t="s">
-        <v>205</v>
-      </c>
-      <c r="L20" s="59">
+      <c r="I20" s="78" t="s">
+        <v>219</v>
+      </c>
+      <c r="J20" s="78" t="s">
+        <v>220</v>
+      </c>
+      <c r="K20" s="54" t="s">
+        <v>195</v>
+      </c>
+      <c r="L20" s="54">
         <v>1</v>
       </c>
-      <c r="M20" s="59">
+      <c r="M20" s="54">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N20" s="59">
-        <v>13</v>
-      </c>
-      <c r="O20" s="59">
+      <c r="N20" s="54">
+        <v>12</v>
+      </c>
+      <c r="O20" s="54">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P20" s="59">
+      <c r="P20" s="54">
         <v>28</v>
       </c>
-      <c r="Q20" s="88" t="s">
-        <v>190</v>
-      </c>
-      <c r="R20" s="94">
-        <v>1.0241</v>
-      </c>
-      <c r="S20" s="90">
+      <c r="Q20" s="83" t="s">
+        <v>185</v>
+      </c>
+      <c r="R20" s="89">
+        <v>0.32369999999999999</v>
+      </c>
+      <c r="S20" s="85">
         <f t="shared" si="2"/>
-        <v>13.3133</v>
-      </c>
-      <c r="T20" s="94">
-        <v>0.98099999999999998</v>
-      </c>
-      <c r="U20" s="60">
+        <v>3.8843999999999999</v>
+      </c>
+      <c r="T20" s="89">
+        <v>0.32369999999999999</v>
+      </c>
+      <c r="U20" s="55">
         <f t="shared" si="3"/>
-        <v>27.468</v>
-      </c>
-      <c r="V20" s="59"/>
-      <c r="W20" s="76"/>
-    </row>
-    <row r="21" spans="1:23" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>9.0635999999999992</v>
+      </c>
+      <c r="V20" s="54"/>
+      <c r="W20" s="116" t="s">
+        <v>221</v>
+      </c>
+      <c r="Y20" s="105"/>
+      <c r="Z20" s="105"/>
+      <c r="AA20" s="105"/>
+      <c r="AB20" s="106"/>
+      <c r="AC20" s="106"/>
+    </row>
+    <row r="21" spans="1:29" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="58">
+      <c r="B21" s="53">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="62" t="s">
+      <c r="C21" s="57" t="s">
         <v>169</v>
       </c>
-      <c r="D21" s="62" t="s">
+      <c r="D21" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="62" t="s">
+      <c r="E21" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="62" t="s">
+      <c r="F21" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="G21" s="62" t="s">
+      <c r="G21" s="57" t="s">
         <v>99</v>
       </c>
-      <c r="H21" s="62" t="s">
+      <c r="H21" s="57" t="s">
         <v>125</v>
       </c>
-      <c r="I21" s="84"/>
-      <c r="J21" s="84"/>
-      <c r="K21" s="62" t="s">
+      <c r="I21" s="79"/>
+      <c r="J21" s="79" t="s">
         <v>205</v>
       </c>
-      <c r="L21" s="62">
+      <c r="K21" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="L21" s="57">
         <v>1</v>
       </c>
-      <c r="M21" s="62">
+      <c r="M21" s="57">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N21" s="62">
+      <c r="N21" s="57">
         <v>15</v>
       </c>
-      <c r="O21" s="62">
+      <c r="O21" s="57">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P21" s="62">
+      <c r="P21" s="57">
         <v>30</v>
       </c>
-      <c r="Q21" s="91" t="s">
+      <c r="Q21" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="R21" s="92">
+      <c r="R21" s="87">
         <v>0.1186</v>
       </c>
-      <c r="S21" s="93">
+      <c r="S21" s="88">
         <f t="shared" si="2"/>
         <v>1.7789999999999999</v>
       </c>
-      <c r="T21" s="92">
+      <c r="T21" s="87">
         <v>0.1186</v>
       </c>
-      <c r="U21" s="80">
+      <c r="U21" s="75">
         <f t="shared" si="3"/>
         <v>3.5579999999999998</v>
       </c>
-      <c r="V21" s="62"/>
-      <c r="W21" s="63"/>
-    </row>
-    <row r="22" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V21" s="57"/>
+      <c r="W21" s="58"/>
+      <c r="Y21" s="105"/>
+      <c r="Z21" s="105"/>
+      <c r="AA21" s="105"/>
+      <c r="AB21" s="106"/>
+      <c r="AC21" s="106"/>
+    </row>
+    <row r="22" spans="1:29" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="B22" s="58">
+      <c r="B22" s="53">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="59" t="s">
+      <c r="C22" s="54" t="s">
         <v>169</v>
       </c>
-      <c r="D22" s="59" t="s">
+      <c r="D22" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="E22" s="59" t="s">
+      <c r="E22" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="F22" s="59" t="s">
+      <c r="F22" s="54" t="s">
         <v>166</v>
       </c>
-      <c r="G22" s="64" t="s">
+      <c r="G22" s="59" t="s">
         <v>100</v>
       </c>
-      <c r="H22" s="59" t="s">
+      <c r="H22" s="54" t="s">
         <v>126</v>
       </c>
-      <c r="I22" s="95" t="s">
+      <c r="I22" s="118" t="s">
+        <v>189</v>
+      </c>
+      <c r="J22" s="119" t="s">
+        <v>190</v>
+      </c>
+      <c r="K22" s="54" t="s">
         <v>195</v>
       </c>
-      <c r="J22" s="96" t="s">
-        <v>196</v>
-      </c>
-      <c r="K22" s="59" t="s">
-        <v>205</v>
-      </c>
-      <c r="L22" s="59">
+      <c r="L22" s="54">
         <v>1</v>
       </c>
-      <c r="M22" s="59">
+      <c r="M22" s="54">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N22" s="59">
-        <v>13</v>
-      </c>
-      <c r="O22" s="59">
+      <c r="N22" s="54">
+        <v>12</v>
+      </c>
+      <c r="O22" s="54">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P22" s="59">
+      <c r="P22" s="54">
         <v>28</v>
       </c>
-      <c r="Q22" s="88" t="s">
+      <c r="Q22" s="83" t="s">
         <v>185</v>
       </c>
-      <c r="R22" s="94">
+      <c r="R22" s="89">
         <v>0.2868</v>
       </c>
-      <c r="S22" s="90">
+      <c r="S22" s="85">
         <f t="shared" si="2"/>
-        <v>3.7284000000000002</v>
-      </c>
-      <c r="T22" s="94">
+        <v>3.4416000000000002</v>
+      </c>
+      <c r="T22" s="89">
         <v>0.2868</v>
       </c>
-      <c r="U22" s="60">
+      <c r="U22" s="55">
         <f t="shared" si="3"/>
         <v>8.0304000000000002</v>
       </c>
-      <c r="V22" s="59"/>
-      <c r="W22" s="76"/>
-    </row>
-    <row r="23" spans="1:23" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V22" s="54"/>
+      <c r="W22" s="117" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y22" s="105"/>
+      <c r="Z22" s="105"/>
+      <c r="AA22" s="105"/>
+      <c r="AB22" s="106"/>
+      <c r="AC22" s="106"/>
+    </row>
+    <row r="23" spans="1:29" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
-      <c r="B23" s="58">
+      <c r="B23" s="53">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="62" t="s">
+      <c r="C23" s="57" t="s">
         <v>170</v>
       </c>
-      <c r="D23" s="62" t="s">
+      <c r="D23" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="62" t="s">
+      <c r="E23" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="F23" s="62" t="s">
+      <c r="F23" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="G23" s="62" t="s">
+      <c r="G23" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="H23" s="62" t="s">
+      <c r="H23" s="57" t="s">
         <v>127</v>
       </c>
-      <c r="I23" s="63"/>
-      <c r="J23" s="84"/>
-      <c r="K23" s="62" t="s">
+      <c r="I23" s="58"/>
+      <c r="J23" s="57" t="s">
+        <v>206</v>
+      </c>
+      <c r="K23" s="57" t="s">
         <v>149</v>
       </c>
-      <c r="L23" s="62">
+      <c r="L23" s="57">
         <v>1</v>
       </c>
-      <c r="M23" s="62">
+      <c r="M23" s="57">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N23" s="62">
-        <v>15</v>
-      </c>
-      <c r="O23" s="62">
+      <c r="N23" s="57">
+        <v>12</v>
+      </c>
+      <c r="O23" s="57">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P23" s="62">
-        <v>30</v>
-      </c>
-      <c r="Q23" s="91" t="s">
+      <c r="P23" s="57">
+        <v>28</v>
+      </c>
+      <c r="Q23" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="R23" s="92">
+      <c r="R23" s="87">
         <v>0.37009999999999998</v>
       </c>
-      <c r="S23" s="93">
+      <c r="S23" s="88">
         <f t="shared" si="2"/>
-        <v>5.5514999999999999</v>
-      </c>
-      <c r="T23" s="92">
+        <v>4.4412000000000003</v>
+      </c>
+      <c r="T23" s="87">
         <v>0.33050000000000002</v>
       </c>
-      <c r="U23" s="80">
+      <c r="U23" s="75">
         <f t="shared" si="3"/>
-        <v>9.9150000000000009</v>
-      </c>
-      <c r="V23" s="62"/>
-      <c r="W23" s="63"/>
-    </row>
-    <row r="24" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>9.2540000000000013</v>
+      </c>
+      <c r="V23" s="57"/>
+      <c r="W23" s="58"/>
+      <c r="Y23" s="105"/>
+      <c r="Z23" s="105"/>
+      <c r="AA23" s="105"/>
+      <c r="AB23" s="106"/>
+      <c r="AC23" s="106"/>
+    </row>
+    <row r="24" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
-      <c r="B24" s="58">
+      <c r="B24" s="53">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="54" t="s">
         <v>171</v>
       </c>
-      <c r="D24" s="59" t="s">
+      <c r="D24" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="59" t="s">
+      <c r="E24" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="F24" s="59" t="s">
+      <c r="F24" s="54" t="s">
         <v>166</v>
       </c>
-      <c r="G24" s="59">
+      <c r="G24" s="54">
         <v>61300311121</v>
       </c>
-      <c r="H24" s="59" t="s">
+      <c r="H24" s="54" t="s">
         <v>128</v>
       </c>
-      <c r="I24" s="83"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="59" t="s">
-        <v>205</v>
-      </c>
-      <c r="L24" s="59">
+      <c r="I24" s="78" t="s">
+        <v>223</v>
+      </c>
+      <c r="J24" s="78" t="s">
+        <v>224</v>
+      </c>
+      <c r="K24" s="54" t="s">
+        <v>195</v>
+      </c>
+      <c r="L24" s="54">
         <v>1</v>
       </c>
-      <c r="M24" s="59">
+      <c r="M24" s="54">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N24" s="59">
-        <v>13</v>
-      </c>
-      <c r="O24" s="59">
+      <c r="N24" s="54">
+        <v>50</v>
+      </c>
+      <c r="O24" s="54">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P24" s="59">
-        <v>28</v>
-      </c>
-      <c r="Q24" s="88" t="s">
-        <v>191</v>
-      </c>
-      <c r="R24" s="97">
-        <v>9.8519999999999996E-2</v>
-      </c>
-      <c r="S24" s="90">
+      <c r="P24" s="54">
+        <v>50</v>
+      </c>
+      <c r="Q24" s="83" t="s">
+        <v>185</v>
+      </c>
+      <c r="R24" s="90">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="S24" s="85">
         <f t="shared" si="2"/>
-        <v>1.2807599999999999</v>
-      </c>
-      <c r="T24" s="97">
-        <v>9.8519999999999996E-2</v>
-      </c>
-      <c r="U24" s="60">
+        <v>0.755</v>
+      </c>
+      <c r="T24" s="90">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="U24" s="55">
         <f t="shared" si="3"/>
-        <v>2.7585600000000001</v>
-      </c>
-      <c r="V24" s="59"/>
-      <c r="W24" s="76"/>
-    </row>
-    <row r="25" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.755</v>
+      </c>
+      <c r="V24" s="54"/>
+      <c r="W24" s="71"/>
+      <c r="Y24" s="105"/>
+      <c r="Z24" s="105"/>
+      <c r="AA24" s="105"/>
+      <c r="AB24" s="106"/>
+      <c r="AC24" s="106"/>
+    </row>
+    <row r="25" spans="1:29" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="B25" s="58">
+      <c r="B25" s="53">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="62" t="s">
+      <c r="C25" s="57" t="s">
         <v>172</v>
       </c>
-      <c r="D25" s="62" t="s">
+      <c r="D25" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="62" t="s">
+      <c r="E25" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="F25" s="62" t="s">
+      <c r="F25" s="57" t="s">
         <v>80</v>
       </c>
-      <c r="G25" s="65" t="s">
+      <c r="G25" s="60" t="s">
         <v>101</v>
       </c>
-      <c r="H25" s="62" t="s">
+      <c r="H25" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="I25" s="98" t="s">
-        <v>192</v>
-      </c>
-      <c r="J25" s="99" t="s">
-        <v>193</v>
-      </c>
-      <c r="K25" s="62" t="s">
-        <v>205</v>
-      </c>
-      <c r="L25" s="62">
+      <c r="I25" s="125" t="s">
+        <v>187</v>
+      </c>
+      <c r="J25" s="126" t="s">
+        <v>225</v>
+      </c>
+      <c r="K25" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="L25" s="57">
         <v>6</v>
       </c>
-      <c r="M25" s="62">
+      <c r="M25" s="57">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="N25" s="62">
+      <c r="N25" s="57">
         <v>80</v>
       </c>
-      <c r="O25" s="62">
+      <c r="O25" s="57">
         <f t="shared" si="1"/>
         <v>150</v>
       </c>
-      <c r="P25" s="62">
+      <c r="P25" s="57">
         <v>160</v>
       </c>
-      <c r="Q25" s="91" t="s">
+      <c r="Q25" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="R25" s="92">
+      <c r="R25" s="87">
         <v>2.3800000000000002E-2</v>
       </c>
-      <c r="S25" s="93">
+      <c r="S25" s="88">
         <f t="shared" si="2"/>
         <v>1.9040000000000001</v>
       </c>
-      <c r="T25" s="92">
+      <c r="T25" s="87">
         <v>2.3800000000000002E-2</v>
       </c>
-      <c r="U25" s="80">
+      <c r="U25" s="75">
         <f t="shared" si="3"/>
         <v>3.8080000000000003</v>
       </c>
-      <c r="V25" s="62" t="s">
-        <v>201</v>
-      </c>
-      <c r="W25" s="63"/>
-    </row>
-    <row r="26" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V25" s="57" t="s">
+        <v>222</v>
+      </c>
+      <c r="W25" s="58"/>
+      <c r="Y25" s="105"/>
+      <c r="Z25" s="105"/>
+      <c r="AA25" s="105"/>
+      <c r="AB25" s="106"/>
+      <c r="AC25" s="106"/>
+    </row>
+    <row r="26" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
-      <c r="B26" s="58">
+      <c r="B26" s="53">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="59" t="s">
+      <c r="C26" s="54" t="s">
         <v>173</v>
       </c>
-      <c r="D26" s="59" t="s">
+      <c r="D26" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="E26" s="59" t="s">
+      <c r="E26" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="F26" s="59" t="s">
+      <c r="F26" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="G26" s="64" t="s">
+      <c r="G26" s="59" t="s">
         <v>102</v>
       </c>
-      <c r="H26" s="59" t="s">
+      <c r="H26" s="54" t="s">
         <v>130</v>
       </c>
-      <c r="I26" s="100" t="s">
-        <v>186</v>
-      </c>
-      <c r="J26" s="100" t="s">
-        <v>187</v>
-      </c>
-      <c r="K26" s="59" t="s">
+      <c r="I26" s="92" t="s">
+        <v>226</v>
+      </c>
+      <c r="J26" s="92" t="s">
+        <v>227</v>
+      </c>
+      <c r="K26" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="L26" s="59">
+      <c r="L26" s="54">
         <v>2</v>
       </c>
-      <c r="M26" s="59">
+      <c r="M26" s="54">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="N26" s="59">
-        <v>50</v>
-      </c>
-      <c r="O26" s="59">
+      <c r="N26" s="54">
+        <v>30</v>
+      </c>
+      <c r="O26" s="54">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="P26" s="59">
-        <v>100</v>
-      </c>
-      <c r="Q26" s="88" t="s">
+      <c r="P26" s="54">
+        <v>60</v>
+      </c>
+      <c r="Q26" s="83" t="s">
         <v>185</v>
       </c>
-      <c r="R26" s="89">
-        <v>1.26E-2</v>
-      </c>
-      <c r="S26" s="90">
+      <c r="R26" s="84">
+        <v>7.4499999999999997E-2</v>
+      </c>
+      <c r="S26" s="85">
         <f t="shared" si="2"/>
-        <v>0.63</v>
-      </c>
-      <c r="T26" s="89">
-        <v>1.26E-2</v>
-      </c>
-      <c r="U26" s="60">
+        <v>2.2349999999999999</v>
+      </c>
+      <c r="T26" s="84">
+        <v>7.4499999999999997E-2</v>
+      </c>
+      <c r="U26" s="55">
         <f t="shared" si="3"/>
-        <v>1.26</v>
-      </c>
-      <c r="V26" s="66" t="s">
-        <v>202</v>
-      </c>
-      <c r="W26" s="76"/>
-    </row>
-    <row r="27" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>4.47</v>
+      </c>
+      <c r="V26" s="61"/>
+      <c r="W26" s="71"/>
+      <c r="Y26" s="105"/>
+      <c r="Z26" s="105"/>
+      <c r="AA26" s="105"/>
+      <c r="AB26" s="106"/>
+      <c r="AC26" s="106"/>
+    </row>
+    <row r="27" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
-      <c r="B27" s="58">
+      <c r="B27" s="53">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="62" t="s">
+      <c r="C27" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="D27" s="62" t="s">
+      <c r="D27" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="E27" s="62" t="s">
+      <c r="E27" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="F27" s="62" t="s">
+      <c r="F27" s="57" t="s">
         <v>82</v>
       </c>
-      <c r="G27" s="65" t="s">
+      <c r="G27" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="H27" s="62" t="s">
+      <c r="H27" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="I27" s="98" t="s">
-        <v>188</v>
-      </c>
-      <c r="J27" s="99" t="s">
-        <v>189</v>
-      </c>
-      <c r="K27" s="62" t="s">
+      <c r="I27" s="125" t="s">
+        <v>186</v>
+      </c>
+      <c r="J27" s="91" t="s">
+        <v>228</v>
+      </c>
+      <c r="K27" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="L27" s="62">
+      <c r="L27" s="57">
         <v>1</v>
       </c>
-      <c r="M27" s="62">
+      <c r="M27" s="57">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N27" s="62">
+      <c r="N27" s="57">
         <v>50</v>
       </c>
-      <c r="O27" s="62">
+      <c r="O27" s="57">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P27" s="62">
+      <c r="P27" s="57">
         <v>50</v>
       </c>
-      <c r="Q27" s="91" t="s">
+      <c r="Q27" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="R27" s="92">
+      <c r="R27" s="87">
         <v>1.46E-2</v>
       </c>
-      <c r="S27" s="93">
+      <c r="S27" s="88">
         <f t="shared" si="2"/>
         <v>0.73</v>
       </c>
-      <c r="T27" s="92">
+      <c r="T27" s="87">
         <v>1.46E-2</v>
       </c>
-      <c r="U27" s="80">
+      <c r="U27" s="75">
         <f t="shared" si="3"/>
         <v>0.73</v>
       </c>
-      <c r="V27" s="62"/>
-      <c r="W27" s="63"/>
-    </row>
-    <row r="28" spans="1:23" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V27" s="57"/>
+      <c r="W27" s="58"/>
+      <c r="Y27" s="105"/>
+      <c r="Z27" s="105"/>
+      <c r="AA27" s="105"/>
+      <c r="AB27" s="106"/>
+      <c r="AC27" s="106"/>
+    </row>
+    <row r="28" spans="1:29" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
-      <c r="B28" s="58">
+      <c r="B28" s="53">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="59" t="s">
+      <c r="C28" s="54" t="s">
         <v>173</v>
       </c>
-      <c r="D28" s="59" t="s">
+      <c r="D28" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="E28" s="59" t="s">
+      <c r="E28" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="F28" s="59" t="s">
+      <c r="F28" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="G28" s="59" t="s">
+      <c r="G28" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="H28" s="59" t="s">
+      <c r="H28" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="I28" s="101"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="59" t="s">
+      <c r="I28" s="93"/>
+      <c r="J28" s="54" t="s">
+        <v>207</v>
+      </c>
+      <c r="K28" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="L28" s="59">
+      <c r="L28" s="54">
         <v>11</v>
       </c>
-      <c r="M28" s="59">
+      <c r="M28" s="54">
         <f t="shared" si="4"/>
         <v>110</v>
       </c>
-      <c r="N28" s="59">
-        <v>100</v>
-      </c>
-      <c r="O28" s="59">
+      <c r="N28" s="54">
+        <v>200</v>
+      </c>
+      <c r="O28" s="54">
         <f t="shared" si="1"/>
         <v>275</v>
       </c>
-      <c r="P28" s="59">
-        <v>100</v>
-      </c>
-      <c r="Q28" s="88" t="s">
+      <c r="P28" s="54">
+        <v>300</v>
+      </c>
+      <c r="Q28" s="83" t="s">
         <v>185</v>
       </c>
-      <c r="R28" s="89">
+      <c r="R28" s="84">
         <v>1.4E-3</v>
       </c>
-      <c r="S28" s="90">
+      <c r="S28" s="85">
         <f t="shared" si="2"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="T28" s="89">
+        <v>0.27999999999999997</v>
+      </c>
+      <c r="T28" s="84">
         <v>1.4E-3</v>
       </c>
-      <c r="U28" s="60">
+      <c r="U28" s="55">
         <f t="shared" si="3"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="V28" s="59"/>
-      <c r="W28" s="76"/>
-    </row>
-    <row r="29" spans="1:23" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.42</v>
+      </c>
+      <c r="V28" s="54"/>
+      <c r="W28" s="71"/>
+      <c r="Y28" s="105"/>
+      <c r="Z28" s="105"/>
+      <c r="AA28" s="105"/>
+      <c r="AB28" s="106"/>
+      <c r="AC28" s="106"/>
+    </row>
+    <row r="29" spans="1:29" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
-      <c r="B29" s="58">
+      <c r="B29" s="53">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="62" t="s">
+      <c r="C29" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="D29" s="62" t="s">
+      <c r="D29" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="E29" s="62" t="s">
+      <c r="E29" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="F29" s="62" t="s">
+      <c r="F29" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="G29" s="62" t="s">
+      <c r="G29" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="H29" s="62" t="s">
+      <c r="H29" s="57" t="s">
         <v>117</v>
       </c>
-      <c r="I29" s="84"/>
-      <c r="J29" s="84"/>
-      <c r="K29" s="62" t="s">
+      <c r="I29" s="79"/>
+      <c r="J29" s="57" t="s">
+        <v>208</v>
+      </c>
+      <c r="K29" s="57" t="s">
         <v>153</v>
       </c>
-      <c r="L29" s="62">
+      <c r="L29" s="57">
         <v>13</v>
       </c>
-      <c r="M29" s="62">
+      <c r="M29" s="57">
         <f t="shared" si="4"/>
         <v>130</v>
       </c>
-      <c r="N29" s="62">
+      <c r="N29" s="57">
         <v>200</v>
       </c>
-      <c r="O29" s="62">
+      <c r="O29" s="57">
         <f t="shared" si="1"/>
         <v>325</v>
       </c>
-      <c r="P29" s="62">
+      <c r="P29" s="57">
         <v>400</v>
       </c>
-      <c r="Q29" s="91" t="s">
+      <c r="Q29" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="R29" s="92">
+      <c r="R29" s="87">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="S29" s="93">
+      <c r="S29" s="88">
         <f t="shared" si="2"/>
         <v>0.22</v>
       </c>
-      <c r="T29" s="92">
+      <c r="T29" s="87">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="U29" s="80">
+      <c r="U29" s="75">
         <f t="shared" si="3"/>
         <v>0.44</v>
       </c>
-      <c r="V29" s="62"/>
-      <c r="W29" s="63"/>
-    </row>
-    <row r="30" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V29" s="57"/>
+      <c r="W29" s="58"/>
+      <c r="Y29" s="105"/>
+      <c r="Z29" s="105"/>
+      <c r="AA29" s="105"/>
+      <c r="AB29" s="106"/>
+      <c r="AC29" s="106"/>
+    </row>
+    <row r="30" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
-      <c r="B30" s="58">
+      <c r="B30" s="53">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="59" t="s">
+      <c r="C30" s="54" t="s">
         <v>173</v>
       </c>
-      <c r="D30" s="59" t="s">
+      <c r="D30" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="G30" s="59" t="s">
+      <c r="G30" s="54" t="s">
         <v>106</v>
       </c>
-      <c r="H30" s="59" t="s">
+      <c r="H30" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="I30" s="83"/>
-      <c r="J30" s="83"/>
-      <c r="K30" s="59" t="s">
+      <c r="I30" s="78"/>
+      <c r="J30" s="78" t="s">
+        <v>209</v>
+      </c>
+      <c r="K30" s="54" t="s">
         <v>154</v>
       </c>
-      <c r="L30" s="59">
+      <c r="L30" s="54">
         <v>1</v>
       </c>
-      <c r="M30" s="59">
+      <c r="M30" s="54">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N30" s="59">
+      <c r="N30" s="54">
         <v>100</v>
       </c>
-      <c r="O30" s="59">
+      <c r="O30" s="54">
         <f>L30*25</f>
         <v>25</v>
       </c>
-      <c r="P30" s="59">
+      <c r="P30" s="54">
         <v>100</v>
       </c>
-      <c r="Q30" s="88" t="s">
+      <c r="Q30" s="83" t="s">
         <v>185</v>
       </c>
-      <c r="R30" s="89">
+      <c r="R30" s="84">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="S30" s="90">
+      <c r="S30" s="85">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="T30" s="89">
+      <c r="T30" s="84">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="U30" s="60">
+      <c r="U30" s="55">
         <f t="shared" si="3"/>
         <v>0.13</v>
       </c>
-      <c r="V30" s="59"/>
-      <c r="W30" s="76"/>
-    </row>
-    <row r="31" spans="1:23" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V30" s="54"/>
+      <c r="W30" s="71"/>
+      <c r="Y30" s="105"/>
+      <c r="Z30" s="105"/>
+      <c r="AA30" s="105"/>
+      <c r="AB30" s="106"/>
+      <c r="AC30" s="106"/>
+    </row>
+    <row r="31" spans="1:29" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
-      <c r="B31" s="58">
+      <c r="B31" s="53">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="62" t="s">
+      <c r="C31" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="D31" s="62" t="s">
+      <c r="D31" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="E31" s="62" t="s">
+      <c r="E31" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="F31" s="62" t="s">
+      <c r="F31" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="G31" s="62" t="s">
+      <c r="G31" s="57" t="s">
         <v>107</v>
       </c>
-      <c r="H31" s="62" t="s">
+      <c r="H31" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="I31" s="84"/>
-      <c r="J31" s="84"/>
-      <c r="K31" s="62" t="s">
+      <c r="I31" s="79"/>
+      <c r="J31" s="57" t="s">
+        <v>210</v>
+      </c>
+      <c r="K31" s="57" t="s">
         <v>155</v>
       </c>
-      <c r="L31" s="62">
+      <c r="L31" s="57">
         <v>1</v>
       </c>
-      <c r="M31" s="62">
+      <c r="M31" s="57">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N31" s="62">
+      <c r="N31" s="57">
         <v>50</v>
       </c>
-      <c r="O31" s="62">
+      <c r="O31" s="57">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P31" s="62">
+      <c r="P31" s="57">
         <v>50</v>
       </c>
-      <c r="Q31" s="91" t="s">
+      <c r="Q31" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="R31" s="92">
+      <c r="R31" s="87">
         <v>4.1000000000000003E-3</v>
       </c>
-      <c r="S31" s="93">
+      <c r="S31" s="88">
         <f t="shared" si="2"/>
         <v>0.20500000000000002</v>
       </c>
-      <c r="T31" s="92">
+      <c r="T31" s="87">
         <v>4.1000000000000003E-3</v>
       </c>
-      <c r="U31" s="80">
+      <c r="U31" s="75">
         <f t="shared" si="3"/>
         <v>0.20500000000000002</v>
       </c>
-      <c r="V31" s="62"/>
-      <c r="W31" s="63"/>
-    </row>
-    <row r="32" spans="1:23" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V31" s="57"/>
+      <c r="W31" s="58"/>
+      <c r="Y31" s="105"/>
+      <c r="Z31" s="105"/>
+      <c r="AA31" s="105"/>
+      <c r="AB31" s="106"/>
+      <c r="AC31" s="106"/>
+    </row>
+    <row r="32" spans="1:29" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
-      <c r="B32" s="58">
+      <c r="B32" s="53">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="59" t="s">
+      <c r="C32" s="54" t="s">
         <v>173</v>
       </c>
-      <c r="D32" s="59" t="s">
+      <c r="D32" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="E32" s="59" t="s">
+      <c r="E32" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="F32" s="59" t="s">
+      <c r="F32" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="G32" s="59" t="s">
+      <c r="G32" s="54" t="s">
         <v>108</v>
       </c>
-      <c r="H32" s="59" t="s">
+      <c r="H32" s="54" t="s">
         <v>133</v>
       </c>
-      <c r="I32" s="83"/>
-      <c r="J32" s="83"/>
-      <c r="K32" s="59" t="s">
+      <c r="I32" s="78"/>
+      <c r="J32" s="54" t="s">
+        <v>211</v>
+      </c>
+      <c r="K32" s="54" t="s">
         <v>156</v>
       </c>
-      <c r="L32" s="59">
+      <c r="L32" s="54">
         <v>1</v>
       </c>
-      <c r="M32" s="59">
+      <c r="M32" s="54">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N32" s="59">
+      <c r="N32" s="54">
         <v>15</v>
       </c>
-      <c r="O32" s="59">
+      <c r="O32" s="54">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P32" s="59">
+      <c r="P32" s="54">
         <v>30</v>
       </c>
-      <c r="Q32" s="88" t="s">
+      <c r="Q32" s="83" t="s">
         <v>185</v>
       </c>
-      <c r="R32" s="89">
+      <c r="R32" s="84">
         <v>0.14979999999999999</v>
       </c>
-      <c r="S32" s="90">
+      <c r="S32" s="85">
         <f t="shared" si="2"/>
         <v>2.2469999999999999</v>
       </c>
-      <c r="T32" s="89">
+      <c r="T32" s="84">
         <v>0.1348</v>
       </c>
-      <c r="U32" s="60">
+      <c r="U32" s="55">
         <f t="shared" si="3"/>
         <v>4.0440000000000005</v>
       </c>
-      <c r="V32" s="59"/>
-      <c r="W32" s="76"/>
-    </row>
-    <row r="33" spans="1:23" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V32" s="54"/>
+      <c r="W32" s="71"/>
+      <c r="Y32" s="105"/>
+      <c r="Z32" s="105"/>
+      <c r="AA32" s="105"/>
+      <c r="AB32" s="106"/>
+      <c r="AC32" s="106"/>
+    </row>
+    <row r="33" spans="1:32" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
-      <c r="B33" s="58">
+      <c r="B33" s="53">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="62" t="s">
+      <c r="C33" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="D33" s="62" t="s">
+      <c r="D33" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="E33" s="62" t="s">
+      <c r="E33" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="F33" s="62" t="s">
+      <c r="F33" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="G33" s="62" t="s">
+      <c r="G33" s="57" t="s">
         <v>109</v>
       </c>
-      <c r="H33" s="62" t="s">
+      <c r="H33" s="57" t="s">
         <v>134</v>
       </c>
-      <c r="I33" s="84"/>
-      <c r="J33" s="84"/>
-      <c r="K33" s="62" t="s">
+      <c r="I33" s="79"/>
+      <c r="J33" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K33" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="L33" s="62">
+      <c r="L33" s="57">
         <v>1</v>
       </c>
-      <c r="M33" s="62">
+      <c r="M33" s="57">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N33" s="62">
+      <c r="N33" s="57">
         <v>100</v>
       </c>
-      <c r="O33" s="62">
+      <c r="O33" s="57">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P33" s="62">
+      <c r="P33" s="57">
         <v>100</v>
       </c>
-      <c r="Q33" s="91" t="s">
+      <c r="Q33" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="R33" s="92">
+      <c r="R33" s="87">
         <v>1E-3</v>
       </c>
-      <c r="S33" s="93">
+      <c r="S33" s="88">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="T33" s="92">
+      <c r="T33" s="87">
         <v>1E-3</v>
       </c>
-      <c r="U33" s="80">
+      <c r="U33" s="75">
         <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
-      <c r="V33" s="62"/>
-      <c r="W33" s="63"/>
-    </row>
-    <row r="34" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V33" s="57"/>
+      <c r="W33" s="58"/>
+      <c r="X33" s="105"/>
+      <c r="Y33" s="105"/>
+      <c r="Z33" s="105"/>
+      <c r="AA33" s="105"/>
+      <c r="AB33" s="105"/>
+      <c r="AC33" s="105"/>
+      <c r="AD33" s="105"/>
+      <c r="AE33" s="105"/>
+      <c r="AF33" s="106"/>
+    </row>
+    <row r="34" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
-      <c r="B34" s="58">
+      <c r="B34" s="53">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="64" t="s">
-        <v>194</v>
-      </c>
-      <c r="D34" s="64" t="s">
+      <c r="C34" s="59" t="s">
+        <v>188</v>
+      </c>
+      <c r="D34" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="E34" s="64" t="s">
+      <c r="E34" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="F34" s="64" t="s">
+      <c r="F34" s="59" t="s">
         <v>166</v>
       </c>
-      <c r="G34" s="64"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="85"/>
-      <c r="J34" s="85"/>
-      <c r="K34" s="64" t="s">
+      <c r="G34" s="59"/>
+      <c r="H34" s="59"/>
+      <c r="I34" s="80"/>
+      <c r="J34" s="80" t="s">
+        <v>195</v>
+      </c>
+      <c r="K34" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="L34" s="64">
+      <c r="L34" s="59">
         <v>1</v>
       </c>
-      <c r="M34" s="64">
+      <c r="M34" s="59">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N34" s="64"/>
-      <c r="O34" s="64">
+      <c r="N34" s="59"/>
+      <c r="O34" s="59">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P34" s="64"/>
-      <c r="Q34" s="64"/>
-      <c r="R34" s="102"/>
-      <c r="S34" s="103">
+      <c r="P34" s="59"/>
+      <c r="Q34" s="59"/>
+      <c r="R34" s="94"/>
+      <c r="S34" s="95">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T34" s="102"/>
-      <c r="U34" s="67">
+      <c r="T34" s="94"/>
+      <c r="U34" s="62">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V34" s="64" t="s">
-        <v>199</v>
-      </c>
-      <c r="W34" s="77"/>
-    </row>
-    <row r="35" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V34" s="59" t="s">
+        <v>192</v>
+      </c>
+      <c r="W34" s="72"/>
+      <c r="X34" s="105"/>
+      <c r="Y34" s="105"/>
+      <c r="Z34" s="105"/>
+      <c r="AA34" s="105"/>
+      <c r="AB34" s="105"/>
+      <c r="AC34" s="105"/>
+      <c r="AD34" s="105"/>
+      <c r="AE34" s="105"/>
+      <c r="AF34" s="106"/>
+    </row>
+    <row r="35" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
-      <c r="B35" s="58">
+      <c r="B35" s="53">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="62" t="s">
+      <c r="C35" s="57" t="s">
         <v>176</v>
       </c>
-      <c r="D35" s="62" t="s">
+      <c r="D35" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="E35" s="62" t="s">
+      <c r="E35" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="F35" s="62" t="s">
+      <c r="F35" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="G35" s="62" t="s">
+      <c r="G35" s="57" t="s">
         <v>110</v>
       </c>
-      <c r="H35" s="62" t="s">
+      <c r="H35" s="57" t="s">
         <v>135</v>
       </c>
-      <c r="I35" s="84"/>
-      <c r="J35" s="84"/>
-      <c r="K35" s="62" t="s">
-        <v>205</v>
-      </c>
-      <c r="L35" s="62">
+      <c r="I35" s="79"/>
+      <c r="J35" s="79" t="s">
+        <v>213</v>
+      </c>
+      <c r="K35" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="L35" s="57">
         <v>1</v>
       </c>
-      <c r="M35" s="62">
+      <c r="M35" s="57">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N35" s="62">
-        <v>20</v>
-      </c>
-      <c r="O35" s="62">
+      <c r="N35" s="57">
+        <v>15</v>
+      </c>
+      <c r="O35" s="57">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P35" s="62">
+      <c r="P35" s="57">
         <v>30</v>
       </c>
-      <c r="Q35" s="91" t="s">
+      <c r="Q35" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="R35" s="92">
-        <v>0.18</v>
-      </c>
-      <c r="S35" s="93">
+      <c r="R35" s="87">
+        <v>0.47339999999999999</v>
+      </c>
+      <c r="S35" s="88">
         <f t="shared" si="2"/>
-        <v>3.5999999999999996</v>
-      </c>
-      <c r="T35" s="92">
-        <v>0.18</v>
-      </c>
-      <c r="U35" s="80">
+        <v>7.101</v>
+      </c>
+      <c r="T35" s="87">
+        <v>0.42870000000000003</v>
+      </c>
+      <c r="U35" s="75">
         <f t="shared" si="3"/>
-        <v>5.3999999999999995</v>
-      </c>
-      <c r="V35" s="62"/>
-      <c r="W35" s="63"/>
-    </row>
-    <row r="36" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>12.861000000000001</v>
+      </c>
+      <c r="V35" s="57"/>
+      <c r="W35" s="58"/>
+      <c r="X35" s="105"/>
+      <c r="Y35" s="105"/>
+      <c r="Z35" s="105"/>
+      <c r="AA35" s="105"/>
+      <c r="AB35" s="105"/>
+      <c r="AC35" s="105"/>
+      <c r="AD35" s="105"/>
+      <c r="AE35" s="105"/>
+      <c r="AF35" s="106"/>
+    </row>
+    <row r="36" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
-      <c r="B36" s="58">
+      <c r="B36" s="53">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="59" t="s">
+      <c r="C36" s="54" t="s">
         <v>175</v>
       </c>
-      <c r="D36" s="59" t="s">
+      <c r="D36" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="E36" s="59" t="s">
+      <c r="E36" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="F36" s="59" t="s">
+      <c r="F36" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="G36" s="59" t="s">
+      <c r="G36" s="54" t="s">
         <v>111</v>
       </c>
-      <c r="H36" s="59" t="s">
+      <c r="H36" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="I36" s="83"/>
-      <c r="J36" s="83"/>
-      <c r="K36" s="59" t="s">
-        <v>205</v>
-      </c>
-      <c r="L36" s="59">
+      <c r="I36" s="78"/>
+      <c r="J36" s="78" t="s">
+        <v>214</v>
+      </c>
+      <c r="K36" s="54" t="s">
+        <v>195</v>
+      </c>
+      <c r="L36" s="54">
         <v>1</v>
       </c>
-      <c r="M36" s="59">
+      <c r="M36" s="54">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N36" s="59">
-        <v>13</v>
-      </c>
-      <c r="O36" s="59">
+      <c r="N36" s="54">
+        <v>12</v>
+      </c>
+      <c r="O36" s="54">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P36" s="59">
-        <v>28</v>
-      </c>
-      <c r="Q36" s="88" t="s">
+      <c r="P36" s="54">
+        <v>27</v>
+      </c>
+      <c r="Q36" s="83" t="s">
         <v>185</v>
       </c>
-      <c r="R36" s="89">
+      <c r="R36" s="84">
         <v>9.0368999999999993</v>
       </c>
-      <c r="S36" s="90">
+      <c r="S36" s="85">
         <f t="shared" si="2"/>
-        <v>117.47969999999999</v>
-      </c>
-      <c r="T36" s="89">
+        <v>108.44279999999999</v>
+      </c>
+      <c r="T36" s="84">
         <v>9.0368999999999993</v>
       </c>
-      <c r="U36" s="60">
+      <c r="U36" s="55">
         <f t="shared" si="3"/>
-        <v>253.03319999999997</v>
-      </c>
-      <c r="V36" s="59"/>
-      <c r="W36" s="76"/>
-    </row>
-    <row r="37" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>243.99629999999999</v>
+      </c>
+      <c r="V36" s="54"/>
+      <c r="W36" s="71"/>
+      <c r="X36" s="105"/>
+      <c r="Y36" s="105"/>
+      <c r="Z36" s="105"/>
+      <c r="AA36" s="105"/>
+      <c r="AB36" s="105"/>
+      <c r="AC36" s="105"/>
+      <c r="AD36" s="105"/>
+      <c r="AE36" s="105"/>
+      <c r="AF36" s="106"/>
+    </row>
+    <row r="37" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
-      <c r="B37" s="58">
+      <c r="B37" s="53">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="62" t="s">
+      <c r="C37" s="57" t="s">
         <v>175</v>
       </c>
-      <c r="D37" s="62" t="s">
+      <c r="D37" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="E37" s="62" t="s">
+      <c r="E37" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="F37" s="62" t="s">
+      <c r="F37" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="G37" s="62" t="s">
+      <c r="G37" s="57" t="s">
         <v>112</v>
       </c>
-      <c r="H37" s="62" t="s">
+      <c r="H37" s="57" t="s">
         <v>136</v>
       </c>
-      <c r="I37" s="84"/>
-      <c r="J37" s="84"/>
-      <c r="K37" s="62" t="s">
-        <v>205</v>
-      </c>
-      <c r="L37" s="62">
+      <c r="I37" s="79"/>
+      <c r="J37" s="79" t="s">
+        <v>215</v>
+      </c>
+      <c r="K37" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="L37" s="57">
         <v>1</v>
       </c>
-      <c r="M37" s="62">
+      <c r="M37" s="57">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N37" s="62">
-        <v>13</v>
-      </c>
-      <c r="O37" s="62">
+      <c r="N37" s="57">
+        <v>12</v>
+      </c>
+      <c r="O37" s="57">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P37" s="62">
-        <v>28</v>
-      </c>
-      <c r="Q37" s="91" t="s">
+      <c r="P37" s="57">
+        <v>27</v>
+      </c>
+      <c r="Q37" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="R37" s="92">
+      <c r="R37" s="87">
         <v>0.54910000000000003</v>
       </c>
-      <c r="S37" s="93">
+      <c r="S37" s="88">
         <f t="shared" si="2"/>
-        <v>7.1383000000000001</v>
-      </c>
-      <c r="T37" s="92">
+        <v>6.5891999999999999</v>
+      </c>
+      <c r="T37" s="87">
         <v>0.54910000000000003</v>
       </c>
-      <c r="U37" s="80">
+      <c r="U37" s="75">
         <f t="shared" si="3"/>
-        <v>15.3748</v>
-      </c>
-      <c r="V37" s="62"/>
-      <c r="W37" s="63"/>
-    </row>
-    <row r="38" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>14.825700000000001</v>
+      </c>
+      <c r="V37" s="57"/>
+      <c r="W37" s="58"/>
+      <c r="X37" s="105"/>
+      <c r="Y37" s="105"/>
+      <c r="Z37" s="105"/>
+      <c r="AA37" s="105"/>
+      <c r="AB37" s="105"/>
+      <c r="AC37" s="105"/>
+      <c r="AD37" s="105"/>
+      <c r="AE37" s="105"/>
+      <c r="AF37" s="106"/>
+    </row>
+    <row r="38" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
-      <c r="B38" s="58">
+      <c r="B38" s="53">
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="59" t="s">
+      <c r="C38" s="54" t="s">
         <v>175</v>
       </c>
-      <c r="D38" s="59" t="s">
+      <c r="D38" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="E38" s="59" t="s">
+      <c r="E38" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="F38" s="59" t="s">
+      <c r="F38" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="G38" s="59" t="s">
+      <c r="G38" s="54" t="s">
         <v>113</v>
       </c>
-      <c r="H38" s="59" t="s">
+      <c r="H38" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="I38" s="83"/>
-      <c r="J38" s="83"/>
-      <c r="K38" s="59" t="s">
-        <v>205</v>
-      </c>
-      <c r="L38" s="59">
+      <c r="I38" s="78"/>
+      <c r="J38" s="78" t="s">
+        <v>216</v>
+      </c>
+      <c r="K38" s="54" t="s">
+        <v>195</v>
+      </c>
+      <c r="L38" s="54">
         <v>1</v>
       </c>
-      <c r="M38" s="59">
+      <c r="M38" s="54">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N38" s="59">
-        <v>13</v>
-      </c>
-      <c r="O38" s="59">
+      <c r="N38" s="54">
+        <v>12</v>
+      </c>
+      <c r="O38" s="54">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P38" s="59">
-        <v>28</v>
-      </c>
-      <c r="Q38" s="88" t="s">
+      <c r="P38" s="54">
+        <v>27</v>
+      </c>
+      <c r="Q38" s="83" t="s">
         <v>185</v>
       </c>
-      <c r="R38" s="89">
+      <c r="R38" s="84">
         <v>0.32369999999999999</v>
       </c>
-      <c r="S38" s="90">
+      <c r="S38" s="85">
         <f t="shared" si="2"/>
-        <v>4.2081</v>
-      </c>
-      <c r="T38" s="89">
+        <v>3.8843999999999999</v>
+      </c>
+      <c r="T38" s="84">
         <v>0.32369999999999999</v>
       </c>
-      <c r="U38" s="60">
+      <c r="U38" s="55">
         <f t="shared" si="3"/>
-        <v>9.0635999999999992</v>
-      </c>
-      <c r="V38" s="59"/>
-      <c r="W38" s="76"/>
-    </row>
-    <row r="39" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>8.7399000000000004</v>
+      </c>
+      <c r="V38" s="54"/>
+      <c r="W38" s="71"/>
+      <c r="Y38" s="105"/>
+      <c r="Z38" s="105"/>
+      <c r="AA38" s="105"/>
+      <c r="AB38" s="106"/>
+      <c r="AC38" s="106"/>
+      <c r="AD38" s="106"/>
+      <c r="AE38" s="106"/>
+      <c r="AF38" s="106"/>
+    </row>
+    <row r="39" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
-      <c r="B39" s="58">
+      <c r="B39" s="53">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="62" t="s">
+      <c r="C39" s="57" t="s">
         <v>171</v>
       </c>
-      <c r="D39" s="62" t="s">
+      <c r="D39" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="E39" s="62" t="s">
+      <c r="E39" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="F39" s="62" t="s">
+      <c r="F39" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="G39" s="62" t="s">
+      <c r="G39" s="57" t="s">
         <v>114</v>
       </c>
-      <c r="H39" s="62" t="s">
+      <c r="H39" s="57" t="s">
         <v>138</v>
       </c>
-      <c r="I39" s="84"/>
-      <c r="J39" s="84"/>
-      <c r="K39" s="62" t="s">
-        <v>205</v>
-      </c>
-      <c r="L39" s="62">
+      <c r="I39" s="79"/>
+      <c r="J39" s="79" t="s">
+        <v>217</v>
+      </c>
+      <c r="K39" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="L39" s="57">
         <v>1</v>
       </c>
-      <c r="M39" s="62">
+      <c r="M39" s="57">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N39" s="62">
-        <v>13</v>
-      </c>
-      <c r="O39" s="62">
+      <c r="N39" s="57">
+        <v>12</v>
+      </c>
+      <c r="O39" s="57">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P39" s="62">
-        <v>28</v>
-      </c>
-      <c r="Q39" s="91" t="s">
+      <c r="P39" s="57">
+        <v>27</v>
+      </c>
+      <c r="Q39" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="R39" s="92">
+      <c r="R39" s="87">
         <v>0.2319</v>
       </c>
-      <c r="S39" s="93">
+      <c r="S39" s="88">
         <f t="shared" si="2"/>
-        <v>3.0146999999999999</v>
-      </c>
-      <c r="T39" s="92">
+        <v>2.7827999999999999</v>
+      </c>
+      <c r="T39" s="87">
         <v>0.2319</v>
       </c>
-      <c r="U39" s="80">
+      <c r="U39" s="75">
         <f t="shared" si="3"/>
-        <v>6.4931999999999999</v>
-      </c>
-      <c r="V39" s="62"/>
-      <c r="W39" s="63"/>
-    </row>
-    <row r="40" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>6.2613000000000003</v>
+      </c>
+      <c r="V39" s="57"/>
+      <c r="W39" s="58"/>
+      <c r="Y39" s="105"/>
+      <c r="Z39" s="105"/>
+      <c r="AA39" s="105"/>
+      <c r="AB39" s="106"/>
+      <c r="AC39" s="106"/>
+      <c r="AD39" s="106"/>
+      <c r="AE39" s="106"/>
+      <c r="AF39" s="106"/>
+    </row>
+    <row r="40" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
-      <c r="B40" s="70">
+      <c r="B40" s="65">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="71" t="s">
+      <c r="C40" s="66" t="s">
         <v>174</v>
       </c>
-      <c r="D40" s="71" t="s">
+      <c r="D40" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="E40" s="71" t="s">
+      <c r="E40" s="66" t="s">
         <v>71</v>
       </c>
-      <c r="F40" s="71" t="s">
+      <c r="F40" s="66" t="s">
         <v>166</v>
       </c>
-      <c r="G40" s="72" t="s">
+      <c r="G40" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="H40" s="71" t="s">
+      <c r="H40" s="66" t="s">
         <v>139</v>
       </c>
-      <c r="I40" s="104" t="s">
-        <v>197</v>
-      </c>
-      <c r="J40" s="105" t="s">
-        <v>198</v>
-      </c>
-      <c r="K40" s="71" t="s">
+      <c r="I40" s="96" t="s">
+        <v>191</v>
+      </c>
+      <c r="J40" s="97" t="s">
+        <v>229</v>
+      </c>
+      <c r="K40" s="66" t="s">
         <v>158</v>
       </c>
-      <c r="L40" s="71">
+      <c r="L40" s="66">
         <v>1</v>
       </c>
-      <c r="M40" s="71">
+      <c r="M40" s="66">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N40" s="71">
-        <v>13</v>
-      </c>
-      <c r="O40" s="71">
+      <c r="N40" s="66">
+        <v>12</v>
+      </c>
+      <c r="O40" s="66">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P40" s="71">
-        <v>28</v>
-      </c>
-      <c r="Q40" s="106" t="s">
+      <c r="P40" s="66">
+        <v>27</v>
+      </c>
+      <c r="Q40" s="98" t="s">
         <v>185</v>
       </c>
-      <c r="R40" s="107">
+      <c r="R40" s="99">
         <v>0.1618</v>
       </c>
-      <c r="S40" s="108">
+      <c r="S40" s="100">
         <f t="shared" si="2"/>
-        <v>2.1034000000000002</v>
-      </c>
-      <c r="T40" s="107">
+        <v>1.9416</v>
+      </c>
+      <c r="T40" s="99">
         <v>0.1618</v>
       </c>
-      <c r="U40" s="73">
+      <c r="U40" s="68">
         <f t="shared" si="3"/>
-        <v>4.5304000000000002</v>
-      </c>
-      <c r="V40" s="71" t="s">
-        <v>200</v>
-      </c>
-      <c r="W40" s="78"/>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+        <v>4.3685999999999998</v>
+      </c>
+      <c r="V40" s="127" t="s">
+        <v>221</v>
+      </c>
+      <c r="W40" s="73"/>
+      <c r="Y40" s="105"/>
+      <c r="Z40" s="105"/>
+      <c r="AA40" s="105"/>
+      <c r="AB40" s="106"/>
+      <c r="AC40" s="106"/>
+    </row>
+    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="30"/>
       <c r="C41" s="40"/>
@@ -4190,32 +4545,37 @@
       <c r="E41" s="32"/>
       <c r="F41" s="33"/>
       <c r="G41" s="34"/>
-      <c r="H41" s="81"/>
-      <c r="I41" s="81"/>
-      <c r="J41" s="81"/>
+      <c r="H41" s="76"/>
+      <c r="I41" s="76"/>
+      <c r="J41" s="76"/>
       <c r="K41" s="34"/>
       <c r="L41" s="34"/>
       <c r="M41" s="34"/>
       <c r="N41" s="34"/>
       <c r="O41" s="34"/>
       <c r="P41" s="34"/>
-      <c r="Q41" s="111" t="s">
-        <v>203</v>
-      </c>
-      <c r="R41" s="74"/>
-      <c r="S41" s="109">
+      <c r="Q41" s="103" t="s">
+        <v>193</v>
+      </c>
+      <c r="R41" s="69"/>
+      <c r="S41" s="101">
         <f>SUM(S10:S40)</f>
-        <v>193.59665999999999</v>
-      </c>
-      <c r="T41" s="74"/>
-      <c r="U41" s="109">
+        <v>173.23060000000001</v>
+      </c>
+      <c r="T41" s="69"/>
+      <c r="U41" s="101">
         <f>SUM(U10:U40)</f>
-        <v>400.88915999999995</v>
-      </c>
-      <c r="V41" s="74"/>
-      <c r="W41" s="75"/>
-    </row>
-    <row r="42" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>377.60679999999996</v>
+      </c>
+      <c r="V41" s="69"/>
+      <c r="W41" s="70"/>
+      <c r="Y41" s="105"/>
+      <c r="Z41" s="105"/>
+      <c r="AA41" s="106"/>
+      <c r="AB41" s="106"/>
+      <c r="AC41" s="106"/>
+    </row>
+    <row r="42" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="24"/>
       <c r="C42" s="41"/>
@@ -4223,30 +4583,208 @@
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
       <c r="G42" s="9"/>
-      <c r="H42" s="82"/>
-      <c r="I42" s="82"/>
-      <c r="J42" s="82"/>
+      <c r="H42" s="77"/>
+      <c r="I42" s="77"/>
+      <c r="J42" s="77"/>
       <c r="K42" s="9"/>
       <c r="L42" s="9"/>
       <c r="M42" s="9"/>
       <c r="N42" s="9"/>
       <c r="O42" s="9"/>
       <c r="P42" s="9"/>
-      <c r="Q42" s="112" t="s">
-        <v>204</v>
-      </c>
-      <c r="R42" s="68"/>
-      <c r="S42" s="110">
+      <c r="Q42" s="104" t="s">
+        <v>194</v>
+      </c>
+      <c r="R42" s="63"/>
+      <c r="S42" s="102">
         <f>S41/10</f>
-        <v>19.359665999999997</v>
-      </c>
-      <c r="T42" s="68"/>
-      <c r="U42" s="110">
+        <v>17.323060000000002</v>
+      </c>
+      <c r="T42" s="63"/>
+      <c r="U42" s="102">
         <f>U41/25</f>
-        <v>16.035566399999997</v>
-      </c>
-      <c r="V42" s="68"/>
-      <c r="W42" s="69"/>
+        <v>15.104271999999998</v>
+      </c>
+      <c r="V42" s="63"/>
+      <c r="W42" s="64"/>
+      <c r="Y42" s="105"/>
+      <c r="Z42" s="105"/>
+    </row>
+    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="Y43" s="105"/>
+      <c r="Z43" s="105"/>
+    </row>
+    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="Y44" s="105"/>
+      <c r="Z44" s="105"/>
+    </row>
+    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="Y45" s="105"/>
+      <c r="Z45" s="105"/>
+    </row>
+    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="Y46" s="105"/>
+      <c r="Z46" s="105"/>
+    </row>
+    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="Y47" s="105"/>
+      <c r="Z47" s="105"/>
+    </row>
+    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="Y48" s="105"/>
+      <c r="Z48" s="105"/>
+    </row>
+    <row r="49" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y49" s="105"/>
+      <c r="Z49" s="105"/>
+    </row>
+    <row r="50" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y50" s="105"/>
+      <c r="Z50" s="105"/>
+    </row>
+    <row r="51" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y51" s="105"/>
+      <c r="Z51" s="105"/>
+    </row>
+    <row r="52" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y52" s="105"/>
+      <c r="Z52" s="105"/>
+    </row>
+    <row r="53" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y53" s="105"/>
+      <c r="Z53" s="105"/>
+    </row>
+    <row r="54" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y54" s="105"/>
+      <c r="Z54" s="105"/>
+    </row>
+    <row r="55" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y55" s="105"/>
+      <c r="Z55" s="105"/>
+    </row>
+    <row r="56" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y56" s="105"/>
+      <c r="Z56" s="105"/>
+    </row>
+    <row r="57" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y57" s="105"/>
+      <c r="Z57" s="105"/>
+    </row>
+    <row r="58" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y58" s="105"/>
+      <c r="Z58" s="105"/>
+    </row>
+    <row r="59" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y59" s="105"/>
+      <c r="Z59" s="105"/>
+    </row>
+    <row r="60" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y60" s="105"/>
+      <c r="Z60" s="105"/>
+    </row>
+    <row r="61" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y61" s="105"/>
+      <c r="Z61" s="105"/>
+    </row>
+    <row r="62" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y62" s="105"/>
+      <c r="Z62" s="105"/>
+    </row>
+    <row r="63" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y63" s="105"/>
+      <c r="Z63" s="105"/>
+    </row>
+    <row r="64" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y64" s="105"/>
+      <c r="Z64" s="105"/>
+    </row>
+    <row r="65" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y65" s="105"/>
+      <c r="Z65" s="105"/>
+    </row>
+    <row r="66" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y66" s="105"/>
+      <c r="Z66" s="105"/>
+    </row>
+    <row r="67" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y67" s="105"/>
+      <c r="Z67" s="105"/>
+    </row>
+    <row r="68" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y68" s="105"/>
+      <c r="Z68" s="105"/>
+    </row>
+    <row r="69" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y69" s="105"/>
+      <c r="Z69" s="105"/>
+    </row>
+    <row r="70" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y70" s="105"/>
+      <c r="Z70" s="105"/>
+    </row>
+    <row r="71" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y71" s="106"/>
+      <c r="Z71" s="105"/>
+    </row>
+    <row r="72" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y72" s="105"/>
+      <c r="Z72" s="105"/>
+    </row>
+    <row r="73" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y73" s="105"/>
+      <c r="Z73" s="105"/>
+    </row>
+    <row r="74" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y74" s="105"/>
+      <c r="Z74" s="105"/>
+    </row>
+    <row r="75" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y75" s="105"/>
+      <c r="Z75" s="105"/>
+    </row>
+    <row r="76" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y76" s="105"/>
+      <c r="Z76" s="105"/>
+    </row>
+    <row r="77" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y77" s="105"/>
+      <c r="Z77" s="105"/>
+    </row>
+    <row r="78" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y78" s="106"/>
+      <c r="Z78" s="106"/>
+    </row>
+    <row r="79" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y79" s="106"/>
+      <c r="Z79" s="106"/>
+    </row>
+    <row r="80" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y80" s="106"/>
+      <c r="Z80" s="106"/>
+    </row>
+    <row r="81" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y81" s="106"/>
+      <c r="Z81" s="106"/>
+    </row>
+    <row r="82" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y82" s="106"/>
+      <c r="Z82" s="106"/>
+    </row>
+    <row r="83" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y83" s="106"/>
+      <c r="Z83" s="106"/>
+    </row>
+    <row r="84" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y84" s="106"/>
+      <c r="Z84" s="106"/>
+    </row>
+    <row r="85" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y85" s="106"/>
+      <c r="Z85" s="106"/>
+    </row>
+    <row r="86" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y86" s="106"/>
+      <c r="Z86" s="106"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4280,11 +4818,11 @@
     <hyperlink ref="Q38" r:id="rId23"/>
     <hyperlink ref="Q39" r:id="rId24"/>
     <hyperlink ref="Q20" r:id="rId25"/>
-    <hyperlink ref="Q24" r:id="rId26"/>
-    <hyperlink ref="Q25" r:id="rId27"/>
-    <hyperlink ref="Q35" r:id="rId28"/>
-    <hyperlink ref="Q22" r:id="rId29"/>
-    <hyperlink ref="Q40" r:id="rId30"/>
+    <hyperlink ref="Q25" r:id="rId26"/>
+    <hyperlink ref="Q35" r:id="rId27"/>
+    <hyperlink ref="Q22" r:id="rId28"/>
+    <hyperlink ref="Q40" r:id="rId29"/>
+    <hyperlink ref="Q24" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId31"/>

--- a/Deliverables/BOM/Espark_BOM.xlsx
+++ b/Deliverables/BOM/Espark_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\JohnWollam-LCDProject\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014C0970-D35D-495B-827E-575320382BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A71E665-A050-4A05-A973-21CA348C056A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1602,6 +1602,77 @@
     <xf numFmtId="166" fontId="17" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1630,77 +1701,6 @@
     <xf numFmtId="0" fontId="28" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2085,15 +2085,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
-      <c r="R1" s="101"/>
-      <c r="S1" s="102"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="128"/>
+      <c r="S1" s="129"/>
     </row>
     <row r="2" spans="1:27" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2118,27 +2118,27 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
-      <c r="S2" s="104"/>
-      <c r="T2" s="104"/>
-      <c r="U2" s="104"/>
-      <c r="V2" s="104"/>
-      <c r="W2" s="105"/>
+      <c r="S2" s="131"/>
+      <c r="T2" s="131"/>
+      <c r="U2" s="131"/>
+      <c r="V2" s="131"/>
+      <c r="W2" s="132"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="17"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111" t="s">
+      <c r="C3" s="101"/>
+      <c r="D3" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="111"/>
-      <c r="F3" s="112" t="s">
+      <c r="E3" s="102"/>
+      <c r="F3" s="103" t="s">
         <v>224</v>
       </c>
-      <c r="G3" s="111"/>
-      <c r="H3" s="113"/>
-      <c r="I3" s="111"/>
-      <c r="J3" s="113"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="104"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="104"/>
       <c r="K3" s="39"/>
       <c r="L3" s="39"/>
       <c r="M3" s="39"/>
@@ -2151,16 +2151,16 @@
       <c r="T3" s="40"/>
       <c r="U3" s="40"/>
       <c r="V3" s="40"/>
-      <c r="W3" s="103"/>
+      <c r="W3" s="130"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="17"/>
-      <c r="C4" s="110"/>
-      <c r="D4" s="111" t="s">
+      <c r="C4" s="101"/>
+      <c r="D4" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="111"/>
+      <c r="E4" s="102"/>
       <c r="F4" s="33" t="s">
         <v>224</v>
       </c>
@@ -2180,16 +2180,16 @@
       <c r="T4" s="36"/>
       <c r="U4" s="36"/>
       <c r="V4" s="36"/>
-      <c r="W4" s="103"/>
+      <c r="W4" s="130"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="17"/>
-      <c r="C5" s="110"/>
-      <c r="D5" s="111" t="s">
+      <c r="C5" s="101"/>
+      <c r="D5" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="111"/>
+      <c r="E5" s="102"/>
       <c r="F5" s="34" t="s">
         <v>5</v>
       </c>
@@ -2209,7 +2209,7 @@
       <c r="T5" s="37"/>
       <c r="U5" s="37"/>
       <c r="V5" s="37"/>
-      <c r="W5" s="103"/>
+      <c r="W5" s="130"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2234,57 +2234,57 @@
       <c r="T6" s="37"/>
       <c r="U6" s="37"/>
       <c r="V6" s="37"/>
-      <c r="W6" s="103"/>
+      <c r="W6" s="130"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="19"/>
-      <c r="C7" s="114"/>
-      <c r="D7" s="115"/>
-      <c r="E7" s="115"/>
+      <c r="C7" s="105"/>
+      <c r="D7" s="106"/>
+      <c r="E7" s="106"/>
       <c r="F7" s="14"/>
-      <c r="G7" s="115"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="115"/>
-      <c r="J7" s="116"/>
-      <c r="K7" s="116"/>
-      <c r="L7" s="116"/>
-      <c r="M7" s="116"/>
-      <c r="N7" s="116"/>
-      <c r="O7" s="116"/>
-      <c r="P7" s="116"/>
-      <c r="Q7" s="116"/>
-      <c r="R7" s="117"/>
-      <c r="S7" s="117"/>
-      <c r="T7" s="117"/>
-      <c r="U7" s="117"/>
-      <c r="V7" s="117"/>
-      <c r="W7" s="103"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
+      <c r="N7" s="107"/>
+      <c r="O7" s="107"/>
+      <c r="P7" s="107"/>
+      <c r="Q7" s="107"/>
+      <c r="R7" s="108"/>
+      <c r="S7" s="108"/>
+      <c r="T7" s="108"/>
+      <c r="U7" s="108"/>
+      <c r="V7" s="108"/>
+      <c r="W7" s="130"/>
     </row>
     <row r="8" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="22"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="115"/>
-      <c r="H8" s="116"/>
-      <c r="I8" s="115"/>
-      <c r="J8" s="116"/>
-      <c r="K8" s="116"/>
-      <c r="L8" s="116"/>
-      <c r="M8" s="116"/>
-      <c r="N8" s="116"/>
-      <c r="O8" s="116"/>
-      <c r="P8" s="116"/>
-      <c r="Q8" s="116"/>
+      <c r="C8" s="109"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="110"/>
+      <c r="F8" s="111"/>
+      <c r="G8" s="106"/>
+      <c r="H8" s="107"/>
+      <c r="I8" s="106"/>
+      <c r="J8" s="107"/>
+      <c r="K8" s="107"/>
+      <c r="L8" s="107"/>
+      <c r="M8" s="107"/>
+      <c r="N8" s="107"/>
+      <c r="O8" s="107"/>
+      <c r="P8" s="107"/>
+      <c r="Q8" s="107"/>
       <c r="R8" s="35"/>
       <c r="S8" s="35"/>
       <c r="T8" s="35"/>
       <c r="U8" s="35"/>
       <c r="V8" s="35"/>
-      <c r="W8" s="103"/>
+      <c r="W8" s="130"/>
     </row>
     <row r="9" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2357,11 +2357,11 @@
     </row>
     <row r="10" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="135">
+      <c r="B10" s="126">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="129" t="s">
+      <c r="C10" s="120" t="s">
         <v>162</v>
       </c>
       <c r="D10" s="90" t="s">
@@ -2423,18 +2423,18 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="V10" s="90"/>
-      <c r="W10" s="121"/>
+      <c r="W10" s="112"/>
       <c r="Y10" s="79"/>
       <c r="Z10" s="79"/>
       <c r="AA10" s="79"/>
     </row>
     <row r="11" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="135">
+      <c r="B11" s="126">
         <f t="shared" ref="B11:B39" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="130" t="s">
+      <c r="C11" s="121" t="s">
         <v>162</v>
       </c>
       <c r="D11" s="43" t="s">
@@ -2496,18 +2496,18 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="V11" s="43"/>
-      <c r="W11" s="122"/>
+      <c r="W11" s="113"/>
       <c r="Y11" s="79"/>
       <c r="Z11" s="79"/>
       <c r="AA11" s="79"/>
     </row>
     <row r="12" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="135">
+      <c r="B12" s="126">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="131" t="s">
+      <c r="C12" s="122" t="s">
         <v>162</v>
       </c>
       <c r="D12" s="41" t="s">
@@ -2569,18 +2569,18 @@
         <v>1.764</v>
       </c>
       <c r="V12" s="41"/>
-      <c r="W12" s="123"/>
+      <c r="W12" s="114"/>
       <c r="Y12" s="79"/>
       <c r="Z12" s="79"/>
       <c r="AA12" s="79"/>
     </row>
     <row r="13" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="135">
+      <c r="B13" s="126">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="130" t="s">
+      <c r="C13" s="121" t="s">
         <v>162</v>
       </c>
       <c r="D13" s="43" t="s">
@@ -2642,18 +2642,18 @@
         <v>0.22</v>
       </c>
       <c r="V13" s="43"/>
-      <c r="W13" s="122"/>
+      <c r="W13" s="113"/>
       <c r="Y13" s="79"/>
       <c r="Z13" s="79"/>
       <c r="AA13" s="79"/>
     </row>
     <row r="14" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="135">
+      <c r="B14" s="126">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="131" t="s">
+      <c r="C14" s="122" t="s">
         <v>162</v>
       </c>
       <c r="D14" s="41" t="s">
@@ -2715,18 +2715,18 @@
         <v>4.0619999999999994</v>
       </c>
       <c r="V14" s="41"/>
-      <c r="W14" s="124"/>
+      <c r="W14" s="115"/>
       <c r="Y14" s="79"/>
       <c r="Z14" s="79"/>
       <c r="AA14" s="79"/>
     </row>
     <row r="15" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="135">
+      <c r="B15" s="126">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="130" t="s">
+      <c r="C15" s="121" t="s">
         <v>162</v>
       </c>
       <c r="D15" s="43" t="s">
@@ -2788,18 +2788,18 @@
         <v>0.26</v>
       </c>
       <c r="V15" s="43"/>
-      <c r="W15" s="122"/>
+      <c r="W15" s="113"/>
       <c r="Y15" s="79"/>
       <c r="Z15" s="79"/>
       <c r="AA15" s="79"/>
     </row>
     <row r="16" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="135">
+      <c r="B16" s="126">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="131" t="s">
+      <c r="C16" s="122" t="s">
         <v>162</v>
       </c>
       <c r="D16" s="41" t="s">
@@ -2861,18 +2861,18 @@
         <v>29.534399999999998</v>
       </c>
       <c r="V16" s="41"/>
-      <c r="W16" s="124"/>
+      <c r="W16" s="115"/>
       <c r="Y16" s="79"/>
       <c r="Z16" s="79"/>
       <c r="AA16" s="79"/>
     </row>
     <row r="17" spans="1:27" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="136">
+      <c r="B17" s="127">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="132" t="s">
+      <c r="C17" s="123" t="s">
         <v>162</v>
       </c>
       <c r="D17" s="80" t="s">
@@ -2934,17 +2934,17 @@
         <v>9.6684000000000001</v>
       </c>
       <c r="V17" s="80"/>
-      <c r="W17" s="122"/>
+      <c r="W17" s="113"/>
       <c r="Y17" s="79"/>
       <c r="Z17" s="79"/>
     </row>
     <row r="18" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="B18" s="135">
+      <c r="B18" s="126">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="131" t="s">
+      <c r="C18" s="122" t="s">
         <v>163</v>
       </c>
       <c r="D18" s="41" t="s">
@@ -3006,18 +3006,18 @@
         <v>1.548</v>
       </c>
       <c r="V18" s="41"/>
-      <c r="W18" s="123"/>
+      <c r="W18" s="114"/>
       <c r="Y18" s="79"/>
       <c r="Z18" s="79"/>
       <c r="AA18" s="79"/>
     </row>
     <row r="19" spans="1:27" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-      <c r="B19" s="135">
+      <c r="B19" s="126">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="130" t="s">
+      <c r="C19" s="121" t="s">
         <v>163</v>
       </c>
       <c r="D19" s="43" t="s">
@@ -3079,18 +3079,18 @@
         <v>1.252</v>
       </c>
       <c r="V19" s="43"/>
-      <c r="W19" s="122"/>
+      <c r="W19" s="113"/>
       <c r="Y19" s="79"/>
       <c r="Z19" s="79"/>
       <c r="AA19" s="79"/>
     </row>
     <row r="20" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="135">
+      <c r="B20" s="126">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="131" t="s">
+      <c r="C20" s="122" t="s">
         <v>164</v>
       </c>
       <c r="D20" s="41" t="s">
@@ -3152,7 +3152,7 @@
         <v>9.0635999999999992</v>
       </c>
       <c r="V20" s="41"/>
-      <c r="W20" s="125" t="s">
+      <c r="W20" s="116" t="s">
         <v>214</v>
       </c>
       <c r="Y20" s="79"/>
@@ -3161,11 +3161,11 @@
     </row>
     <row r="21" spans="1:27" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="135">
+      <c r="B21" s="126">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="130" t="s">
+      <c r="C21" s="121" t="s">
         <v>164</v>
       </c>
       <c r="D21" s="43" t="s">
@@ -3227,18 +3227,18 @@
         <v>3.5579999999999998</v>
       </c>
       <c r="V21" s="43"/>
-      <c r="W21" s="122"/>
+      <c r="W21" s="113"/>
       <c r="Y21" s="79"/>
       <c r="Z21" s="79"/>
       <c r="AA21" s="79"/>
     </row>
     <row r="22" spans="1:27" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="B22" s="135">
+      <c r="B22" s="126">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="131" t="s">
+      <c r="C22" s="122" t="s">
         <v>164</v>
       </c>
       <c r="D22" s="41" t="s">
@@ -3300,7 +3300,7 @@
         <v>6.5190000000000001</v>
       </c>
       <c r="V22" s="41"/>
-      <c r="W22" s="126" t="s">
+      <c r="W22" s="117" t="s">
         <v>215</v>
       </c>
       <c r="Y22" s="79"/>
@@ -3309,11 +3309,11 @@
     </row>
     <row r="23" spans="1:27" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
-      <c r="B23" s="135">
+      <c r="B23" s="126">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="130" t="s">
+      <c r="C23" s="121" t="s">
         <v>165</v>
       </c>
       <c r="D23" s="43" t="s">
@@ -3375,18 +3375,18 @@
         <v>10.693200000000001</v>
       </c>
       <c r="V23" s="43"/>
-      <c r="W23" s="122"/>
+      <c r="W23" s="113"/>
       <c r="Y23" s="79"/>
       <c r="Z23" s="79"/>
       <c r="AA23" s="79"/>
     </row>
     <row r="24" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
-      <c r="B24" s="135">
+      <c r="B24" s="126">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="131" t="s">
+      <c r="C24" s="122" t="s">
         <v>166</v>
       </c>
       <c r="D24" s="41" t="s">
@@ -3448,18 +3448,18 @@
         <v>0.755</v>
       </c>
       <c r="V24" s="41"/>
-      <c r="W24" s="123"/>
+      <c r="W24" s="114"/>
       <c r="Y24" s="79"/>
       <c r="Z24" s="79"/>
       <c r="AA24" s="79"/>
     </row>
     <row r="25" spans="1:27" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="B25" s="135">
+      <c r="B25" s="126">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="130" t="s">
+      <c r="C25" s="121" t="s">
         <v>167</v>
       </c>
       <c r="D25" s="43" t="s">
@@ -3523,18 +3523,18 @@
       <c r="V25" s="43" t="s">
         <v>215</v>
       </c>
-      <c r="W25" s="122"/>
+      <c r="W25" s="113"/>
       <c r="Y25" s="79"/>
       <c r="Z25" s="79"/>
       <c r="AA25" s="79"/>
     </row>
     <row r="26" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
-      <c r="B26" s="135">
+      <c r="B26" s="126">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="131" t="s">
+      <c r="C26" s="122" t="s">
         <v>168</v>
       </c>
       <c r="D26" s="41" t="s">
@@ -3596,18 +3596,18 @@
         <v>4.47</v>
       </c>
       <c r="V26" s="46"/>
-      <c r="W26" s="123"/>
+      <c r="W26" s="114"/>
       <c r="Y26" s="79"/>
       <c r="Z26" s="79"/>
       <c r="AA26" s="79"/>
     </row>
     <row r="27" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
-      <c r="B27" s="135">
+      <c r="B27" s="126">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="130" t="s">
+      <c r="C27" s="121" t="s">
         <v>168</v>
       </c>
       <c r="D27" s="43" t="s">
@@ -3669,18 +3669,18 @@
         <v>0.76500000000000001</v>
       </c>
       <c r="V27" s="43"/>
-      <c r="W27" s="122"/>
+      <c r="W27" s="113"/>
       <c r="Y27" s="79"/>
       <c r="Z27" s="79"/>
       <c r="AA27" s="79"/>
     </row>
     <row r="28" spans="1:27" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
-      <c r="B28" s="135">
+      <c r="B28" s="126">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="131" t="s">
+      <c r="C28" s="122" t="s">
         <v>168</v>
       </c>
       <c r="D28" s="41" t="s">
@@ -3742,18 +3742,18 @@
         <v>0.42</v>
       </c>
       <c r="V28" s="41"/>
-      <c r="W28" s="123"/>
+      <c r="W28" s="114"/>
       <c r="Y28" s="79"/>
       <c r="Z28" s="79"/>
       <c r="AA28" s="79"/>
     </row>
     <row r="29" spans="1:27" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
-      <c r="B29" s="135">
+      <c r="B29" s="126">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="130" t="s">
+      <c r="C29" s="121" t="s">
         <v>168</v>
       </c>
       <c r="D29" s="43" t="s">
@@ -3815,18 +3815,18 @@
         <v>0.44</v>
       </c>
       <c r="V29" s="43"/>
-      <c r="W29" s="122"/>
+      <c r="W29" s="113"/>
       <c r="Y29" s="79"/>
       <c r="Z29" s="79"/>
       <c r="AA29" s="79"/>
     </row>
     <row r="30" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
-      <c r="B30" s="135">
+      <c r="B30" s="126">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="131" t="s">
+      <c r="C30" s="122" t="s">
         <v>168</v>
       </c>
       <c r="D30" s="41" t="s">
@@ -3888,18 +3888,18 @@
         <v>0.13</v>
       </c>
       <c r="V30" s="41"/>
-      <c r="W30" s="123"/>
+      <c r="W30" s="114"/>
       <c r="Y30" s="79"/>
       <c r="Z30" s="79"/>
       <c r="AA30" s="79"/>
     </row>
     <row r="31" spans="1:27" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
-      <c r="B31" s="135">
+      <c r="B31" s="126">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="130" t="s">
+      <c r="C31" s="121" t="s">
         <v>168</v>
       </c>
       <c r="D31" s="43" t="s">
@@ -3961,18 +3961,18 @@
         <v>0.20500000000000002</v>
       </c>
       <c r="V31" s="43"/>
-      <c r="W31" s="122"/>
+      <c r="W31" s="113"/>
       <c r="Y31" s="79"/>
       <c r="Z31" s="79"/>
       <c r="AA31" s="79"/>
     </row>
     <row r="32" spans="1:27" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
-      <c r="B32" s="135">
+      <c r="B32" s="126">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="131" t="s">
+      <c r="C32" s="122" t="s">
         <v>168</v>
       </c>
       <c r="D32" s="41" t="s">
@@ -4034,18 +4034,18 @@
         <v>3.7744</v>
       </c>
       <c r="V32" s="41"/>
-      <c r="W32" s="123"/>
+      <c r="W32" s="114"/>
       <c r="Y32" s="79"/>
       <c r="Z32" s="79"/>
       <c r="AA32" s="79"/>
     </row>
     <row r="33" spans="1:31" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
-      <c r="B33" s="135">
+      <c r="B33" s="126">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="130" t="s">
+      <c r="C33" s="121" t="s">
         <v>168</v>
       </c>
       <c r="D33" s="43" t="s">
@@ -4107,7 +4107,7 @@
         <v>0.1</v>
       </c>
       <c r="V33" s="43"/>
-      <c r="W33" s="122"/>
+      <c r="W33" s="113"/>
       <c r="X33" s="79"/>
       <c r="Y33" s="79"/>
       <c r="Z33" s="79"/>
@@ -4119,11 +4119,11 @@
     </row>
     <row r="34" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
-      <c r="B34" s="135">
+      <c r="B34" s="126">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="133" t="s">
+      <c r="C34" s="124" t="s">
         <v>183</v>
       </c>
       <c r="D34" s="44" t="s">
@@ -4185,7 +4185,7 @@
       <c r="V34" s="44" t="s">
         <v>185</v>
       </c>
-      <c r="W34" s="127"/>
+      <c r="W34" s="118"/>
       <c r="X34" s="79"/>
       <c r="Y34" s="79"/>
       <c r="Z34" s="79"/>
@@ -4197,11 +4197,11 @@
     </row>
     <row r="35" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
-      <c r="B35" s="135">
+      <c r="B35" s="126">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="130" t="s">
+      <c r="C35" s="121" t="s">
         <v>171</v>
       </c>
       <c r="D35" s="43" t="s">
@@ -4263,7 +4263,7 @@
         <v>12.0036</v>
       </c>
       <c r="V35" s="43"/>
-      <c r="W35" s="122"/>
+      <c r="W35" s="113"/>
       <c r="X35" s="79"/>
       <c r="Y35" s="79"/>
       <c r="Z35" s="79"/>
@@ -4275,11 +4275,11 @@
     </row>
     <row r="36" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
-      <c r="B36" s="135">
+      <c r="B36" s="126">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="131" t="s">
+      <c r="C36" s="122" t="s">
         <v>170</v>
       </c>
       <c r="D36" s="41" t="s">
@@ -4341,7 +4341,7 @@
         <v>243.99629999999999</v>
       </c>
       <c r="V36" s="41"/>
-      <c r="W36" s="123"/>
+      <c r="W36" s="114"/>
       <c r="X36" s="79"/>
       <c r="Y36" s="79"/>
       <c r="Z36" s="79"/>
@@ -4353,11 +4353,11 @@
     </row>
     <row r="37" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
-      <c r="B37" s="135">
+      <c r="B37" s="126">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="130" t="s">
+      <c r="C37" s="121" t="s">
         <v>170</v>
       </c>
       <c r="D37" s="43" t="s">
@@ -4419,7 +4419,7 @@
         <v>14.825700000000001</v>
       </c>
       <c r="V37" s="43"/>
-      <c r="W37" s="122"/>
+      <c r="W37" s="113"/>
       <c r="X37" s="79"/>
       <c r="Y37" s="79"/>
       <c r="Z37" s="79"/>
@@ -4431,11 +4431,11 @@
     </row>
     <row r="38" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
-      <c r="B38" s="135">
+      <c r="B38" s="126">
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="131" t="s">
+      <c r="C38" s="122" t="s">
         <v>170</v>
       </c>
       <c r="D38" s="41" t="s">
@@ -4497,18 +4497,18 @@
         <v>8.7399000000000004</v>
       </c>
       <c r="V38" s="41"/>
-      <c r="W38" s="123"/>
+      <c r="W38" s="114"/>
       <c r="Y38" s="79"/>
       <c r="Z38" s="79"/>
       <c r="AA38" s="79"/>
     </row>
     <row r="39" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
-      <c r="B39" s="135">
+      <c r="B39" s="126">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="130" t="s">
+      <c r="C39" s="121" t="s">
         <v>166</v>
       </c>
       <c r="D39" s="43" t="s">
@@ -4570,18 +4570,18 @@
         <v>8.2080000000000002</v>
       </c>
       <c r="V39" s="43"/>
-      <c r="W39" s="122"/>
+      <c r="W39" s="113"/>
       <c r="Y39" s="79"/>
       <c r="Z39" s="79"/>
       <c r="AA39" s="79"/>
     </row>
     <row r="40" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
-      <c r="B40" s="135">
+      <c r="B40" s="126">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="134" t="s">
+      <c r="C40" s="125" t="s">
         <v>169</v>
       </c>
       <c r="D40" s="50" t="s">
@@ -4645,7 +4645,7 @@
       <c r="V40" s="89" t="s">
         <v>214</v>
       </c>
-      <c r="W40" s="128"/>
+      <c r="W40" s="119"/>
       <c r="Y40" s="79"/>
       <c r="Z40" s="79"/>
       <c r="AA40" s="79"/>
@@ -4667,10 +4667,10 @@
       <c r="N41" s="28"/>
       <c r="O41" s="28"/>
       <c r="P41" s="28"/>
-      <c r="Q41" s="106" t="s">
+      <c r="Q41" s="133" t="s">
         <v>186</v>
       </c>
-      <c r="R41" s="107"/>
+      <c r="R41" s="134"/>
       <c r="S41" s="99">
         <f>SUM(S10:S40)</f>
         <v>177.0273</v>
@@ -4702,10 +4702,10 @@
       <c r="N42" s="7"/>
       <c r="O42" s="7"/>
       <c r="P42" s="7"/>
-      <c r="Q42" s="108" t="s">
+      <c r="Q42" s="135" t="s">
         <v>187</v>
       </c>
-      <c r="R42" s="109"/>
+      <c r="R42" s="136"/>
       <c r="S42" s="100">
         <f>S41/10</f>
         <v>17.702729999999999</v>

--- a/Deliverables/BOM/Espark_BOM.xlsx
+++ b/Deliverables/BOM/Espark_BOM.xlsx
@@ -1,36 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\JohnWollam-LCDProject\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A71E665-A050-4A05-A973-21CA348C056A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{406D14AC-9FD5-43C5-ABD3-C99DE92E2683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="233">
   <si>
     <t>Component list</t>
   </si>
@@ -110,9 +100,6 @@
     <t>R6, R7, R8, R9, R10, R11, R12, R13, R14, R15, R17</t>
   </si>
   <si>
-    <t>R18, R20, R21, R22, R23, R24, R25, R26, R27, R28, R29, R30, R31</t>
-  </si>
-  <si>
     <t>R19</t>
   </si>
   <si>
@@ -209,9 +196,6 @@
     <t>RES SMD 10K Ohm 1% 1/10W 0603</t>
   </si>
   <si>
-    <t>RES 56K OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
     <t>±1% 1/10W Thick Film Resistors 75V ±600ppm/℃ -55℃~+155℃ 0.33Ω 0603 Chip Resistor - Surface Mount ROHS</t>
   </si>
   <si>
@@ -341,9 +325,6 @@
     <t>RC0603FR-0710KL</t>
   </si>
   <si>
-    <t>RC0603FR-0756KL</t>
-  </si>
-  <si>
     <t>RTT03R330FTP</t>
   </si>
   <si>
@@ -482,9 +463,6 @@
     <t>10K</t>
   </si>
   <si>
-    <t>56K</t>
-  </si>
-  <si>
     <t>0.33R</t>
   </si>
   <si>
@@ -638,9 +616,6 @@
     <t>C98220</t>
   </si>
   <si>
-    <t>C114630</t>
-  </si>
-  <si>
     <t>C103893</t>
   </si>
   <si>
@@ -717,6 +692,33 @@
   </si>
   <si>
     <t>Reviewer Remarks</t>
+  </si>
+  <si>
+    <t>R20, R21, R22, R23, R24, R25, R26, R27, R28, R29, R30, R31</t>
+  </si>
+  <si>
+    <t>R18</t>
+  </si>
+  <si>
+    <t>RES SMD 1K OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RC0603FR-071KL</t>
+  </si>
+  <si>
+    <t>C22548</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>DNP</t>
+  </si>
+  <si>
+    <t>Terminal Block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R18 Value changed BOM and Design also </t>
   </si>
 </sst>
 </file>
@@ -729,7 +731,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -933,6 +935,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -972,7 +990,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1306,13 +1324,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1442,24 +1473,12 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1481,9 +1500,6 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1516,27 +1532,6 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="22" fillId="2" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="2" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1565,9 +1560,6 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1643,35 +1635,11 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1701,6 +1669,87 @@
     <xf numFmtId="0" fontId="28" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="4" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="4" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="4" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="4" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2045,7 +2094,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AE77"/>
+  <dimension ref="A1:AE78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" style="21" bestFit="1" customWidth="1"/>
@@ -2063,7 +2112,7 @@
     <col min="14" max="14" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -2085,15 +2134,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="128"/>
-      <c r="L1" s="128"/>
-      <c r="M1" s="128"/>
-      <c r="N1" s="128"/>
-      <c r="O1" s="128"/>
-      <c r="P1" s="128"/>
-      <c r="Q1" s="128"/>
-      <c r="R1" s="128"/>
-      <c r="S1" s="129"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="108"/>
     </row>
     <row r="2" spans="1:27" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2104,7 +2153,7 @@
       </c>
       <c r="E2" s="8"/>
       <c r="F2" s="38" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="3"/>
@@ -2118,27 +2167,27 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
-      <c r="S2" s="131"/>
-      <c r="T2" s="131"/>
-      <c r="U2" s="131"/>
-      <c r="V2" s="131"/>
-      <c r="W2" s="132"/>
+      <c r="S2" s="110"/>
+      <c r="T2" s="110"/>
+      <c r="U2" s="110"/>
+      <c r="V2" s="110"/>
+      <c r="W2" s="111"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="17"/>
-      <c r="C3" s="101"/>
-      <c r="D3" s="102" t="s">
+      <c r="C3" s="88"/>
+      <c r="D3" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="102"/>
-      <c r="F3" s="103" t="s">
-        <v>224</v>
-      </c>
-      <c r="G3" s="102"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="104"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="90" t="s">
+        <v>219</v>
+      </c>
+      <c r="G3" s="89"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="91"/>
       <c r="K3" s="39"/>
       <c r="L3" s="39"/>
       <c r="M3" s="39"/>
@@ -2151,18 +2200,18 @@
       <c r="T3" s="40"/>
       <c r="U3" s="40"/>
       <c r="V3" s="40"/>
-      <c r="W3" s="130"/>
+      <c r="W3" s="109"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="17"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="102" t="s">
+      <c r="C4" s="88"/>
+      <c r="D4" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="102"/>
+      <c r="E4" s="89"/>
       <c r="F4" s="33" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="5"/>
@@ -2180,16 +2229,16 @@
       <c r="T4" s="36"/>
       <c r="U4" s="36"/>
       <c r="V4" s="36"/>
-      <c r="W4" s="130"/>
+      <c r="W4" s="109"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="17"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="102" t="s">
+      <c r="C5" s="88"/>
+      <c r="D5" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="102"/>
+      <c r="E5" s="89"/>
       <c r="F5" s="34" t="s">
         <v>5</v>
       </c>
@@ -2209,7 +2258,7 @@
       <c r="T5" s="37"/>
       <c r="U5" s="37"/>
       <c r="V5" s="37"/>
-      <c r="W5" s="130"/>
+      <c r="W5" s="109"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2234,232 +2283,232 @@
       <c r="T6" s="37"/>
       <c r="U6" s="37"/>
       <c r="V6" s="37"/>
-      <c r="W6" s="130"/>
+      <c r="W6" s="109"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="19"/>
-      <c r="C7" s="105"/>
-      <c r="D7" s="106"/>
-      <c r="E7" s="106"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="93"/>
       <c r="F7" s="14"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="107"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="107"/>
-      <c r="K7" s="107"/>
-      <c r="L7" s="107"/>
-      <c r="M7" s="107"/>
-      <c r="N7" s="107"/>
-      <c r="O7" s="107"/>
-      <c r="P7" s="107"/>
-      <c r="Q7" s="107"/>
-      <c r="R7" s="108"/>
-      <c r="S7" s="108"/>
-      <c r="T7" s="108"/>
-      <c r="U7" s="108"/>
-      <c r="V7" s="108"/>
-      <c r="W7" s="130"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="94"/>
+      <c r="K7" s="94"/>
+      <c r="L7" s="94"/>
+      <c r="M7" s="94"/>
+      <c r="N7" s="94"/>
+      <c r="O7" s="94"/>
+      <c r="P7" s="94"/>
+      <c r="Q7" s="94"/>
+      <c r="R7" s="95"/>
+      <c r="S7" s="95"/>
+      <c r="T7" s="95"/>
+      <c r="U7" s="95"/>
+      <c r="V7" s="95"/>
+      <c r="W7" s="109"/>
     </row>
     <row r="8" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="22"/>
-      <c r="C8" s="109"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
-      <c r="F8" s="111"/>
-      <c r="G8" s="106"/>
-      <c r="H8" s="107"/>
-      <c r="I8" s="106"/>
-      <c r="J8" s="107"/>
-      <c r="K8" s="107"/>
-      <c r="L8" s="107"/>
-      <c r="M8" s="107"/>
-      <c r="N8" s="107"/>
-      <c r="O8" s="107"/>
-      <c r="P8" s="107"/>
-      <c r="Q8" s="107"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="94"/>
+      <c r="K8" s="94"/>
+      <c r="L8" s="94"/>
+      <c r="M8" s="94"/>
+      <c r="N8" s="94"/>
+      <c r="O8" s="94"/>
+      <c r="P8" s="94"/>
+      <c r="Q8" s="94"/>
       <c r="R8" s="35"/>
       <c r="S8" s="35"/>
       <c r="T8" s="35"/>
       <c r="U8" s="35"/>
       <c r="V8" s="35"/>
-      <c r="W8" s="130"/>
+      <c r="W8" s="109"/>
     </row>
     <row r="9" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="97" t="s">
-        <v>156</v>
+      <c r="C9" s="84" t="s">
+        <v>152</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="96" t="s">
-        <v>38</v>
+      <c r="E9" s="83" t="s">
+        <v>37</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="G9" s="96" t="s">
-        <v>85</v>
+        <v>68</v>
+      </c>
+      <c r="G9" s="83" t="s">
+        <v>83</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>227</v>
-      </c>
-      <c r="L9" s="96" t="s">
+        <v>222</v>
+      </c>
+      <c r="L9" s="83" t="s">
+        <v>151</v>
+      </c>
+      <c r="M9" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="N9" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="O9" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="P9" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q9" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="M9" s="23" t="s">
+      <c r="R9" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="N9" s="23" t="s">
+      <c r="S9" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="O9" s="23" t="s">
+      <c r="T9" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="P9" s="23" t="s">
+      <c r="U9" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="Q9" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="R9" s="23" t="s">
-        <v>176</v>
-      </c>
-      <c r="S9" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="T9" s="23" t="s">
-        <v>178</v>
-      </c>
-      <c r="U9" s="23" t="s">
-        <v>179</v>
-      </c>
-      <c r="V9" s="97" t="s">
-        <v>160</v>
-      </c>
-      <c r="W9" s="97" t="s">
-        <v>228</v>
+      <c r="V9" s="84" t="s">
+        <v>156</v>
+      </c>
+      <c r="W9" s="84" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="126">
+      <c r="B10" s="106">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="120" t="s">
-        <v>162</v>
-      </c>
-      <c r="D10" s="90" t="s">
+      <c r="C10" s="137" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="133" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="90" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="90" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="90" t="s">
-        <v>86</v>
-      </c>
-      <c r="H10" s="90" t="s">
-        <v>114</v>
-      </c>
-      <c r="I10" s="91" t="s">
-        <v>188</v>
-      </c>
-      <c r="J10" s="91" t="s">
-        <v>189</v>
-      </c>
-      <c r="K10" s="90" t="s">
-        <v>137</v>
-      </c>
-      <c r="L10" s="90">
+      <c r="E10" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="77" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="77" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="I10" s="78" t="s">
+        <v>184</v>
+      </c>
+      <c r="J10" s="78" t="s">
+        <v>185</v>
+      </c>
+      <c r="K10" s="77" t="s">
+        <v>134</v>
+      </c>
+      <c r="L10" s="77">
         <v>6</v>
       </c>
-      <c r="M10" s="90">
+      <c r="M10" s="77">
         <f>L10*10</f>
         <v>60</v>
       </c>
-      <c r="N10" s="90">
+      <c r="N10" s="77">
         <v>100</v>
       </c>
-      <c r="O10" s="90">
+      <c r="O10" s="77">
         <f>L10*25</f>
         <v>150</v>
       </c>
-      <c r="P10" s="90">
+      <c r="P10" s="77">
         <v>200</v>
       </c>
-      <c r="Q10" s="92" t="s">
-        <v>180</v>
-      </c>
-      <c r="R10" s="93">
+      <c r="Q10" s="79" t="s">
+        <v>176</v>
+      </c>
+      <c r="R10" s="80">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="S10" s="94">
+      <c r="S10" s="81">
         <f>R10*N10</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="T10" s="93">
+      <c r="T10" s="80">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="U10" s="95">
+      <c r="U10" s="82">
         <f>T10*P10</f>
         <v>0.57999999999999996</v>
       </c>
-      <c r="V10" s="90"/>
-      <c r="W10" s="112"/>
-      <c r="Y10" s="79"/>
-      <c r="Z10" s="79"/>
-      <c r="AA10" s="79"/>
+      <c r="V10" s="77"/>
+      <c r="W10" s="99"/>
+      <c r="Y10" s="67"/>
+      <c r="Z10" s="67"/>
+      <c r="AA10" s="67"/>
     </row>
     <row r="11" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="126">
-        <f t="shared" ref="B11:B39" si="0">ROW(B11) - ROW($B$9)</f>
+      <c r="B11" s="106">
+        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="121" t="s">
-        <v>162</v>
-      </c>
-      <c r="D11" s="43" t="s">
+      <c r="C11" s="138" t="s">
+        <v>158</v>
+      </c>
+      <c r="D11" s="134" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F11" s="43" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H11" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="I11" s="59" t="s">
-        <v>188</v>
-      </c>
-      <c r="J11" s="59" t="s">
-        <v>190</v>
+        <v>111</v>
+      </c>
+      <c r="I11" s="55" t="s">
+        <v>184</v>
+      </c>
+      <c r="J11" s="55" t="s">
+        <v>186</v>
       </c>
       <c r="K11" s="43" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="L11" s="43">
         <v>2</v>
@@ -2472,73 +2521,73 @@
         <v>100</v>
       </c>
       <c r="O11" s="43">
-        <f t="shared" ref="O11:O40" si="1">L11*25</f>
+        <f t="shared" ref="O11:O41" si="1">L11*25</f>
         <v>50</v>
       </c>
       <c r="P11" s="43">
         <v>100</v>
       </c>
-      <c r="Q11" s="64" t="s">
-        <v>180</v>
-      </c>
-      <c r="R11" s="65">
+      <c r="Q11" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="R11" s="60">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="S11" s="66">
-        <f t="shared" ref="S11:S40" si="2">R11*N11</f>
+      <c r="S11" s="61">
+        <f t="shared" ref="S11:S41" si="2">R11*N11</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="T11" s="65">
+      <c r="T11" s="60">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="U11" s="55">
-        <f t="shared" ref="U11:U40" si="3">T11*P11</f>
+      <c r="U11" s="51">
+        <f t="shared" ref="U11:U41" si="3">T11*P11</f>
         <v>0.28999999999999998</v>
       </c>
       <c r="V11" s="43"/>
-      <c r="W11" s="113"/>
-      <c r="Y11" s="79"/>
-      <c r="Z11" s="79"/>
-      <c r="AA11" s="79"/>
+      <c r="W11" s="100"/>
+      <c r="Y11" s="67"/>
+      <c r="Z11" s="67"/>
+      <c r="AA11" s="67"/>
     </row>
     <row r="12" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="126">
-        <f>ROW(B12) - ROW($B$9)</f>
+      <c r="B12" s="106">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="122" t="s">
-        <v>162</v>
-      </c>
-      <c r="D12" s="41" t="s">
+      <c r="C12" s="139" t="s">
+        <v>158</v>
+      </c>
+      <c r="D12" s="135" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F12" s="41" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G12" s="41" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H12" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="I12" s="58" t="s">
-        <v>188</v>
-      </c>
-      <c r="J12" s="58" t="s">
-        <v>191</v>
+        <v>112</v>
+      </c>
+      <c r="I12" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="J12" s="54" t="s">
+        <v>187</v>
       </c>
       <c r="K12" s="41" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="L12" s="41">
         <v>2</v>
       </c>
       <c r="M12" s="41">
-        <f t="shared" ref="M12:M40" si="4">L12*10</f>
+        <f t="shared" ref="M12:M41" si="4">L12*10</f>
         <v>20</v>
       </c>
       <c r="N12" s="41">
@@ -2551,17 +2600,17 @@
       <c r="P12" s="41">
         <v>60</v>
       </c>
-      <c r="Q12" s="61" t="s">
-        <v>180</v>
-      </c>
-      <c r="R12" s="62">
+      <c r="Q12" s="56" t="s">
+        <v>176</v>
+      </c>
+      <c r="R12" s="57">
         <v>2.9399999999999999E-2</v>
       </c>
-      <c r="S12" s="63">
+      <c r="S12" s="58">
         <f t="shared" si="2"/>
         <v>1.1759999999999999</v>
       </c>
-      <c r="T12" s="62">
+      <c r="T12" s="57">
         <v>2.9399999999999999E-2</v>
       </c>
       <c r="U12" s="42">
@@ -2569,43 +2618,43 @@
         <v>1.764</v>
       </c>
       <c r="V12" s="41"/>
-      <c r="W12" s="114"/>
-      <c r="Y12" s="79"/>
-      <c r="Z12" s="79"/>
-      <c r="AA12" s="79"/>
+      <c r="W12" s="101"/>
+      <c r="Y12" s="67"/>
+      <c r="Z12" s="67"/>
+      <c r="AA12" s="67"/>
     </row>
     <row r="13" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="126">
+      <c r="B13" s="106">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="121" t="s">
-        <v>162</v>
-      </c>
-      <c r="D13" s="43" t="s">
+      <c r="C13" s="138" t="s">
+        <v>158</v>
+      </c>
+      <c r="D13" s="134" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F13" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H13" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="I13" s="59" t="s">
+        <v>111</v>
+      </c>
+      <c r="I13" s="55" t="s">
+        <v>184</v>
+      </c>
+      <c r="J13" s="55" t="s">
         <v>188</v>
       </c>
-      <c r="J13" s="59" t="s">
-        <v>192</v>
-      </c>
       <c r="K13" s="43" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="L13" s="43">
         <v>1</v>
@@ -2624,61 +2673,61 @@
       <c r="P13" s="43">
         <v>100</v>
       </c>
-      <c r="Q13" s="64" t="s">
-        <v>180</v>
-      </c>
-      <c r="R13" s="65">
+      <c r="Q13" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="R13" s="60">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="S13" s="66">
+      <c r="S13" s="61">
         <f t="shared" si="2"/>
         <v>0.22</v>
       </c>
-      <c r="T13" s="65">
+      <c r="T13" s="60">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="U13" s="55">
+      <c r="U13" s="51">
         <f t="shared" si="3"/>
         <v>0.22</v>
       </c>
       <c r="V13" s="43"/>
-      <c r="W13" s="113"/>
-      <c r="Y13" s="79"/>
-      <c r="Z13" s="79"/>
-      <c r="AA13" s="79"/>
+      <c r="W13" s="100"/>
+      <c r="Y13" s="67"/>
+      <c r="Z13" s="67"/>
+      <c r="AA13" s="67"/>
     </row>
     <row r="14" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="126">
-        <f>ROW(B14) - ROW($B$9)</f>
+      <c r="B14" s="106">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="122" t="s">
-        <v>162</v>
-      </c>
-      <c r="D14" s="41" t="s">
+      <c r="C14" s="139" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" s="135" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F14" s="41" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G14" s="41" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H14" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="I14" s="58" t="s">
-        <v>188</v>
-      </c>
-      <c r="J14" s="58" t="s">
-        <v>193</v>
+        <v>113</v>
+      </c>
+      <c r="I14" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="J14" s="54" t="s">
+        <v>189</v>
       </c>
       <c r="K14" s="41" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="L14" s="41">
         <v>2</v>
@@ -2697,17 +2746,17 @@
       <c r="P14" s="41">
         <v>60</v>
       </c>
-      <c r="Q14" s="61" t="s">
-        <v>180</v>
-      </c>
-      <c r="R14" s="62">
+      <c r="Q14" s="56" t="s">
+        <v>176</v>
+      </c>
+      <c r="R14" s="57">
         <v>6.7699999999999996E-2</v>
       </c>
-      <c r="S14" s="63">
+      <c r="S14" s="58">
         <f t="shared" si="2"/>
         <v>2.0309999999999997</v>
       </c>
-      <c r="T14" s="62">
+      <c r="T14" s="57">
         <v>6.7699999999999996E-2</v>
       </c>
       <c r="U14" s="42">
@@ -2715,43 +2764,43 @@
         <v>4.0619999999999994</v>
       </c>
       <c r="V14" s="41"/>
-      <c r="W14" s="115"/>
-      <c r="Y14" s="79"/>
-      <c r="Z14" s="79"/>
-      <c r="AA14" s="79"/>
+      <c r="W14" s="102"/>
+      <c r="Y14" s="67"/>
+      <c r="Z14" s="67"/>
+      <c r="AA14" s="67"/>
     </row>
     <row r="15" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="126">
+      <c r="B15" s="106">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="121" t="s">
-        <v>162</v>
-      </c>
-      <c r="D15" s="43" t="s">
+      <c r="C15" s="138" t="s">
+        <v>158</v>
+      </c>
+      <c r="D15" s="134" t="s">
         <v>12</v>
       </c>
       <c r="E15" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F15" s="43" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G15" s="43" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H15" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="I15" s="59" t="s">
-        <v>188</v>
-      </c>
-      <c r="J15" s="59" t="s">
-        <v>194</v>
+        <v>111</v>
+      </c>
+      <c r="I15" s="55" t="s">
+        <v>184</v>
+      </c>
+      <c r="J15" s="55" t="s">
+        <v>190</v>
       </c>
       <c r="K15" s="43" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="L15" s="43">
         <v>1</v>
@@ -2770,61 +2819,61 @@
       <c r="P15" s="43">
         <v>100</v>
       </c>
-      <c r="Q15" s="64" t="s">
-        <v>180</v>
-      </c>
-      <c r="R15" s="65">
+      <c r="Q15" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="R15" s="60">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="S15" s="66">
+      <c r="S15" s="61">
         <f t="shared" si="2"/>
         <v>0.26</v>
       </c>
-      <c r="T15" s="65">
+      <c r="T15" s="60">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="U15" s="55">
+      <c r="U15" s="51">
         <f t="shared" si="3"/>
         <v>0.26</v>
       </c>
       <c r="V15" s="43"/>
-      <c r="W15" s="113"/>
-      <c r="Y15" s="79"/>
-      <c r="Z15" s="79"/>
-      <c r="AA15" s="79"/>
+      <c r="W15" s="100"/>
+      <c r="Y15" s="67"/>
+      <c r="Z15" s="67"/>
+      <c r="AA15" s="67"/>
     </row>
     <row r="16" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="126">
-        <f>ROW(B16) - ROW($B$9)</f>
+      <c r="B16" s="106">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="122" t="s">
-        <v>162</v>
-      </c>
-      <c r="D16" s="41" t="s">
+      <c r="C16" s="139" t="s">
+        <v>158</v>
+      </c>
+      <c r="D16" s="135" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F16" s="41" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G16" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H16" s="41" t="s">
-        <v>117</v>
-      </c>
-      <c r="I16" s="58" t="s">
-        <v>188</v>
-      </c>
-      <c r="J16" s="58" t="s">
-        <v>195</v>
+        <v>114</v>
+      </c>
+      <c r="I16" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="J16" s="54" t="s">
+        <v>191</v>
       </c>
       <c r="K16" s="41" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="L16" s="41">
         <v>1</v>
@@ -2843,17 +2892,17 @@
       <c r="P16" s="41">
         <v>28</v>
       </c>
-      <c r="Q16" s="61" t="s">
-        <v>180</v>
-      </c>
-      <c r="R16" s="62">
+      <c r="Q16" s="56" t="s">
+        <v>176</v>
+      </c>
+      <c r="R16" s="57">
         <v>1.0548</v>
       </c>
-      <c r="S16" s="63">
+      <c r="S16" s="58">
         <f t="shared" si="2"/>
         <v>12.657599999999999</v>
       </c>
-      <c r="T16" s="62">
+      <c r="T16" s="57">
         <v>1.0548</v>
       </c>
       <c r="U16" s="42">
@@ -2861,115 +2910,115 @@
         <v>29.534399999999998</v>
       </c>
       <c r="V16" s="41"/>
-      <c r="W16" s="115"/>
-      <c r="Y16" s="79"/>
-      <c r="Z16" s="79"/>
-      <c r="AA16" s="79"/>
+      <c r="W16" s="102"/>
+      <c r="Y16" s="67"/>
+      <c r="Z16" s="67"/>
+      <c r="AA16" s="67"/>
     </row>
     <row r="17" spans="1:27" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="127">
+      <c r="B17" s="106">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="123" t="s">
-        <v>162</v>
-      </c>
-      <c r="D17" s="80" t="s">
+      <c r="C17" s="140" t="s">
+        <v>158</v>
+      </c>
+      <c r="D17" s="85" t="s">
         <v>14</v>
       </c>
       <c r="E17" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="80" t="s">
-        <v>161</v>
-      </c>
-      <c r="G17" s="80" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="80" t="s">
-        <v>118</v>
-      </c>
-      <c r="I17" s="81" t="s">
-        <v>188</v>
-      </c>
-      <c r="J17" s="80" t="s">
-        <v>211</v>
-      </c>
-      <c r="K17" s="80" t="s">
-        <v>144</v>
-      </c>
-      <c r="L17" s="80">
+        <v>45</v>
+      </c>
+      <c r="F17" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="I17" s="69" t="s">
+        <v>184</v>
+      </c>
+      <c r="J17" s="68" t="s">
+        <v>206</v>
+      </c>
+      <c r="K17" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="L17" s="68">
         <v>1</v>
       </c>
-      <c r="M17" s="80">
+      <c r="M17" s="68">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N17" s="80">
+      <c r="N17" s="68">
         <v>12</v>
       </c>
-      <c r="O17" s="80">
+      <c r="O17" s="68">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P17" s="80">
+      <c r="P17" s="68">
         <v>28</v>
       </c>
-      <c r="Q17" s="82" t="s">
-        <v>180</v>
-      </c>
-      <c r="R17" s="65">
+      <c r="Q17" s="70" t="s">
+        <v>176</v>
+      </c>
+      <c r="R17" s="60">
         <v>0.37180000000000002</v>
       </c>
-      <c r="S17" s="83">
+      <c r="S17" s="71">
         <f t="shared" si="2"/>
         <v>4.4616000000000007</v>
       </c>
-      <c r="T17" s="65">
+      <c r="T17" s="60">
         <v>0.3453</v>
       </c>
-      <c r="U17" s="84">
+      <c r="U17" s="72">
         <f t="shared" si="3"/>
         <v>9.6684000000000001</v>
       </c>
-      <c r="V17" s="80"/>
-      <c r="W17" s="113"/>
-      <c r="Y17" s="79"/>
-      <c r="Z17" s="79"/>
+      <c r="V17" s="68"/>
+      <c r="W17" s="100"/>
+      <c r="Y17" s="67"/>
+      <c r="Z17" s="67"/>
     </row>
     <row r="18" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="B18" s="126">
-        <f>ROW(B18) - ROW($B$9)</f>
+      <c r="B18" s="106">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="122" t="s">
-        <v>163</v>
-      </c>
-      <c r="D18" s="41" t="s">
+      <c r="C18" s="139" t="s">
+        <v>159</v>
+      </c>
+      <c r="D18" s="135" t="s">
         <v>15</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F18" s="41" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G18" s="41" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H18" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="I18" s="58" t="s">
-        <v>188</v>
-      </c>
-      <c r="J18" s="58" t="s">
-        <v>196</v>
+        <v>116</v>
+      </c>
+      <c r="I18" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="J18" s="54" t="s">
+        <v>192</v>
       </c>
       <c r="K18" s="41" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L18" s="41">
         <v>2</v>
@@ -2988,17 +3037,17 @@
       <c r="P18" s="41">
         <v>60</v>
       </c>
-      <c r="Q18" s="61" t="s">
-        <v>180</v>
-      </c>
-      <c r="R18" s="62">
+      <c r="Q18" s="56" t="s">
+        <v>176</v>
+      </c>
+      <c r="R18" s="57">
         <v>2.58E-2</v>
       </c>
-      <c r="S18" s="63">
+      <c r="S18" s="58">
         <f t="shared" si="2"/>
         <v>1.032</v>
       </c>
-      <c r="T18" s="62">
+      <c r="T18" s="57">
         <v>2.58E-2</v>
       </c>
       <c r="U18" s="42">
@@ -3006,43 +3055,43 @@
         <v>1.548</v>
       </c>
       <c r="V18" s="41"/>
-      <c r="W18" s="114"/>
-      <c r="Y18" s="79"/>
-      <c r="Z18" s="79"/>
-      <c r="AA18" s="79"/>
+      <c r="W18" s="101"/>
+      <c r="Y18" s="67"/>
+      <c r="Z18" s="67"/>
+      <c r="AA18" s="67"/>
     </row>
     <row r="19" spans="1:27" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-      <c r="B19" s="126">
+      <c r="B19" s="106">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="121" t="s">
-        <v>163</v>
-      </c>
-      <c r="D19" s="43" t="s">
+      <c r="C19" s="138" t="s">
+        <v>159</v>
+      </c>
+      <c r="D19" s="134" t="s">
         <v>16</v>
       </c>
       <c r="E19" s="43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F19" s="43" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G19" s="43" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H19" s="43" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I19" s="43" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="J19" s="43" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K19" s="43" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L19" s="43">
         <v>1</v>
@@ -3061,61 +3110,61 @@
       <c r="P19" s="43">
         <v>40</v>
       </c>
-      <c r="Q19" s="64" t="s">
-        <v>180</v>
-      </c>
-      <c r="R19" s="65">
+      <c r="Q19" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="R19" s="60">
         <v>3.1300000000000001E-2</v>
       </c>
-      <c r="S19" s="66">
+      <c r="S19" s="61">
         <f t="shared" si="2"/>
         <v>0.626</v>
       </c>
-      <c r="T19" s="65">
+      <c r="T19" s="60">
         <v>3.1300000000000001E-2</v>
       </c>
-      <c r="U19" s="55">
+      <c r="U19" s="51">
         <f t="shared" si="3"/>
         <v>1.252</v>
       </c>
       <c r="V19" s="43"/>
-      <c r="W19" s="113"/>
-      <c r="Y19" s="79"/>
-      <c r="Z19" s="79"/>
-      <c r="AA19" s="79"/>
+      <c r="W19" s="100"/>
+      <c r="Y19" s="67"/>
+      <c r="Z19" s="67"/>
+      <c r="AA19" s="67"/>
     </row>
     <row r="20" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="126">
-        <f>ROW(B20) - ROW($B$9)</f>
+      <c r="B20" s="106">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="122" t="s">
-        <v>164</v>
-      </c>
-      <c r="D20" s="41" t="s">
+      <c r="C20" s="139" t="s">
+        <v>231</v>
+      </c>
+      <c r="D20" s="135" t="s">
         <v>17</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F20" s="41" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G20" s="44" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H20" s="41" t="s">
-        <v>121</v>
-      </c>
-      <c r="I20" s="58" t="s">
-        <v>212</v>
-      </c>
-      <c r="J20" s="58" t="s">
-        <v>213</v>
+        <v>118</v>
+      </c>
+      <c r="I20" s="54" t="s">
+        <v>207</v>
+      </c>
+      <c r="J20" s="54" t="s">
+        <v>208</v>
       </c>
       <c r="K20" s="41" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L20" s="41">
         <v>1</v>
@@ -3134,17 +3183,17 @@
       <c r="P20" s="41">
         <v>28</v>
       </c>
-      <c r="Q20" s="61" t="s">
-        <v>180</v>
-      </c>
-      <c r="R20" s="67">
+      <c r="Q20" s="56" t="s">
+        <v>176</v>
+      </c>
+      <c r="R20" s="62">
         <v>0.32369999999999999</v>
       </c>
-      <c r="S20" s="63">
+      <c r="S20" s="58">
         <f t="shared" si="2"/>
         <v>3.8843999999999999</v>
       </c>
-      <c r="T20" s="67">
+      <c r="T20" s="62">
         <v>0.32369999999999999</v>
       </c>
       <c r="U20" s="42">
@@ -3152,45 +3201,45 @@
         <v>9.0635999999999992</v>
       </c>
       <c r="V20" s="41"/>
-      <c r="W20" s="116" t="s">
-        <v>214</v>
-      </c>
-      <c r="Y20" s="79"/>
-      <c r="Z20" s="79"/>
-      <c r="AA20" s="79"/>
+      <c r="W20" s="103" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y20" s="67"/>
+      <c r="Z20" s="67"/>
+      <c r="AA20" s="67"/>
     </row>
     <row r="21" spans="1:27" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="126">
+      <c r="B21" s="106">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="121" t="s">
-        <v>164</v>
-      </c>
-      <c r="D21" s="43" t="s">
+      <c r="C21" s="138" t="s">
+        <v>231</v>
+      </c>
+      <c r="D21" s="134" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F21" s="43" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G21" s="43" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H21" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="I21" s="59" t="s">
-        <v>188</v>
+        <v>119</v>
+      </c>
+      <c r="I21" s="55" t="s">
+        <v>184</v>
       </c>
       <c r="J21" s="43" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="K21" s="43" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L21" s="43">
         <v>1</v>
@@ -3209,61 +3258,61 @@
       <c r="P21" s="43">
         <v>30</v>
       </c>
-      <c r="Q21" s="64" t="s">
-        <v>180</v>
-      </c>
-      <c r="R21" s="65">
+      <c r="Q21" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="R21" s="60">
         <v>0.1186</v>
       </c>
-      <c r="S21" s="66">
+      <c r="S21" s="61">
         <f t="shared" si="2"/>
         <v>1.7789999999999999</v>
       </c>
-      <c r="T21" s="65">
+      <c r="T21" s="60">
         <v>0.1186</v>
       </c>
-      <c r="U21" s="55">
+      <c r="U21" s="51">
         <f t="shared" si="3"/>
         <v>3.5579999999999998</v>
       </c>
       <c r="V21" s="43"/>
-      <c r="W21" s="113"/>
-      <c r="Y21" s="79"/>
-      <c r="Z21" s="79"/>
-      <c r="AA21" s="79"/>
+      <c r="W21" s="100"/>
+      <c r="Y21" s="67"/>
+      <c r="Z21" s="67"/>
+      <c r="AA21" s="67"/>
     </row>
     <row r="22" spans="1:27" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="B22" s="126">
-        <f>ROW(B22) - ROW($B$9)</f>
+      <c r="B22" s="106">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="122" t="s">
-        <v>164</v>
-      </c>
-      <c r="D22" s="41" t="s">
+      <c r="C22" s="139" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" s="135" t="s">
         <v>19</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F22" s="41" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G22" s="44" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H22" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="I22" s="85" t="s">
-        <v>225</v>
-      </c>
-      <c r="J22" s="86" t="s">
-        <v>226</v>
+        <v>120</v>
+      </c>
+      <c r="I22" s="73" t="s">
+        <v>220</v>
+      </c>
+      <c r="J22" s="74" t="s">
+        <v>221</v>
       </c>
       <c r="K22" s="41" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L22" s="41">
         <v>1</v>
@@ -3282,17 +3331,17 @@
       <c r="P22" s="41">
         <v>30</v>
       </c>
-      <c r="Q22" s="61" t="s">
-        <v>180</v>
-      </c>
-      <c r="R22" s="67">
+      <c r="Q22" s="56" t="s">
+        <v>176</v>
+      </c>
+      <c r="R22" s="62">
         <v>0.21729999999999999</v>
       </c>
-      <c r="S22" s="63">
+      <c r="S22" s="58">
         <f t="shared" si="2"/>
         <v>2.6075999999999997</v>
       </c>
-      <c r="T22" s="67">
+      <c r="T22" s="62">
         <v>0.21729999999999999</v>
       </c>
       <c r="U22" s="42">
@@ -3300,45 +3349,45 @@
         <v>6.5190000000000001</v>
       </c>
       <c r="V22" s="41"/>
-      <c r="W22" s="117" t="s">
-        <v>215</v>
-      </c>
-      <c r="Y22" s="79"/>
-      <c r="Z22" s="79"/>
-      <c r="AA22" s="79"/>
+      <c r="W22" s="104" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y22" s="67"/>
+      <c r="Z22" s="67"/>
+      <c r="AA22" s="67"/>
     </row>
     <row r="23" spans="1:27" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
-      <c r="B23" s="126">
+      <c r="B23" s="106">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="121" t="s">
-        <v>165</v>
-      </c>
-      <c r="D23" s="43" t="s">
+      <c r="C23" s="138" t="s">
+        <v>161</v>
+      </c>
+      <c r="D23" s="134" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F23" s="43" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G23" s="43" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H23" s="43" t="s">
-        <v>124</v>
-      </c>
-      <c r="I23" s="98" t="s">
-        <v>188</v>
+        <v>121</v>
+      </c>
+      <c r="I23" s="85" t="s">
+        <v>184</v>
       </c>
       <c r="J23" s="43" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="K23" s="43" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="L23" s="43">
         <v>1</v>
@@ -3357,61 +3406,61 @@
       <c r="P23" s="43">
         <v>28</v>
       </c>
-      <c r="Q23" s="64" t="s">
-        <v>180</v>
-      </c>
-      <c r="R23" s="65">
+      <c r="Q23" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="R23" s="60">
         <v>0.38190000000000002</v>
       </c>
-      <c r="S23" s="66">
+      <c r="S23" s="61">
         <f t="shared" si="2"/>
         <v>4.5828000000000007</v>
       </c>
-      <c r="T23" s="65">
+      <c r="T23" s="60">
         <v>0.38190000000000002</v>
       </c>
-      <c r="U23" s="55">
+      <c r="U23" s="51">
         <f t="shared" si="3"/>
         <v>10.693200000000001</v>
       </c>
       <c r="V23" s="43"/>
-      <c r="W23" s="113"/>
-      <c r="Y23" s="79"/>
-      <c r="Z23" s="79"/>
-      <c r="AA23" s="79"/>
+      <c r="W23" s="100"/>
+      <c r="Y23" s="67"/>
+      <c r="Z23" s="67"/>
+      <c r="AA23" s="67"/>
     </row>
     <row r="24" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
-      <c r="B24" s="126">
-        <f>ROW(B24) - ROW($B$9)</f>
+      <c r="B24" s="106">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="122" t="s">
-        <v>166</v>
-      </c>
-      <c r="D24" s="41" t="s">
+      <c r="C24" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="D24" s="135" t="s">
         <v>21</v>
       </c>
       <c r="E24" s="41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F24" s="41" t="s">
-        <v>161</v>
-      </c>
-      <c r="G24" s="41">
+        <v>157</v>
+      </c>
+      <c r="G24" s="44">
         <v>61300311121</v>
       </c>
       <c r="H24" s="41" t="s">
-        <v>125</v>
-      </c>
-      <c r="I24" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="J24" s="58" t="s">
-        <v>217</v>
+        <v>122</v>
+      </c>
+      <c r="I24" s="54" t="s">
+        <v>211</v>
+      </c>
+      <c r="J24" s="54" t="s">
+        <v>212</v>
       </c>
       <c r="K24" s="41" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L24" s="41">
         <v>1</v>
@@ -3430,17 +3479,17 @@
       <c r="P24" s="41">
         <v>50</v>
       </c>
-      <c r="Q24" s="61" t="s">
-        <v>180</v>
-      </c>
-      <c r="R24" s="68">
+      <c r="Q24" s="56" t="s">
+        <v>176</v>
+      </c>
+      <c r="R24" s="63">
         <v>1.5100000000000001E-2</v>
       </c>
-      <c r="S24" s="63">
+      <c r="S24" s="58">
         <f t="shared" si="2"/>
         <v>0.755</v>
       </c>
-      <c r="T24" s="68">
+      <c r="T24" s="63">
         <v>1.5100000000000001E-2</v>
       </c>
       <c r="U24" s="42">
@@ -3448,43 +3497,43 @@
         <v>0.755</v>
       </c>
       <c r="V24" s="41"/>
-      <c r="W24" s="114"/>
-      <c r="Y24" s="79"/>
-      <c r="Z24" s="79"/>
-      <c r="AA24" s="79"/>
+      <c r="W24" s="101"/>
+      <c r="Y24" s="67"/>
+      <c r="Z24" s="67"/>
+      <c r="AA24" s="67"/>
     </row>
     <row r="25" spans="1:27" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="B25" s="126">
+      <c r="B25" s="106">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="121" t="s">
-        <v>167</v>
-      </c>
-      <c r="D25" s="43" t="s">
+      <c r="C25" s="138" t="s">
+        <v>163</v>
+      </c>
+      <c r="D25" s="134" t="s">
         <v>22</v>
       </c>
       <c r="E25" s="43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F25" s="43" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G25" s="45" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H25" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="I25" s="87" t="s">
-        <v>182</v>
-      </c>
-      <c r="J25" s="88" t="s">
-        <v>218</v>
+        <v>123</v>
+      </c>
+      <c r="I25" s="75" t="s">
+        <v>178</v>
+      </c>
+      <c r="J25" s="76" t="s">
+        <v>213</v>
       </c>
       <c r="K25" s="43" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L25" s="43">
         <v>6</v>
@@ -3503,63 +3552,63 @@
       <c r="P25" s="43">
         <v>160</v>
       </c>
-      <c r="Q25" s="64" t="s">
-        <v>180</v>
-      </c>
-      <c r="R25" s="65">
+      <c r="Q25" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="R25" s="60">
         <v>2.3800000000000002E-2</v>
       </c>
-      <c r="S25" s="66">
+      <c r="S25" s="61">
         <f t="shared" si="2"/>
         <v>1.9040000000000001</v>
       </c>
-      <c r="T25" s="65">
+      <c r="T25" s="60">
         <v>2.3800000000000002E-2</v>
       </c>
-      <c r="U25" s="55">
+      <c r="U25" s="51">
         <f t="shared" si="3"/>
         <v>3.8080000000000003</v>
       </c>
       <c r="V25" s="43" t="s">
-        <v>215</v>
-      </c>
-      <c r="W25" s="113"/>
-      <c r="Y25" s="79"/>
-      <c r="Z25" s="79"/>
-      <c r="AA25" s="79"/>
+        <v>210</v>
+      </c>
+      <c r="W25" s="100"/>
+      <c r="Y25" s="67"/>
+      <c r="Z25" s="67"/>
+      <c r="AA25" s="67"/>
     </row>
     <row r="26" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
-      <c r="B26" s="126">
-        <f>ROW(B26) - ROW($B$9)</f>
+      <c r="B26" s="106">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="122" t="s">
-        <v>168</v>
-      </c>
-      <c r="D26" s="41" t="s">
+      <c r="C26" s="139" t="s">
+        <v>164</v>
+      </c>
+      <c r="D26" s="135" t="s">
         <v>23</v>
       </c>
       <c r="E26" s="41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F26" s="41" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G26" s="44" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H26" s="41" t="s">
-        <v>127</v>
-      </c>
-      <c r="I26" s="70" t="s">
-        <v>219</v>
-      </c>
-      <c r="J26" s="70" t="s">
-        <v>220</v>
+        <v>124</v>
+      </c>
+      <c r="I26" s="65" t="s">
+        <v>214</v>
+      </c>
+      <c r="J26" s="65" t="s">
+        <v>215</v>
       </c>
       <c r="K26" s="41" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="L26" s="41">
         <v>2</v>
@@ -3578,17 +3627,17 @@
       <c r="P26" s="41">
         <v>60</v>
       </c>
-      <c r="Q26" s="61" t="s">
-        <v>180</v>
-      </c>
-      <c r="R26" s="62">
+      <c r="Q26" s="56" t="s">
+        <v>176</v>
+      </c>
+      <c r="R26" s="57">
         <v>7.4499999999999997E-2</v>
       </c>
-      <c r="S26" s="63">
+      <c r="S26" s="58">
         <f t="shared" si="2"/>
         <v>2.2349999999999999</v>
       </c>
-      <c r="T26" s="62">
+      <c r="T26" s="57">
         <v>7.4499999999999997E-2</v>
       </c>
       <c r="U26" s="42">
@@ -3596,43 +3645,43 @@
         <v>4.47</v>
       </c>
       <c r="V26" s="46"/>
-      <c r="W26" s="114"/>
-      <c r="Y26" s="79"/>
-      <c r="Z26" s="79"/>
-      <c r="AA26" s="79"/>
+      <c r="W26" s="101"/>
+      <c r="Y26" s="67"/>
+      <c r="Z26" s="67"/>
+      <c r="AA26" s="67"/>
     </row>
     <row r="27" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
-      <c r="B27" s="126">
+      <c r="B27" s="106">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="121" t="s">
-        <v>168</v>
-      </c>
-      <c r="D27" s="43" t="s">
+      <c r="C27" s="138" t="s">
+        <v>164</v>
+      </c>
+      <c r="D27" s="134" t="s">
         <v>24</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F27" s="43" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G27" s="45" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H27" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="I27" s="87" t="s">
-        <v>181</v>
-      </c>
-      <c r="J27" s="69" t="s">
-        <v>221</v>
+        <v>125</v>
+      </c>
+      <c r="I27" s="75" t="s">
+        <v>177</v>
+      </c>
+      <c r="J27" s="64" t="s">
+        <v>216</v>
       </c>
       <c r="K27" s="43" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="L27" s="43">
         <v>1</v>
@@ -3651,61 +3700,61 @@
       <c r="P27" s="43">
         <v>50</v>
       </c>
-      <c r="Q27" s="64" t="s">
-        <v>180</v>
-      </c>
-      <c r="R27" s="65">
+      <c r="Q27" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="R27" s="60">
         <v>1.5299999999999999E-2</v>
       </c>
-      <c r="S27" s="66">
+      <c r="S27" s="61">
         <f>R27*N27</f>
         <v>0.76500000000000001</v>
       </c>
-      <c r="T27" s="65">
+      <c r="T27" s="60">
         <v>1.5299999999999999E-2</v>
       </c>
-      <c r="U27" s="55">
+      <c r="U27" s="51">
         <f t="shared" si="3"/>
         <v>0.76500000000000001</v>
       </c>
       <c r="V27" s="43"/>
-      <c r="W27" s="113"/>
-      <c r="Y27" s="79"/>
-      <c r="Z27" s="79"/>
-      <c r="AA27" s="79"/>
+      <c r="W27" s="100"/>
+      <c r="Y27" s="67"/>
+      <c r="Z27" s="67"/>
+      <c r="AA27" s="67"/>
     </row>
     <row r="28" spans="1:27" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
-      <c r="B28" s="126">
-        <f>ROW(B28) - ROW($B$9)</f>
+      <c r="B28" s="106">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="122" t="s">
-        <v>168</v>
-      </c>
-      <c r="D28" s="41" t="s">
+      <c r="C28" s="139" t="s">
+        <v>164</v>
+      </c>
+      <c r="D28" s="135" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F28" s="41" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G28" s="41" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H28" s="41" t="s">
-        <v>114</v>
-      </c>
-      <c r="I28" s="71" t="s">
-        <v>188</v>
+        <v>111</v>
+      </c>
+      <c r="I28" s="66" t="s">
+        <v>184</v>
       </c>
       <c r="J28" s="41" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="K28" s="41" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L28" s="41">
         <v>11</v>
@@ -3724,17 +3773,17 @@
       <c r="P28" s="41">
         <v>300</v>
       </c>
-      <c r="Q28" s="61" t="s">
-        <v>180</v>
-      </c>
-      <c r="R28" s="62">
+      <c r="Q28" s="56" t="s">
+        <v>176</v>
+      </c>
+      <c r="R28" s="57">
         <v>1.4E-3</v>
       </c>
-      <c r="S28" s="63">
+      <c r="S28" s="58">
         <f t="shared" si="2"/>
         <v>0.27999999999999997</v>
       </c>
-      <c r="T28" s="62">
+      <c r="T28" s="57">
         <v>1.4E-3</v>
       </c>
       <c r="U28" s="42">
@@ -3742,262 +3791,266 @@
         <v>0.42</v>
       </c>
       <c r="V28" s="41"/>
-      <c r="W28" s="114"/>
-      <c r="Y28" s="79"/>
-      <c r="Z28" s="79"/>
-      <c r="AA28" s="79"/>
+      <c r="W28" s="101"/>
+      <c r="Y28" s="67"/>
+      <c r="Z28" s="67"/>
+      <c r="AA28" s="67"/>
     </row>
     <row r="29" spans="1:27" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
-      <c r="B29" s="126">
+      <c r="B29" s="106">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="121" t="s">
-        <v>168</v>
-      </c>
-      <c r="D29" s="43" t="s">
-        <v>26</v>
+      <c r="C29" s="138" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29" s="136" t="s">
+        <v>225</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>58</v>
+        <v>226</v>
       </c>
       <c r="F29" s="43" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G29" s="43" t="s">
-        <v>102</v>
+        <v>227</v>
       </c>
       <c r="H29" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="I29" s="59" t="s">
-        <v>188</v>
+        <v>111</v>
+      </c>
+      <c r="I29" s="43" t="s">
+        <v>184</v>
       </c>
       <c r="J29" s="43" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="K29" s="43" t="s">
-        <v>149</v>
-      </c>
-      <c r="L29" s="43">
-        <v>13</v>
+        <v>229</v>
+      </c>
+      <c r="L29" s="105">
+        <v>1</v>
       </c>
       <c r="M29" s="43">
         <f t="shared" si="4"/>
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="N29" s="43">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O29" s="43">
         <f t="shared" si="1"/>
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="P29" s="43">
-        <v>400</v>
-      </c>
-      <c r="Q29" s="64" t="s">
-        <v>180</v>
-      </c>
-      <c r="R29" s="65">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="S29" s="66">
-        <f t="shared" si="2"/>
-        <v>0.22</v>
-      </c>
-      <c r="T29" s="65">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="U29" s="55">
-        <f t="shared" si="3"/>
-        <v>0.44</v>
-      </c>
-      <c r="V29" s="43"/>
-      <c r="W29" s="113"/>
-      <c r="Y29" s="79"/>
-      <c r="Z29" s="79"/>
-      <c r="AA29" s="79"/>
+        <v>100</v>
+      </c>
+      <c r="Q29" s="116" t="s">
+        <v>176</v>
+      </c>
+      <c r="R29" s="60">
+        <v>1E-3</v>
+      </c>
+      <c r="S29" s="61">
+        <f>R29*N29</f>
+        <v>0.1</v>
+      </c>
+      <c r="T29" s="60">
+        <v>1E-3</v>
+      </c>
+      <c r="U29" s="51">
+        <f>T29*P29</f>
+        <v>0.1</v>
+      </c>
+      <c r="V29" s="132" t="s">
+        <v>232</v>
+      </c>
+      <c r="W29" s="100"/>
+      <c r="Y29" s="67"/>
+      <c r="Z29" s="67"/>
+      <c r="AA29" s="67"/>
     </row>
     <row r="30" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
-      <c r="B30" s="126">
-        <f>ROW(B30) - ROW($B$9)</f>
+      <c r="B30" s="106">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="122" t="s">
-        <v>168</v>
-      </c>
-      <c r="D30" s="41" t="s">
-        <v>27</v>
+      <c r="C30" s="139" t="s">
+        <v>164</v>
+      </c>
+      <c r="D30" s="135" t="s">
+        <v>26</v>
       </c>
       <c r="E30" s="41" t="s">
-        <v>59</v>
+        <v>230</v>
       </c>
       <c r="F30" s="41" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G30" s="41" t="s">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="H30" s="41" t="s">
-        <v>114</v>
-      </c>
-      <c r="I30" s="58" t="s">
-        <v>188</v>
-      </c>
-      <c r="J30" s="58" t="s">
-        <v>202</v>
+        <v>184</v>
+      </c>
+      <c r="I30" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="J30" s="54" t="s">
+        <v>184</v>
       </c>
       <c r="K30" s="41" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="L30" s="41">
         <v>1</v>
       </c>
       <c r="M30" s="41">
-        <f t="shared" si="4"/>
+        <f>L30*10</f>
         <v>10</v>
       </c>
-      <c r="N30" s="41">
-        <v>100</v>
+      <c r="N30" s="41" t="s">
+        <v>184</v>
       </c>
       <c r="O30" s="41">
         <f>L30*25</f>
         <v>25</v>
       </c>
-      <c r="P30" s="41">
-        <v>100</v>
-      </c>
-      <c r="Q30" s="61" t="s">
-        <v>180</v>
-      </c>
-      <c r="R30" s="62">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="S30" s="63">
-        <f t="shared" si="2"/>
-        <v>0.13</v>
-      </c>
-      <c r="T30" s="62">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="U30" s="42">
-        <f t="shared" si="3"/>
-        <v>0.13</v>
-      </c>
-      <c r="V30" s="41"/>
-      <c r="W30" s="114"/>
-      <c r="Y30" s="79"/>
-      <c r="Z30" s="79"/>
-      <c r="AA30" s="79"/>
-    </row>
-    <row r="31" spans="1:27" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P30" s="41" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q30" s="56" t="s">
+        <v>184</v>
+      </c>
+      <c r="R30" s="57" t="s">
+        <v>184</v>
+      </c>
+      <c r="S30" s="58" t="s">
+        <v>184</v>
+      </c>
+      <c r="T30" s="57" t="s">
+        <v>184</v>
+      </c>
+      <c r="U30" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="V30" s="41" t="s">
+        <v>184</v>
+      </c>
+      <c r="W30" s="101" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y30" s="67"/>
+      <c r="Z30" s="67"/>
+      <c r="AA30" s="67"/>
+    </row>
+    <row r="31" spans="1:27" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
-      <c r="B31" s="126">
+      <c r="B31" s="106">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="121" t="s">
-        <v>168</v>
+      <c r="C31" s="138" t="s">
+        <v>164</v>
       </c>
       <c r="D31" s="43" t="s">
-        <v>28</v>
+        <v>224</v>
       </c>
       <c r="E31" s="43" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F31" s="43" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G31" s="43" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H31" s="43" t="s">
-        <v>129</v>
-      </c>
-      <c r="I31" s="59" t="s">
-        <v>188</v>
+        <v>111</v>
+      </c>
+      <c r="I31" s="55" t="s">
+        <v>184</v>
       </c>
       <c r="J31" s="43" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="K31" s="43" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="L31" s="43">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M31" s="43">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="N31" s="43">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="O31" s="43">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="P31" s="43">
-        <v>50</v>
-      </c>
-      <c r="Q31" s="64" t="s">
-        <v>180</v>
-      </c>
-      <c r="R31" s="65">
-        <v>4.1000000000000003E-3</v>
-      </c>
-      <c r="S31" s="66">
+        <v>400</v>
+      </c>
+      <c r="Q31" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="R31" s="60">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="S31" s="61">
         <f t="shared" si="2"/>
-        <v>0.20500000000000002</v>
-      </c>
-      <c r="T31" s="65">
-        <v>4.1000000000000003E-3</v>
-      </c>
-      <c r="U31" s="55">
+        <v>0.22</v>
+      </c>
+      <c r="T31" s="60">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="U31" s="51">
         <f t="shared" si="3"/>
-        <v>0.20500000000000002</v>
+        <v>0.44</v>
       </c>
       <c r="V31" s="43"/>
-      <c r="W31" s="113"/>
-      <c r="Y31" s="79"/>
-      <c r="Z31" s="79"/>
-      <c r="AA31" s="79"/>
-    </row>
-    <row r="32" spans="1:27" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="W31" s="100"/>
+      <c r="Y31" s="67"/>
+      <c r="Z31" s="67"/>
+      <c r="AA31" s="67"/>
+    </row>
+    <row r="32" spans="1:27" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
-      <c r="B32" s="126">
-        <f>ROW(B32) - ROW($B$9)</f>
+      <c r="B32" s="106">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="122" t="s">
-        <v>168</v>
+      <c r="C32" s="139" t="s">
+        <v>164</v>
       </c>
       <c r="D32" s="41" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E32" s="41" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F32" s="41" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G32" s="41" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H32" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="I32" s="58" t="s">
-        <v>188</v>
+        <v>126</v>
+      </c>
+      <c r="I32" s="54" t="s">
+        <v>184</v>
       </c>
       <c r="J32" s="41" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="K32" s="41" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="L32" s="41">
         <v>1</v>
@@ -4007,70 +4060,70 @@
         <v>10</v>
       </c>
       <c r="N32" s="41">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="O32" s="41">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="P32" s="41">
-        <v>28</v>
-      </c>
-      <c r="Q32" s="61" t="s">
-        <v>180</v>
+        <v>50</v>
+      </c>
+      <c r="Q32" s="56" t="s">
+        <v>176</v>
       </c>
       <c r="R32" s="62">
-        <v>0.14979999999999999</v>
-      </c>
-      <c r="S32" s="63">
+        <v>4.1000000000000003E-3</v>
+      </c>
+      <c r="S32" s="58">
         <f t="shared" si="2"/>
-        <v>1.7975999999999999</v>
+        <v>0.20500000000000002</v>
       </c>
       <c r="T32" s="62">
-        <v>0.1348</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="U32" s="42">
         <f t="shared" si="3"/>
-        <v>3.7744</v>
+        <v>0.20500000000000002</v>
       </c>
       <c r="V32" s="41"/>
-      <c r="W32" s="114"/>
-      <c r="Y32" s="79"/>
-      <c r="Z32" s="79"/>
-      <c r="AA32" s="79"/>
-    </row>
-    <row r="33" spans="1:31" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="W32" s="102"/>
+      <c r="Y32" s="67"/>
+      <c r="Z32" s="67"/>
+      <c r="AA32" s="67"/>
+    </row>
+    <row r="33" spans="1:31" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
-      <c r="B33" s="126">
+      <c r="B33" s="106">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="121" t="s">
-        <v>168</v>
+      <c r="C33" s="138" t="s">
+        <v>164</v>
       </c>
       <c r="D33" s="43" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E33" s="43" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F33" s="43" t="s">
         <v>79</v>
       </c>
       <c r="G33" s="43" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H33" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="I33" s="59" t="s">
-        <v>188</v>
+        <v>127</v>
+      </c>
+      <c r="I33" s="55" t="s">
+        <v>184</v>
       </c>
       <c r="J33" s="43" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="K33" s="43" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="L33" s="43">
         <v>1</v>
@@ -4080,231 +4133,226 @@
         <v>10</v>
       </c>
       <c r="N33" s="43">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="O33" s="43">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="P33" s="43">
+        <v>28</v>
+      </c>
+      <c r="Q33" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="R33" s="60">
+        <v>0.14979999999999999</v>
+      </c>
+      <c r="S33" s="61">
+        <f t="shared" si="2"/>
+        <v>1.7975999999999999</v>
+      </c>
+      <c r="T33" s="60">
+        <v>0.1348</v>
+      </c>
+      <c r="U33" s="51">
+        <f t="shared" si="3"/>
+        <v>3.7744</v>
+      </c>
+      <c r="V33" s="43"/>
+      <c r="W33" s="100"/>
+      <c r="Y33" s="67"/>
+      <c r="Z33" s="67"/>
+      <c r="AA33" s="67"/>
+    </row>
+    <row r="34" spans="1:31" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1"/>
+      <c r="B34" s="106">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C34" s="139" t="s">
+        <v>164</v>
+      </c>
+      <c r="D34" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="E34" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="F34" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="G34" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="H34" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="I34" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="J34" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="K34" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="L34" s="41">
+        <v>1</v>
+      </c>
+      <c r="M34" s="41">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N34" s="41">
         <v>100</v>
       </c>
-      <c r="Q33" s="64" t="s">
-        <v>180</v>
-      </c>
-      <c r="R33" s="65">
+      <c r="O34" s="41">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="P34" s="41">
+        <v>100</v>
+      </c>
+      <c r="Q34" s="56" t="s">
+        <v>176</v>
+      </c>
+      <c r="R34" s="62">
         <v>1E-3</v>
       </c>
-      <c r="S33" s="66">
+      <c r="S34" s="58">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="T33" s="65">
+      <c r="T34" s="62">
         <v>1E-3</v>
       </c>
-      <c r="U33" s="55">
+      <c r="U34" s="42">
         <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
-      <c r="V33" s="43"/>
-      <c r="W33" s="113"/>
-      <c r="X33" s="79"/>
-      <c r="Y33" s="79"/>
-      <c r="Z33" s="79"/>
-      <c r="AA33" s="79"/>
-      <c r="AB33" s="79"/>
-      <c r="AC33" s="79"/>
-      <c r="AD33" s="79"/>
-      <c r="AE33" s="79"/>
-    </row>
-    <row r="34" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1"/>
-      <c r="B34" s="126">
-        <f>ROW(B34) - ROW($B$9)</f>
-        <v>25</v>
-      </c>
-      <c r="C34" s="124" t="s">
-        <v>183</v>
-      </c>
-      <c r="D34" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="F34" s="44" t="s">
-        <v>161</v>
-      </c>
-      <c r="G34" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="H34" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="I34" s="60" t="s">
-        <v>188</v>
-      </c>
-      <c r="J34" s="60" t="s">
-        <v>188</v>
-      </c>
-      <c r="K34" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="L34" s="44">
+      <c r="V34" s="41"/>
+      <c r="W34" s="102"/>
+      <c r="X34" s="67"/>
+      <c r="Y34" s="67"/>
+      <c r="Z34" s="67"/>
+      <c r="AA34" s="67"/>
+      <c r="AB34" s="67"/>
+      <c r="AC34" s="67"/>
+      <c r="AD34" s="67"/>
+      <c r="AE34" s="67"/>
+    </row>
+    <row r="35" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1"/>
+      <c r="B35" s="106">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C35" s="141" t="s">
+        <v>179</v>
+      </c>
+      <c r="D35" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="G35" s="45" t="s">
+        <v>184</v>
+      </c>
+      <c r="H35" s="45" t="s">
+        <v>184</v>
+      </c>
+      <c r="I35" s="117" t="s">
+        <v>184</v>
+      </c>
+      <c r="J35" s="117" t="s">
+        <v>184</v>
+      </c>
+      <c r="K35" s="45" t="s">
+        <v>184</v>
+      </c>
+      <c r="L35" s="45">
         <v>1</v>
       </c>
-      <c r="M34" s="44">
+      <c r="M35" s="45">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N34" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="O34" s="44">
+      <c r="N35" s="45" t="s">
+        <v>184</v>
+      </c>
+      <c r="O35" s="45">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P34" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q34" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="R34" s="72" t="s">
-        <v>188</v>
-      </c>
-      <c r="S34" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="T34" s="72" t="s">
-        <v>188</v>
-      </c>
-      <c r="U34" s="47" t="s">
-        <v>188</v>
-      </c>
-      <c r="V34" s="44" t="s">
-        <v>185</v>
-      </c>
-      <c r="W34" s="118"/>
-      <c r="X34" s="79"/>
-      <c r="Y34" s="79"/>
-      <c r="Z34" s="79"/>
-      <c r="AA34" s="79"/>
-      <c r="AB34" s="79"/>
-      <c r="AC34" s="79"/>
-      <c r="AD34" s="79"/>
-      <c r="AE34" s="79"/>
-    </row>
-    <row r="35" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1"/>
-      <c r="B35" s="126">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="C35" s="121" t="s">
-        <v>171</v>
-      </c>
-      <c r="D35" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="E35" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="F35" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="G35" s="43" t="s">
-        <v>107</v>
-      </c>
-      <c r="H35" s="43" t="s">
-        <v>132</v>
-      </c>
-      <c r="I35" s="59" t="s">
-        <v>188</v>
-      </c>
-      <c r="J35" s="59" t="s">
-        <v>206</v>
-      </c>
-      <c r="K35" s="43" t="s">
-        <v>188</v>
-      </c>
-      <c r="L35" s="43">
-        <v>1</v>
-      </c>
-      <c r="M35" s="43">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="N35" s="43">
-        <v>12</v>
-      </c>
-      <c r="O35" s="43">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="P35" s="43">
-        <v>28</v>
-      </c>
-      <c r="Q35" s="64" t="s">
-        <v>180</v>
-      </c>
-      <c r="R35" s="65">
-        <v>0.47339999999999999</v>
-      </c>
-      <c r="S35" s="66">
-        <f t="shared" si="2"/>
-        <v>5.6807999999999996</v>
-      </c>
-      <c r="T35" s="65">
-        <v>0.42870000000000003</v>
-      </c>
-      <c r="U35" s="55">
-        <f t="shared" si="3"/>
-        <v>12.0036</v>
-      </c>
-      <c r="V35" s="43"/>
-      <c r="W35" s="113"/>
-      <c r="X35" s="79"/>
-      <c r="Y35" s="79"/>
-      <c r="Z35" s="79"/>
-      <c r="AA35" s="79"/>
-      <c r="AB35" s="79"/>
-      <c r="AC35" s="79"/>
-      <c r="AD35" s="79"/>
-      <c r="AE35" s="79"/>
+      <c r="P35" s="45" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q35" s="45" t="s">
+        <v>184</v>
+      </c>
+      <c r="R35" s="118" t="s">
+        <v>184</v>
+      </c>
+      <c r="S35" s="119" t="s">
+        <v>184</v>
+      </c>
+      <c r="T35" s="118" t="s">
+        <v>184</v>
+      </c>
+      <c r="U35" s="120" t="s">
+        <v>184</v>
+      </c>
+      <c r="V35" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="W35" s="121"/>
+      <c r="X35" s="67"/>
+      <c r="Y35" s="67"/>
+      <c r="Z35" s="67"/>
+      <c r="AA35" s="67"/>
+      <c r="AB35" s="67"/>
+      <c r="AC35" s="67"/>
+      <c r="AD35" s="67"/>
+      <c r="AE35" s="67"/>
     </row>
     <row r="36" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
-      <c r="B36" s="126">
-        <f>ROW(B36) - ROW($B$9)</f>
+      <c r="B36" s="106">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="122" t="s">
-        <v>170</v>
+      <c r="C36" s="139" t="s">
+        <v>167</v>
       </c>
       <c r="D36" s="41" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E36" s="41" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F36" s="41" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="G36" s="41" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H36" s="41" t="s">
-        <v>133</v>
-      </c>
-      <c r="I36" s="58" t="s">
-        <v>188</v>
-      </c>
-      <c r="J36" s="58" t="s">
-        <v>207</v>
+        <v>129</v>
+      </c>
+      <c r="I36" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="J36" s="54" t="s">
+        <v>201</v>
       </c>
       <c r="K36" s="41" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L36" s="41">
         <v>1</v>
@@ -4321,68 +4369,68 @@
         <v>25</v>
       </c>
       <c r="P36" s="41">
-        <v>27</v>
-      </c>
-      <c r="Q36" s="61" t="s">
-        <v>180</v>
+        <v>28</v>
+      </c>
+      <c r="Q36" s="56" t="s">
+        <v>176</v>
       </c>
       <c r="R36" s="62">
-        <v>9.0368999999999993</v>
-      </c>
-      <c r="S36" s="63">
+        <v>0.47339999999999999</v>
+      </c>
+      <c r="S36" s="58">
         <f t="shared" si="2"/>
-        <v>108.44279999999999</v>
+        <v>5.6807999999999996</v>
       </c>
       <c r="T36" s="62">
-        <v>9.0368999999999993</v>
+        <v>0.42870000000000003</v>
       </c>
       <c r="U36" s="42">
         <f t="shared" si="3"/>
-        <v>243.99629999999999</v>
+        <v>12.0036</v>
       </c>
       <c r="V36" s="41"/>
-      <c r="W36" s="114"/>
-      <c r="X36" s="79"/>
-      <c r="Y36" s="79"/>
-      <c r="Z36" s="79"/>
-      <c r="AA36" s="79"/>
-      <c r="AB36" s="79"/>
-      <c r="AC36" s="79"/>
-      <c r="AD36" s="79"/>
-      <c r="AE36" s="79"/>
+      <c r="W36" s="102"/>
+      <c r="X36" s="67"/>
+      <c r="Y36" s="67"/>
+      <c r="Z36" s="67"/>
+      <c r="AA36" s="67"/>
+      <c r="AB36" s="67"/>
+      <c r="AC36" s="67"/>
+      <c r="AD36" s="67"/>
+      <c r="AE36" s="67"/>
     </row>
     <row r="37" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
-      <c r="B37" s="126">
+      <c r="B37" s="106">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="121" t="s">
-        <v>170</v>
+      <c r="C37" s="138" t="s">
+        <v>166</v>
       </c>
       <c r="D37" s="43" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E37" s="43" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F37" s="43" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G37" s="43" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H37" s="43" t="s">
-        <v>133</v>
-      </c>
-      <c r="I37" s="59" t="s">
-        <v>188</v>
-      </c>
-      <c r="J37" s="59" t="s">
-        <v>208</v>
+        <v>130</v>
+      </c>
+      <c r="I37" s="55" t="s">
+        <v>184</v>
+      </c>
+      <c r="J37" s="55" t="s">
+        <v>202</v>
       </c>
       <c r="K37" s="43" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L37" s="43">
         <v>1</v>
@@ -4401,66 +4449,66 @@
       <c r="P37" s="43">
         <v>27</v>
       </c>
-      <c r="Q37" s="64" t="s">
-        <v>180</v>
-      </c>
-      <c r="R37" s="65">
-        <v>0.54910000000000003</v>
-      </c>
-      <c r="S37" s="66">
+      <c r="Q37" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="R37" s="60">
+        <v>9.0368999999999993</v>
+      </c>
+      <c r="S37" s="61">
         <f t="shared" si="2"/>
-        <v>6.5891999999999999</v>
-      </c>
-      <c r="T37" s="65">
-        <v>0.54910000000000003</v>
-      </c>
-      <c r="U37" s="55">
+        <v>108.44279999999999</v>
+      </c>
+      <c r="T37" s="60">
+        <v>9.0368999999999993</v>
+      </c>
+      <c r="U37" s="51">
         <f t="shared" si="3"/>
-        <v>14.825700000000001</v>
+        <v>243.99629999999999</v>
       </c>
       <c r="V37" s="43"/>
-      <c r="W37" s="113"/>
-      <c r="X37" s="79"/>
-      <c r="Y37" s="79"/>
-      <c r="Z37" s="79"/>
-      <c r="AA37" s="79"/>
-      <c r="AB37" s="79"/>
-      <c r="AC37" s="79"/>
-      <c r="AD37" s="79"/>
-      <c r="AE37" s="79"/>
+      <c r="W37" s="100"/>
+      <c r="X37" s="67"/>
+      <c r="Y37" s="67"/>
+      <c r="Z37" s="67"/>
+      <c r="AA37" s="67"/>
+      <c r="AB37" s="67"/>
+      <c r="AC37" s="67"/>
+      <c r="AD37" s="67"/>
+      <c r="AE37" s="67"/>
     </row>
     <row r="38" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
-      <c r="B38" s="126">
-        <f>ROW(B38) - ROW($B$9)</f>
+      <c r="B38" s="106">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="122" t="s">
-        <v>170</v>
+      <c r="C38" s="139" t="s">
+        <v>166</v>
       </c>
       <c r="D38" s="41" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E38" s="41" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F38" s="41" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G38" s="41" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H38" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="I38" s="58" t="s">
-        <v>188</v>
-      </c>
-      <c r="J38" s="58" t="s">
-        <v>209</v>
+        <v>130</v>
+      </c>
+      <c r="I38" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="J38" s="54" t="s">
+        <v>203</v>
       </c>
       <c r="K38" s="41" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L38" s="41">
         <v>1</v>
@@ -4479,61 +4527,66 @@
       <c r="P38" s="41">
         <v>27</v>
       </c>
-      <c r="Q38" s="61" t="s">
-        <v>180</v>
+      <c r="Q38" s="56" t="s">
+        <v>176</v>
       </c>
       <c r="R38" s="62">
-        <v>0.32369999999999999</v>
-      </c>
-      <c r="S38" s="63">
+        <v>0.54910000000000003</v>
+      </c>
+      <c r="S38" s="58">
         <f t="shared" si="2"/>
-        <v>3.8843999999999999</v>
+        <v>6.5891999999999999</v>
       </c>
       <c r="T38" s="62">
-        <v>0.32369999999999999</v>
+        <v>0.54910000000000003</v>
       </c>
       <c r="U38" s="42">
         <f t="shared" si="3"/>
-        <v>8.7399000000000004</v>
+        <v>14.825700000000001</v>
       </c>
       <c r="V38" s="41"/>
-      <c r="W38" s="114"/>
-      <c r="Y38" s="79"/>
-      <c r="Z38" s="79"/>
-      <c r="AA38" s="79"/>
+      <c r="W38" s="102"/>
+      <c r="X38" s="67"/>
+      <c r="Y38" s="67"/>
+      <c r="Z38" s="67"/>
+      <c r="AA38" s="67"/>
+      <c r="AB38" s="67"/>
+      <c r="AC38" s="67"/>
+      <c r="AD38" s="67"/>
+      <c r="AE38" s="67"/>
     </row>
     <row r="39" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
-      <c r="B39" s="126">
+      <c r="B39" s="106">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="121" t="s">
+      <c r="C39" s="138" t="s">
         <v>166</v>
       </c>
       <c r="D39" s="43" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E39" s="43" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F39" s="43" t="s">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="G39" s="43" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H39" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="I39" s="59" t="s">
-        <v>188</v>
-      </c>
-      <c r="J39" s="59" t="s">
-        <v>210</v>
+        <v>131</v>
+      </c>
+      <c r="I39" s="55" t="s">
+        <v>184</v>
+      </c>
+      <c r="J39" s="55" t="s">
+        <v>204</v>
       </c>
       <c r="K39" s="43" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L39" s="43">
         <v>1</v>
@@ -4543,329 +4596,402 @@
         <v>10</v>
       </c>
       <c r="N39" s="43">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O39" s="43">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="P39" s="43">
+        <v>27</v>
+      </c>
+      <c r="Q39" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="R39" s="60">
+        <v>0.32369999999999999</v>
+      </c>
+      <c r="S39" s="61">
+        <f t="shared" si="2"/>
+        <v>3.8843999999999999</v>
+      </c>
+      <c r="T39" s="60">
+        <v>0.32369999999999999</v>
+      </c>
+      <c r="U39" s="51">
+        <f t="shared" si="3"/>
+        <v>8.7399000000000004</v>
+      </c>
+      <c r="V39" s="43"/>
+      <c r="W39" s="100"/>
+      <c r="Y39" s="67"/>
+      <c r="Z39" s="67"/>
+      <c r="AA39" s="67"/>
+    </row>
+    <row r="40" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+      <c r="B40" s="106">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="D40" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="F40" s="41" t="s">
+        <v>157</v>
+      </c>
+      <c r="G40" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="H40" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="I40" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="J40" s="54" t="s">
+        <v>205</v>
+      </c>
+      <c r="K40" s="41" t="s">
+        <v>184</v>
+      </c>
+      <c r="L40" s="41">
+        <v>1</v>
+      </c>
+      <c r="M40" s="41">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N40" s="41">
+        <v>15</v>
+      </c>
+      <c r="O40" s="41">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="P40" s="41">
         <v>30</v>
       </c>
-      <c r="Q39" s="64" t="s">
-        <v>180</v>
-      </c>
-      <c r="R39" s="65">
+      <c r="Q40" s="56" t="s">
+        <v>176</v>
+      </c>
+      <c r="R40" s="62">
         <v>0.27360000000000001</v>
       </c>
-      <c r="S39" s="66">
+      <c r="S40" s="58">
         <f t="shared" si="2"/>
         <v>4.1040000000000001</v>
       </c>
-      <c r="T39" s="65">
+      <c r="T40" s="62">
         <v>0.27360000000000001</v>
       </c>
-      <c r="U39" s="55">
+      <c r="U40" s="42">
         <f t="shared" si="3"/>
         <v>8.2080000000000002</v>
       </c>
-      <c r="V39" s="43"/>
-      <c r="W39" s="113"/>
-      <c r="Y39" s="79"/>
-      <c r="Z39" s="79"/>
-      <c r="AA39" s="79"/>
-    </row>
-    <row r="40" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1"/>
-      <c r="B40" s="126">
-        <f>ROW(B40) - ROW($B$9)</f>
-        <v>31</v>
-      </c>
-      <c r="C40" s="125" t="s">
-        <v>169</v>
-      </c>
-      <c r="D40" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="E40" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="F40" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="G40" s="51" t="s">
-        <v>112</v>
-      </c>
-      <c r="H40" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="I40" s="74" t="s">
-        <v>184</v>
-      </c>
-      <c r="J40" s="75" t="s">
-        <v>222</v>
-      </c>
-      <c r="K40" s="50" t="s">
-        <v>154</v>
-      </c>
-      <c r="L40" s="50">
+      <c r="V40" s="41"/>
+      <c r="W40" s="102"/>
+      <c r="Y40" s="67"/>
+      <c r="Z40" s="67"/>
+      <c r="AA40" s="67"/>
+    </row>
+    <row r="41" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="106">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C41" s="142" t="s">
+        <v>165</v>
+      </c>
+      <c r="D41" s="122" t="s">
+        <v>36</v>
+      </c>
+      <c r="E41" s="122" t="s">
+        <v>67</v>
+      </c>
+      <c r="F41" s="122" t="s">
+        <v>157</v>
+      </c>
+      <c r="G41" s="123" t="s">
+        <v>109</v>
+      </c>
+      <c r="H41" s="122" t="s">
+        <v>133</v>
+      </c>
+      <c r="I41" s="124" t="s">
+        <v>180</v>
+      </c>
+      <c r="J41" s="125" t="s">
+        <v>217</v>
+      </c>
+      <c r="K41" s="122" t="s">
+        <v>150</v>
+      </c>
+      <c r="L41" s="122">
         <v>1</v>
       </c>
-      <c r="M40" s="50">
+      <c r="M41" s="122">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N40" s="50">
+      <c r="N41" s="122">
         <v>15</v>
       </c>
-      <c r="O40" s="50">
+      <c r="O41" s="122">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="P40" s="50">
+      <c r="P41" s="122">
         <v>30</v>
       </c>
-      <c r="Q40" s="76" t="s">
-        <v>180</v>
-      </c>
-      <c r="R40" s="77">
+      <c r="Q41" s="126" t="s">
+        <v>176</v>
+      </c>
+      <c r="R41" s="127">
         <v>0.26910000000000001</v>
       </c>
-      <c r="S40" s="78">
+      <c r="S41" s="128">
         <f t="shared" si="2"/>
         <v>4.0365000000000002</v>
       </c>
-      <c r="T40" s="77">
+      <c r="T41" s="127">
         <v>0.26910000000000001</v>
       </c>
-      <c r="U40" s="52">
+      <c r="U41" s="129">
         <f t="shared" si="3"/>
         <v>8.0730000000000004</v>
       </c>
-      <c r="V40" s="89" t="s">
-        <v>214</v>
-      </c>
-      <c r="W40" s="119"/>
-      <c r="Y40" s="79"/>
-      <c r="Z40" s="79"/>
-      <c r="AA40" s="79"/>
-    </row>
-    <row r="41" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="1"/>
-      <c r="B41" s="24"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="56"/>
-      <c r="I41" s="56"/>
-      <c r="J41" s="56"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="28"/>
-      <c r="M41" s="28"/>
-      <c r="N41" s="28"/>
-      <c r="O41" s="28"/>
-      <c r="P41" s="28"/>
-      <c r="Q41" s="133" t="s">
-        <v>186</v>
-      </c>
-      <c r="R41" s="134"/>
-      <c r="S41" s="99">
-        <f>SUM(S10:S40)</f>
-        <v>177.0273</v>
-      </c>
-      <c r="T41" s="53"/>
-      <c r="U41" s="99">
-        <f>SUM(U10:U40)</f>
-        <v>389.72649999999999</v>
-      </c>
-      <c r="V41" s="53"/>
-      <c r="W41" s="54"/>
-      <c r="Y41" s="79"/>
-      <c r="Z41" s="79"/>
-    </row>
-    <row r="42" spans="1:31" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V41" s="130" t="s">
+        <v>209</v>
+      </c>
+      <c r="W41" s="131"/>
+      <c r="Y41" s="67"/>
+      <c r="Z41" s="67"/>
+      <c r="AA41" s="67"/>
+    </row>
+    <row r="42" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="B42" s="20"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="57"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-      <c r="N42" s="7"/>
-      <c r="O42" s="7"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="135" t="s">
-        <v>187</v>
-      </c>
-      <c r="R42" s="136"/>
-      <c r="S42" s="100">
-        <f>S41/10</f>
-        <v>17.702729999999999</v>
-      </c>
-      <c r="T42" s="48"/>
-      <c r="U42" s="100">
-        <f>U41/25</f>
-        <v>15.58906</v>
-      </c>
-      <c r="V42" s="48"/>
-      <c r="W42" s="49"/>
-      <c r="Y42" s="79"/>
-      <c r="Z42" s="79"/>
-    </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="Y43" s="79"/>
-      <c r="Z43" s="79"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="28"/>
+      <c r="N42" s="28"/>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="112" t="s">
+        <v>182</v>
+      </c>
+      <c r="R42" s="113"/>
+      <c r="S42" s="86">
+        <f>SUM(S10:S41)</f>
+        <v>176.9973</v>
+      </c>
+      <c r="T42" s="49"/>
+      <c r="U42" s="86">
+        <f>SUM(U10:U41)</f>
+        <v>389.69649999999996</v>
+      </c>
+      <c r="V42" s="49"/>
+      <c r="W42" s="50"/>
+      <c r="Y42" s="67"/>
+      <c r="Z42" s="67"/>
+    </row>
+    <row r="43" spans="1:31" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="53"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7"/>
+      <c r="M43" s="7"/>
+      <c r="N43" s="7"/>
+      <c r="O43" s="7"/>
+      <c r="P43" s="7"/>
+      <c r="Q43" s="114" t="s">
+        <v>183</v>
+      </c>
+      <c r="R43" s="115"/>
+      <c r="S43" s="87">
+        <f>S42/10</f>
+        <v>17.699729999999999</v>
+      </c>
+      <c r="T43" s="47"/>
+      <c r="U43" s="87">
+        <f>U42/25</f>
+        <v>15.587859999999999</v>
+      </c>
+      <c r="V43" s="47"/>
+      <c r="W43" s="48"/>
+      <c r="Y43" s="67"/>
+      <c r="Z43" s="67"/>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="Y44" s="79"/>
-      <c r="Z44" s="79"/>
+      <c r="Y44" s="67"/>
+      <c r="Z44" s="67"/>
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="Y45" s="79"/>
-      <c r="Z45" s="79"/>
+      <c r="Y45" s="67"/>
+      <c r="Z45" s="67"/>
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="Y46" s="79"/>
-      <c r="Z46" s="79"/>
+      <c r="Y46" s="67"/>
+      <c r="Z46" s="67"/>
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="Y47" s="79"/>
-      <c r="Z47" s="79"/>
+      <c r="Y47" s="67"/>
+      <c r="Z47" s="67"/>
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="Y48" s="79"/>
-      <c r="Z48" s="79"/>
+      <c r="Y48" s="67"/>
+      <c r="Z48" s="67"/>
     </row>
     <row r="49" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y49" s="79"/>
-      <c r="Z49" s="79"/>
+      <c r="Y49" s="67"/>
+      <c r="Z49" s="67"/>
     </row>
     <row r="50" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y50" s="79"/>
-      <c r="Z50" s="79"/>
+      <c r="Y50" s="67"/>
+      <c r="Z50" s="67"/>
     </row>
     <row r="51" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y51" s="79"/>
-      <c r="Z51" s="79"/>
+      <c r="Y51" s="67"/>
+      <c r="Z51" s="67"/>
     </row>
     <row r="52" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y52" s="79"/>
-      <c r="Z52" s="79"/>
+      <c r="Y52" s="67"/>
+      <c r="Z52" s="67"/>
     </row>
     <row r="53" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y53" s="79"/>
-      <c r="Z53" s="79"/>
+      <c r="Y53" s="67"/>
+      <c r="Z53" s="67"/>
     </row>
     <row r="54" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y54" s="79"/>
-      <c r="Z54" s="79"/>
+      <c r="Y54" s="67"/>
+      <c r="Z54" s="67"/>
     </row>
     <row r="55" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y55" s="79"/>
-      <c r="Z55" s="79"/>
+      <c r="Y55" s="67"/>
+      <c r="Z55" s="67"/>
     </row>
     <row r="56" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y56" s="79"/>
-      <c r="Z56" s="79"/>
+      <c r="Y56" s="67"/>
+      <c r="Z56" s="67"/>
     </row>
     <row r="57" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y57" s="79"/>
-      <c r="Z57" s="79"/>
+      <c r="Y57" s="67"/>
+      <c r="Z57" s="67"/>
     </row>
     <row r="58" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y58" s="79"/>
-      <c r="Z58" s="79"/>
+      <c r="Y58" s="67"/>
+      <c r="Z58" s="67"/>
     </row>
     <row r="59" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y59" s="79"/>
-      <c r="Z59" s="79"/>
+      <c r="Y59" s="67"/>
+      <c r="Z59" s="67"/>
     </row>
     <row r="60" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y60" s="79"/>
-      <c r="Z60" s="79"/>
+      <c r="Y60" s="67"/>
+      <c r="Z60" s="67"/>
     </row>
     <row r="61" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y61" s="79"/>
-      <c r="Z61" s="79"/>
+      <c r="Y61" s="67"/>
+      <c r="Z61" s="67"/>
     </row>
     <row r="62" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y62" s="79"/>
-      <c r="Z62" s="79"/>
+      <c r="Y62" s="67"/>
+      <c r="Z62" s="67"/>
     </row>
     <row r="63" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y63" s="79"/>
-      <c r="Z63" s="79"/>
+      <c r="Y63" s="67"/>
+      <c r="Z63" s="67"/>
     </row>
     <row r="64" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y64" s="79"/>
-      <c r="Z64" s="79"/>
+      <c r="Y64" s="67"/>
+      <c r="Z64" s="67"/>
     </row>
     <row r="65" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y65" s="79"/>
-      <c r="Z65" s="79"/>
+      <c r="Y65" s="67"/>
+      <c r="Z65" s="67"/>
     </row>
     <row r="66" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y66" s="79"/>
-      <c r="Z66" s="79"/>
+      <c r="Y66" s="67"/>
+      <c r="Z66" s="67"/>
     </row>
     <row r="67" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y67" s="79"/>
-      <c r="Z67" s="79"/>
+      <c r="Y67" s="67"/>
+      <c r="Z67" s="67"/>
     </row>
     <row r="68" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y68" s="79"/>
-      <c r="Z68" s="79"/>
+      <c r="Y68" s="67"/>
+      <c r="Z68" s="67"/>
     </row>
     <row r="69" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y69" s="79"/>
-      <c r="Z69" s="79"/>
+      <c r="Y69" s="67"/>
+      <c r="Z69" s="67"/>
     </row>
     <row r="70" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y70" s="79"/>
-      <c r="Z70" s="79"/>
+      <c r="Y70" s="67"/>
+      <c r="Z70" s="67"/>
     </row>
     <row r="71" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Z71" s="79"/>
+      <c r="Y71" s="67"/>
+      <c r="Z71" s="67"/>
     </row>
     <row r="72" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y72" s="79"/>
-      <c r="Z72" s="79"/>
+      <c r="Z72" s="67"/>
     </row>
     <row r="73" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y73" s="79"/>
-      <c r="Z73" s="79"/>
+      <c r="Y73" s="67"/>
+      <c r="Z73" s="67"/>
     </row>
     <row r="74" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y74" s="79"/>
-      <c r="Z74" s="79"/>
+      <c r="Y74" s="67"/>
+      <c r="Z74" s="67"/>
     </row>
     <row r="75" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y75" s="79"/>
-      <c r="Z75" s="79"/>
+      <c r="Y75" s="67"/>
+      <c r="Z75" s="67"/>
     </row>
     <row r="76" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y76" s="79"/>
-      <c r="Z76" s="79"/>
+      <c r="Y76" s="67"/>
+      <c r="Z76" s="67"/>
     </row>
     <row r="77" spans="25:26" x14ac:dyDescent="0.25">
-      <c r="Y77" s="79"/>
-      <c r="Z77" s="79"/>
+      <c r="Y77" s="67"/>
+      <c r="Z77" s="67"/>
+    </row>
+    <row r="78" spans="25:26" x14ac:dyDescent="0.25">
+      <c r="Y78" s="67"/>
+      <c r="Z78" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="W3:W8"/>
     <mergeCell ref="S2:W2"/>
-    <mergeCell ref="Q41:R41"/>
     <mergeCell ref="Q42:R42"/>
+    <mergeCell ref="Q43:R43"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="Q10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -4883,21 +5009,21 @@
     <hyperlink ref="Q26" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
     <hyperlink ref="Q27" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
     <hyperlink ref="Q28" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="Q29" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="Q30" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="Q31" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="Q32" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="Q33" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="Q36" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="Q37" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="Q38" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="Q39" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="Q20" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="Q25" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="Q35" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="Q22" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="Q40" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="Q24" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="Q31" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="Q32" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="Q33" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="Q34" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="Q37" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="Q38" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="Q39" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="Q40" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="Q20" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="Q25" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="Q36" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="Q22" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="Q41" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="Q24" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="Q29" r:id="rId30" xr:uid="{E263CBD2-4E59-41C5-B2CB-D8E722E6BA36}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId31"/>
